--- a/research/traditional_assets/database/data/croatia/croatia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_telecom_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="zgse_ernt" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0665</v>
+        <v>0.0774</v>
       </c>
       <c r="E2">
-        <v>0.099</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G2">
-        <v>0.07313341493268054</v>
+        <v>0.1166897506925208</v>
       </c>
       <c r="H2">
-        <v>0.07313341493268054</v>
+        <v>0.1166897506925208</v>
       </c>
       <c r="I2">
-        <v>0.08017135862913097</v>
+        <v>0.0706371191135734</v>
       </c>
       <c r="J2">
-        <v>0.06826995151480648</v>
+        <v>0.06015548208381735</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="L2">
-        <v>0.06731946144430845</v>
+        <v>0.06405817174515235</v>
       </c>
       <c r="M2">
-        <v>27.501</v>
+        <v>13.01</v>
       </c>
       <c r="N2">
-        <v>0.07458909682668836</v>
+        <v>0.04095058231035568</v>
       </c>
       <c r="O2">
-        <v>1.250045454545455</v>
+        <v>0.7032432432432433</v>
       </c>
       <c r="P2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q2">
-        <v>0.07323026851098455</v>
+        <v>0.03462385898646522</v>
       </c>
       <c r="R2">
-        <v>1.227272727272727</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="S2">
-        <v>0.5010000000000012</v>
+        <v>2.01</v>
       </c>
       <c r="T2">
-        <v>0.0182175193629323</v>
+        <v>0.1544965411222137</v>
       </c>
       <c r="U2">
-        <v>56.9</v>
+        <v>59.7</v>
       </c>
       <c r="V2">
-        <v>0.1543260103064822</v>
+        <v>0.1879131255901794</v>
       </c>
       <c r="W2">
-        <v>0.3697478991596639</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="X2">
-        <v>0.09300132795577531</v>
+        <v>0.1502414720000115</v>
       </c>
       <c r="Y2">
-        <v>0.2767465712038886</v>
+        <v>0.1580918613333219</v>
       </c>
       <c r="Z2">
-        <v>11.15358361774744</v>
+        <v>9.286173633440516</v>
       </c>
       <c r="AA2">
-        <v>0.7614546127999577</v>
+        <v>0.558614251633648</v>
       </c>
       <c r="AB2">
-        <v>0.09093729041685644</v>
+        <v>0.1471237458266367</v>
       </c>
       <c r="AC2">
-        <v>0.6705173223831014</v>
+        <v>0.4114905058070113</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="AG2">
-        <v>-42.9</v>
+        <v>-48.6</v>
       </c>
       <c r="AH2">
-        <v>0.03658217925267834</v>
+        <v>0.03375912408759124</v>
       </c>
       <c r="AI2">
-        <v>0.2052785923753666</v>
+        <v>0.1408629441624366</v>
       </c>
       <c r="AJ2">
-        <v>-0.1316758747697974</v>
+        <v>-0.1806020066889632</v>
       </c>
       <c r="AK2">
-        <v>-3.796460176991149</v>
+        <v>-2.544502617801047</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="AM2">
-        <v>-1.39</v>
+        <v>-0.518</v>
       </c>
       <c r="AN2">
-        <v>0.4430379746835443</v>
+        <v>0.4549180327868853</v>
+      </c>
+      <c r="AO2">
+        <v>41.46341463414634</v>
       </c>
       <c r="AP2">
-        <v>-1.357594936708861</v>
+        <v>-1.991803278688525</v>
       </c>
       <c r="AQ2">
-        <v>-18.84892086330935</v>
+        <v>-39.38223938223938</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8833 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0665</v>
+        <v>0.0774</v>
       </c>
       <c r="E3">
-        <v>0.099</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G3">
-        <v>0.07313341493268054</v>
+        <v>0.1166897506925208</v>
       </c>
       <c r="H3">
-        <v>0.07313341493268054</v>
+        <v>0.1166897506925208</v>
       </c>
       <c r="I3">
-        <v>0.08017135862913097</v>
+        <v>0.0706371191135734</v>
       </c>
       <c r="J3">
-        <v>0.06826995151480648</v>
+        <v>0.06015548208381735</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="L3">
-        <v>0.06731946144430845</v>
+        <v>0.06405817174515235</v>
       </c>
       <c r="M3">
-        <v>27.501</v>
+        <v>13.01</v>
       </c>
       <c r="N3">
-        <v>0.07458909682668836</v>
+        <v>0.04095058231035568</v>
       </c>
       <c r="O3">
-        <v>1.250045454545455</v>
+        <v>0.7032432432432433</v>
       </c>
       <c r="P3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q3">
-        <v>0.07323026851098455</v>
+        <v>0.03462385898646522</v>
       </c>
       <c r="R3">
-        <v>1.227272727272727</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="S3">
-        <v>0.5010000000000012</v>
+        <v>2.01</v>
       </c>
       <c r="T3">
-        <v>0.0182175193629323</v>
+        <v>0.1544965411222137</v>
       </c>
       <c r="U3">
-        <v>56.9</v>
+        <v>59.7</v>
       </c>
       <c r="V3">
-        <v>0.1543260103064822</v>
+        <v>0.1879131255901794</v>
       </c>
       <c r="W3">
-        <v>0.3697478991596639</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="X3">
-        <v>0.09300132795577531</v>
+        <v>0.1502414720000115</v>
       </c>
       <c r="Y3">
-        <v>0.2767465712038886</v>
+        <v>0.1580918613333219</v>
       </c>
       <c r="Z3">
-        <v>11.15358361774744</v>
+        <v>9.286173633440516</v>
       </c>
       <c r="AA3">
-        <v>0.7614546127999577</v>
+        <v>0.558614251633648</v>
       </c>
       <c r="AB3">
-        <v>0.09093729041685644</v>
+        <v>0.1471237458266367</v>
       </c>
       <c r="AC3">
-        <v>0.6705173223831014</v>
+        <v>0.4114905058070113</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="AG3">
-        <v>-42.9</v>
+        <v>-48.6</v>
       </c>
       <c r="AH3">
-        <v>0.03658217925267834</v>
+        <v>0.03375912408759124</v>
       </c>
       <c r="AI3">
-        <v>0.2052785923753666</v>
+        <v>0.1408629441624366</v>
       </c>
       <c r="AJ3">
-        <v>-0.1316758747697974</v>
+        <v>-0.1806020066889632</v>
       </c>
       <c r="AK3">
-        <v>-3.796460176991149</v>
+        <v>-2.544502617801047</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="AM3">
-        <v>-1.39</v>
+        <v>-0.518</v>
       </c>
       <c r="AN3">
-        <v>0.4430379746835443</v>
+        <v>0.4549180327868853</v>
+      </c>
+      <c r="AO3">
+        <v>41.46341463414634</v>
       </c>
       <c r="AP3">
-        <v>-1.357594936708861</v>
+        <v>-1.991803278688525</v>
       </c>
       <c r="AQ3">
-        <v>-18.84892086330935</v>
+        <v>-39.38223938223938</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ericsson Nikola Tesla d.d. (ZGSE:ERNT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ZGSE:ERNT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0337591240875912</v>
+      </c>
+      <c r="F2">
+        <v>0.25</v>
+      </c>
+      <c r="G2">
+        <v>317.7</v>
+      </c>
+      <c r="H2">
+        <v>255.019327575969</v>
+      </c>
+      <c r="I2">
+        <v>269.1</v>
+      </c>
+      <c r="J2">
+        <v>277.519327575969</v>
+      </c>
+      <c r="K2">
+        <v>11.1</v>
+      </c>
+      <c r="L2">
+        <v>82.2</v>
+      </c>
+      <c r="M2">
+        <v>0.147123745826637</v>
+      </c>
+      <c r="N2">
+        <v>0.143837441019197</v>
+      </c>
+      <c r="O2">
+        <v>0.0578893669724771</v>
+      </c>
+      <c r="P2">
+        <v>0.0451</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.150241472000011</v>
+      </c>
+      <c r="T2">
+        <v>0.176749921358929</v>
+      </c>
+      <c r="U2">
+        <v>1.21124890070553</v>
+      </c>
+      <c r="V2">
+        <v>1.49936722478325</v>
+      </c>
+      <c r="W2">
+        <v>4.512276045122761</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>317.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.07059678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>24.4</v>
+      </c>
+      <c r="AH2">
+        <v>4</v>
+      </c>
+      <c r="AI2">
+        <v>5.640000000000004</v>
+      </c>
+      <c r="AJ2">
+        <v>11.1</v>
+      </c>
+      <c r="AK2">
+        <v>11.1</v>
+      </c>
+      <c r="AL2">
+        <v>0.492</v>
+      </c>
+      <c r="AM2">
+        <v>11.1</v>
+      </c>
+      <c r="AN2">
+        <v>59.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1471376345750749</v>
+      </c>
+      <c r="C2">
+        <v>328.7655017185912</v>
+      </c>
+      <c r="D2">
+        <v>269.0655017185912</v>
+      </c>
+      <c r="E2">
+        <v>-11.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>59.7</v>
+      </c>
+      <c r="H2">
+        <v>317.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>24.4</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>20.4</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>20.4</v>
+      </c>
+      <c r="O2">
+        <v>3.671999999999998</v>
+      </c>
+      <c r="P2">
+        <v>16.728</v>
+      </c>
+      <c r="Q2">
+        <v>20.728</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1471376345750749</v>
+      </c>
+      <c r="T2">
+        <v>1.177513527316688</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1469293668328398</v>
+      </c>
+      <c r="C3">
+        <v>325.9957482060873</v>
+      </c>
+      <c r="D3">
+        <v>269.5837482060873</v>
+      </c>
+      <c r="E3">
+        <v>-7.811999999999999</v>
+      </c>
+      <c r="F3">
+        <v>3.288</v>
+      </c>
+      <c r="G3">
+        <v>59.7</v>
+      </c>
+      <c r="H3">
+        <v>317.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>24.4</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>20.4</v>
+      </c>
+      <c r="M3">
+        <v>0.1502616</v>
+      </c>
+      <c r="N3">
+        <v>20.2497384</v>
+      </c>
+      <c r="O3">
+        <v>3.644952911999999</v>
+      </c>
+      <c r="P3">
+        <v>16.604785488</v>
+      </c>
+      <c r="Q3">
+        <v>20.604785488</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1480349765988281</v>
+      </c>
+      <c r="T3">
+        <v>1.187266669664159</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>135.7632289287482</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1467210990906047</v>
+      </c>
+      <c r="C4">
+        <v>323.2279949331432</v>
+      </c>
+      <c r="D4">
+        <v>270.1039949331433</v>
+      </c>
+      <c r="E4">
+        <v>-4.523999999999999</v>
+      </c>
+      <c r="F4">
+        <v>6.576000000000001</v>
+      </c>
+      <c r="G4">
+        <v>59.7</v>
+      </c>
+      <c r="H4">
+        <v>317.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>24.4</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>20.4</v>
+      </c>
+      <c r="M4">
+        <v>0.3005232</v>
+      </c>
+      <c r="N4">
+        <v>20.0994768</v>
+      </c>
+      <c r="O4">
+        <v>3.617905823999998</v>
+      </c>
+      <c r="P4">
+        <v>16.481570976</v>
+      </c>
+      <c r="Q4">
+        <v>20.481570976</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1489506317251068</v>
+      </c>
+      <c r="T4">
+        <v>1.197218855733008</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>67.88161446437411</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1465128313483695</v>
+      </c>
+      <c r="C5">
+        <v>320.4622535024262</v>
+      </c>
+      <c r="D5">
+        <v>270.6262535024262</v>
+      </c>
+      <c r="E5">
+        <v>-1.235999999999999</v>
+      </c>
+      <c r="F5">
+        <v>9.864000000000001</v>
+      </c>
+      <c r="G5">
+        <v>59.7</v>
+      </c>
+      <c r="H5">
+        <v>317.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>24.4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>20.4</v>
+      </c>
+      <c r="M5">
+        <v>0.4507848000000001</v>
+      </c>
+      <c r="N5">
+        <v>19.9492152</v>
+      </c>
+      <c r="O5">
+        <v>3.590858735999998</v>
+      </c>
+      <c r="P5">
+        <v>16.358356464</v>
+      </c>
+      <c r="Q5">
+        <v>20.358356464</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1498851663385253</v>
+      </c>
+      <c r="T5">
+        <v>1.207376241514616</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>45.25440964291607</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1463045636061344</v>
+      </c>
+      <c r="C6">
+        <v>317.6985356065144</v>
+      </c>
+      <c r="D6">
+        <v>271.1505356065144</v>
+      </c>
+      <c r="E6">
+        <v>2.052000000000001</v>
+      </c>
+      <c r="F6">
+        <v>13.152</v>
+      </c>
+      <c r="G6">
+        <v>59.7</v>
+      </c>
+      <c r="H6">
+        <v>317.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>24.4</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>20.4</v>
+      </c>
+      <c r="M6">
+        <v>0.6010464000000001</v>
+      </c>
+      <c r="N6">
+        <v>19.7989536</v>
+      </c>
+      <c r="O6">
+        <v>3.563811647999998</v>
+      </c>
+      <c r="P6">
+        <v>16.235141952</v>
+      </c>
+      <c r="Q6">
+        <v>20.235141952</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1508391704230567</v>
+      </c>
+      <c r="T6">
+        <v>1.217745239500008</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>33.94080723218705</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1460962958638993</v>
+      </c>
+      <c r="C7">
+        <v>314.9368530287695</v>
+      </c>
+      <c r="D7">
+        <v>271.6768530287695</v>
+      </c>
+      <c r="E7">
+        <v>5.340000000000002</v>
+      </c>
+      <c r="F7">
+        <v>16.44</v>
+      </c>
+      <c r="G7">
+        <v>59.7</v>
+      </c>
+      <c r="H7">
+        <v>317.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>24.4</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>20.4</v>
+      </c>
+      <c r="M7">
+        <v>0.7513080000000001</v>
+      </c>
+      <c r="N7">
+        <v>19.648692</v>
+      </c>
+      <c r="O7">
+        <v>3.536764559999998</v>
+      </c>
+      <c r="P7">
+        <v>16.11192744</v>
+      </c>
+      <c r="Q7">
+        <v>20.11192744</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1518132588041045</v>
+      </c>
+      <c r="T7">
+        <v>1.228332532179829</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>27.15264578574964</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1458880281216641</v>
+      </c>
+      <c r="C8">
+        <v>312.17721764422</v>
+      </c>
+      <c r="D8">
+        <v>272.2052176442201</v>
+      </c>
+      <c r="E8">
+        <v>8.628000000000002</v>
+      </c>
+      <c r="F8">
+        <v>19.728</v>
+      </c>
+      <c r="G8">
+        <v>59.7</v>
+      </c>
+      <c r="H8">
+        <v>317.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>24.4</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>20.4</v>
+      </c>
+      <c r="M8">
+        <v>0.9015696000000002</v>
+      </c>
+      <c r="N8">
+        <v>19.4984304</v>
+      </c>
+      <c r="O8">
+        <v>3.509717471999998</v>
+      </c>
+      <c r="P8">
+        <v>15.988712928</v>
+      </c>
+      <c r="Q8">
+        <v>19.988712928</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1528080724698554</v>
+      </c>
+      <c r="T8">
+        <v>1.239145086406029</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>22.62720482145804</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.145679760379429</v>
+      </c>
+      <c r="C9">
+        <v>309.4196414204533</v>
+      </c>
+      <c r="D9">
+        <v>272.7356414204534</v>
+      </c>
+      <c r="E9">
+        <v>11.916</v>
+      </c>
+      <c r="F9">
+        <v>23.016</v>
+      </c>
+      <c r="G9">
+        <v>59.7</v>
+      </c>
+      <c r="H9">
+        <v>317.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24.4</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>20.4</v>
+      </c>
+      <c r="M9">
+        <v>1.0518312</v>
+      </c>
+      <c r="N9">
+        <v>19.3481688</v>
+      </c>
+      <c r="O9">
+        <v>3.482670383999999</v>
+      </c>
+      <c r="P9">
+        <v>15.865498416</v>
+      </c>
+      <c r="Q9">
+        <v>19.865498416</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1538242799778807</v>
+      </c>
+      <c r="T9">
+        <v>1.250190168680105</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.39474698982118</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1454714926371939</v>
+      </c>
+      <c r="C10">
+        <v>306.6641364185208</v>
+      </c>
+      <c r="D10">
+        <v>273.2681364185208</v>
+      </c>
+      <c r="E10">
+        <v>15.204</v>
+      </c>
+      <c r="F10">
+        <v>26.304</v>
+      </c>
+      <c r="G10">
+        <v>59.7</v>
+      </c>
+      <c r="H10">
+        <v>317.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>24.4</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>20.4</v>
+      </c>
+      <c r="M10">
+        <v>1.2020928</v>
+      </c>
+      <c r="N10">
+        <v>19.1979072</v>
+      </c>
+      <c r="O10">
+        <v>3.455623295999999</v>
+      </c>
+      <c r="P10">
+        <v>15.742283904</v>
+      </c>
+      <c r="Q10">
+        <v>19.742283904</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1548625789534716</v>
+      </c>
+      <c r="T10">
+        <v>1.2614753614384</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.97040361609353</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1452632248949587</v>
+      </c>
+      <c r="C11">
+        <v>303.9107147938503</v>
+      </c>
+      <c r="D11">
+        <v>273.8027147938503</v>
+      </c>
+      <c r="E11">
+        <v>18.492</v>
+      </c>
+      <c r="F11">
+        <v>29.592</v>
+      </c>
+      <c r="G11">
+        <v>59.7</v>
+      </c>
+      <c r="H11">
+        <v>317.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>24.4</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>20.4</v>
+      </c>
+      <c r="M11">
+        <v>1.3523544</v>
+      </c>
+      <c r="N11">
+        <v>19.0476456</v>
+      </c>
+      <c r="O11">
+        <v>3.428576207999999</v>
+      </c>
+      <c r="P11">
+        <v>15.619069392</v>
+      </c>
+      <c r="Q11">
+        <v>19.619069392</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1559236976867678</v>
+      </c>
+      <c r="T11">
+        <v>1.273008580411162</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.08480321430536</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1450549571527236</v>
+      </c>
+      <c r="C12">
+        <v>301.1593887971724</v>
+      </c>
+      <c r="D12">
+        <v>274.3393887971724</v>
+      </c>
+      <c r="E12">
+        <v>21.78</v>
+      </c>
+      <c r="F12">
+        <v>32.88</v>
+      </c>
+      <c r="G12">
+        <v>59.7</v>
+      </c>
+      <c r="H12">
+        <v>317.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>24.4</v>
+      </c>
+      <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>20.4</v>
+      </c>
+      <c r="M12">
+        <v>1.502616</v>
+      </c>
+      <c r="N12">
+        <v>18.897384</v>
+      </c>
+      <c r="O12">
+        <v>3.401529119999998</v>
+      </c>
+      <c r="P12">
+        <v>15.49585488</v>
+      </c>
+      <c r="Q12">
+        <v>19.49585488</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1570083968363595</v>
+      </c>
+      <c r="T12">
+        <v>1.284798093138875</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.03747400000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.57632289287482</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1449910094104885</v>
+      </c>
+      <c r="C13">
+        <v>298.0365947276663</v>
+      </c>
+      <c r="D13">
+        <v>274.5045947276663</v>
+      </c>
+      <c r="E13">
+        <v>25.068</v>
+      </c>
+      <c r="F13">
+        <v>36.168</v>
+      </c>
+      <c r="G13">
+        <v>59.7</v>
+      </c>
+      <c r="H13">
+        <v>317.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>24.4</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>20.4</v>
+      </c>
+      <c r="M13">
+        <v>1.7107464</v>
+      </c>
+      <c r="N13">
+        <v>18.6892536</v>
+      </c>
+      <c r="O13">
+        <v>3.364065647999998</v>
+      </c>
+      <c r="P13">
+        <v>15.325187952</v>
+      </c>
+      <c r="Q13">
+        <v>19.325187952</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1581174712477398</v>
+      </c>
+      <c r="T13">
+        <v>1.296852538736873</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.038786</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.92461956956332</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1447958616682533</v>
+      </c>
+      <c r="C14">
+        <v>295.2539819291208</v>
+      </c>
+      <c r="D14">
+        <v>275.0099819291208</v>
+      </c>
+      <c r="E14">
+        <v>28.356</v>
+      </c>
+      <c r="F14">
+        <v>39.456</v>
+      </c>
+      <c r="G14">
+        <v>59.7</v>
+      </c>
+      <c r="H14">
+        <v>317.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>24.4</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <v>20.4</v>
+      </c>
+      <c r="M14">
+        <v>1.8662688</v>
+      </c>
+      <c r="N14">
+        <v>18.5337312</v>
+      </c>
+      <c r="O14">
+        <v>3.336071615999999</v>
+      </c>
+      <c r="P14">
+        <v>15.197659584</v>
+      </c>
+      <c r="Q14">
+        <v>19.197659584</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1592517518957424</v>
+      </c>
+      <c r="T14">
+        <v>1.309180949007554</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.038786</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.93090127209971</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1450057939260182</v>
+      </c>
+      <c r="C15">
+        <v>291.4223819589113</v>
+      </c>
+      <c r="D15">
+        <v>274.4663819589113</v>
+      </c>
+      <c r="E15">
+        <v>31.644</v>
+      </c>
+      <c r="F15">
+        <v>42.744</v>
+      </c>
+      <c r="G15">
+        <v>59.7</v>
+      </c>
+      <c r="H15">
+        <v>317.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>24.4</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <v>20.4</v>
+      </c>
+      <c r="M15">
+        <v>2.1842184</v>
+      </c>
+      <c r="N15">
+        <v>18.2157816</v>
+      </c>
+      <c r="O15">
+        <v>3.278840687999999</v>
+      </c>
+      <c r="P15">
+        <v>14.936940912</v>
+      </c>
+      <c r="Q15">
+        <v>18.936940912</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1604121079609405</v>
+      </c>
+      <c r="T15">
+        <v>1.321792771008595</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.041902</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.339725368122529</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1448418061837831</v>
+      </c>
+      <c r="C16">
+        <v>288.5588289191873</v>
+      </c>
+      <c r="D16">
+        <v>274.8908289191873</v>
+      </c>
+      <c r="E16">
+        <v>34.932</v>
+      </c>
+      <c r="F16">
+        <v>46.032</v>
+      </c>
+      <c r="G16">
+        <v>59.7</v>
+      </c>
+      <c r="H16">
+        <v>317.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>24.4</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>20.4</v>
+      </c>
+      <c r="M16">
+        <v>2.3522352</v>
+      </c>
+      <c r="N16">
+        <v>18.0477648</v>
+      </c>
+      <c r="O16">
+        <v>3.248597663999999</v>
+      </c>
+      <c r="P16">
+        <v>14.799167136</v>
+      </c>
+      <c r="Q16">
+        <v>18.799167136</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1615994490509106</v>
+      </c>
+      <c r="T16">
+        <v>1.334697891195706</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.041902</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.672602127542348</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1446778184415479</v>
+      </c>
+      <c r="C17">
+        <v>285.6965906798576</v>
+      </c>
+      <c r="D17">
+        <v>275.3165906798577</v>
+      </c>
+      <c r="E17">
+        <v>38.22</v>
+      </c>
+      <c r="F17">
+        <v>49.32</v>
+      </c>
+      <c r="G17">
+        <v>59.7</v>
+      </c>
+      <c r="H17">
+        <v>317.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>24.4</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>20.4</v>
+      </c>
+      <c r="M17">
+        <v>2.520252</v>
+      </c>
+      <c r="N17">
+        <v>17.879748</v>
+      </c>
+      <c r="O17">
+        <v>3.218354639999999</v>
+      </c>
+      <c r="P17">
+        <v>14.66139336</v>
+      </c>
+      <c r="Q17">
+        <v>18.66139336</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1628147275782917</v>
+      </c>
+      <c r="T17">
+        <v>1.347906661269573</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.041902</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.094428652372857</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1447631106993128</v>
+      </c>
+      <c r="C18">
+        <v>282.1869817306277</v>
+      </c>
+      <c r="D18">
+        <v>275.0949817306277</v>
+      </c>
+      <c r="E18">
+        <v>41.508</v>
+      </c>
+      <c r="F18">
+        <v>52.608</v>
+      </c>
+      <c r="G18">
+        <v>59.7</v>
+      </c>
+      <c r="H18">
+        <v>317.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>24.4</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <v>20.4</v>
+      </c>
+      <c r="M18">
+        <v>2.788224</v>
+      </c>
+      <c r="N18">
+        <v>17.611776</v>
+      </c>
+      <c r="O18">
+        <v>3.170119679999999</v>
+      </c>
+      <c r="P18">
+        <v>14.44165632</v>
+      </c>
+      <c r="Q18">
+        <v>18.44165632</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1640589413087057</v>
+      </c>
+      <c r="T18">
+        <v>1.361429925869008</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.04346000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.316485332598814</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1446147029570777</v>
+      </c>
+      <c r="C19">
+        <v>279.2848092574074</v>
+      </c>
+      <c r="D19">
+        <v>275.4808092574074</v>
+      </c>
+      <c r="E19">
+        <v>44.79600000000001</v>
+      </c>
+      <c r="F19">
+        <v>55.89600000000001</v>
+      </c>
+      <c r="G19">
+        <v>59.7</v>
+      </c>
+      <c r="H19">
+        <v>317.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>24.4</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>20.4</v>
+      </c>
+      <c r="M19">
+        <v>2.962488000000001</v>
+      </c>
+      <c r="N19">
+        <v>17.437512</v>
+      </c>
+      <c r="O19">
+        <v>3.138752159999999</v>
+      </c>
+      <c r="P19">
+        <v>14.29875984</v>
+      </c>
+      <c r="Q19">
+        <v>18.29875984</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1653331360928646</v>
+      </c>
+      <c r="T19">
+        <v>1.375279052266021</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.04346000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>6.886103842445942</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1444662952148425</v>
+      </c>
+      <c r="C20">
+        <v>276.3837205695517</v>
+      </c>
+      <c r="D20">
+        <v>275.8677205695517</v>
+      </c>
+      <c r="E20">
+        <v>48.084</v>
+      </c>
+      <c r="F20">
+        <v>59.184</v>
+      </c>
+      <c r="G20">
+        <v>59.7</v>
+      </c>
+      <c r="H20">
+        <v>317.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>24.4</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>20.4</v>
+      </c>
+      <c r="M20">
+        <v>3.136752</v>
+      </c>
+      <c r="N20">
+        <v>17.263248</v>
+      </c>
+      <c r="O20">
+        <v>3.107384639999998</v>
+      </c>
+      <c r="P20">
+        <v>14.15586336</v>
+      </c>
+      <c r="Q20">
+        <v>18.15586336</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1666384087985884</v>
+      </c>
+      <c r="T20">
+        <v>1.389465962233691</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.04346000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.503542517865613</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1446294874726074</v>
+      </c>
+      <c r="C21">
+        <v>272.6703242339997</v>
+      </c>
+      <c r="D21">
+        <v>275.4423242339997</v>
+      </c>
+      <c r="E21">
+        <v>51.372</v>
+      </c>
+      <c r="F21">
+        <v>62.472</v>
+      </c>
+      <c r="G21">
+        <v>59.7</v>
+      </c>
+      <c r="H21">
+        <v>317.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>24.4</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <v>20.4</v>
+      </c>
+      <c r="M21">
+        <v>3.43596</v>
+      </c>
+      <c r="N21">
+        <v>16.96404</v>
+      </c>
+      <c r="O21">
+        <v>3.053527199999998</v>
+      </c>
+      <c r="P21">
+        <v>13.9105128</v>
+      </c>
+      <c r="Q21">
+        <v>17.9105128</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1679759104600091</v>
+      </c>
+      <c r="T21">
+        <v>1.404003166274638</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.0451</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.937205322529947</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1444974797303722</v>
+      </c>
+      <c r="C22">
+        <v>269.7263297810655</v>
+      </c>
+      <c r="D22">
+        <v>275.7863297810655</v>
+      </c>
+      <c r="E22">
+        <v>54.66</v>
+      </c>
+      <c r="F22">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="G22">
+        <v>59.7</v>
+      </c>
+      <c r="H22">
+        <v>317.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>24.4</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>20.4</v>
+      </c>
+      <c r="M22">
+        <v>3.6168</v>
+      </c>
+      <c r="N22">
+        <v>16.7832</v>
+      </c>
+      <c r="O22">
+        <v>3.020975999999998</v>
+      </c>
+      <c r="P22">
+        <v>13.762224</v>
+      </c>
+      <c r="Q22">
+        <v>17.762224</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1693468496629653</v>
+      </c>
+      <c r="T22">
+        <v>1.418903800416609</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.0451</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.640345056403449</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1443654719881371</v>
+      </c>
+      <c r="C23">
+        <v>266.7831956737487</v>
+      </c>
+      <c r="D23">
+        <v>276.1311956737487</v>
+      </c>
+      <c r="E23">
+        <v>57.948</v>
+      </c>
+      <c r="F23">
+        <v>69.048</v>
+      </c>
+      <c r="G23">
+        <v>59.7</v>
+      </c>
+      <c r="H23">
+        <v>317.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>24.4</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>20.4</v>
+      </c>
+      <c r="M23">
+        <v>3.79764</v>
+      </c>
+      <c r="N23">
+        <v>16.60236</v>
+      </c>
+      <c r="O23">
+        <v>2.988424799999998</v>
+      </c>
+      <c r="P23">
+        <v>13.6139352</v>
+      </c>
+      <c r="Q23">
+        <v>17.6139352</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1707524961875153</v>
+      </c>
+      <c r="T23">
+        <v>1.43418166580268</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.0451</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.371757196574714</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.144233464245902</v>
+      </c>
+      <c r="C24">
+        <v>263.8409251436309</v>
+      </c>
+      <c r="D24">
+        <v>276.4769251436309</v>
+      </c>
+      <c r="E24">
+        <v>61.236</v>
+      </c>
+      <c r="F24">
+        <v>72.336</v>
+      </c>
+      <c r="G24">
+        <v>59.7</v>
+      </c>
+      <c r="H24">
+        <v>317.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>24.4</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>20.4</v>
+      </c>
+      <c r="M24">
+        <v>3.97848</v>
+      </c>
+      <c r="N24">
+        <v>16.42152</v>
+      </c>
+      <c r="O24">
+        <v>2.955873599999999</v>
+      </c>
+      <c r="P24">
+        <v>13.4656464</v>
+      </c>
+      <c r="Q24">
+        <v>17.4656464</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1721941849306436</v>
+      </c>
+      <c r="T24">
+        <v>1.449851271326855</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.0451</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.127586414912227</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1441014565036668</v>
+      </c>
+      <c r="C25">
+        <v>260.8995214384984</v>
+      </c>
+      <c r="D25">
+        <v>276.8235214384985</v>
+      </c>
+      <c r="E25">
+        <v>64.52400000000002</v>
+      </c>
+      <c r="F25">
+        <v>75.62400000000001</v>
+      </c>
+      <c r="G25">
+        <v>59.7</v>
+      </c>
+      <c r="H25">
+        <v>317.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>24.4</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25">
+        <v>20.4</v>
+      </c>
+      <c r="M25">
+        <v>4.15932</v>
+      </c>
+      <c r="N25">
+        <v>16.24068</v>
+      </c>
+      <c r="O25">
+        <v>2.923322399999999</v>
+      </c>
+      <c r="P25">
+        <v>13.3173576</v>
+      </c>
+      <c r="Q25">
+        <v>17.3173576</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1736733201346323</v>
+      </c>
+      <c r="T25">
+        <v>1.465927879591918</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.0451</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>4.904647875133435</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1439694487614317</v>
+      </c>
+      <c r="C26">
+        <v>257.958987822444</v>
+      </c>
+      <c r="D26">
+        <v>277.170987822444</v>
+      </c>
+      <c r="E26">
+        <v>67.81200000000001</v>
+      </c>
+      <c r="F26">
+        <v>78.91200000000001</v>
+      </c>
+      <c r="G26">
+        <v>59.7</v>
+      </c>
+      <c r="H26">
+        <v>317.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>24.4</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>20.4</v>
+      </c>
+      <c r="M26">
+        <v>4.34016</v>
+      </c>
+      <c r="N26">
+        <v>16.05984</v>
+      </c>
+      <c r="O26">
+        <v>2.890771199999999</v>
+      </c>
+      <c r="P26">
+        <v>13.1690688</v>
+      </c>
+      <c r="Q26">
+        <v>17.1690688</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1751913799492522</v>
+      </c>
+      <c r="T26">
+        <v>1.482427556495535</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.0451</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.700287547002874</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1438374410191966</v>
+      </c>
+      <c r="C27">
+        <v>255.0193275759689</v>
+      </c>
+      <c r="D27">
+        <v>277.5193275759689</v>
+      </c>
+      <c r="E27">
+        <v>71.10000000000001</v>
+      </c>
+      <c r="F27">
+        <v>82.2</v>
+      </c>
+      <c r="G27">
+        <v>59.7</v>
+      </c>
+      <c r="H27">
+        <v>317.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>24.4</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <v>20.4</v>
+      </c>
+      <c r="M27">
+        <v>4.521</v>
+      </c>
+      <c r="N27">
+        <v>15.879</v>
+      </c>
+      <c r="O27">
+        <v>2.858219999999998</v>
+      </c>
+      <c r="P27">
+        <v>13.02078</v>
+      </c>
+      <c r="Q27">
+        <v>17.02078</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1767499213589288</v>
+      </c>
+      <c r="T27">
+        <v>1.499367224783249</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.0451</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.512276045122761</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1445155932769614</v>
+      </c>
+      <c r="C28">
+        <v>249.9510759334703</v>
+      </c>
+      <c r="D28">
+        <v>275.7390759334704</v>
+      </c>
+      <c r="E28">
+        <v>74.38800000000001</v>
+      </c>
+      <c r="F28">
+        <v>85.488</v>
+      </c>
+      <c r="G28">
+        <v>59.7</v>
+      </c>
+      <c r="H28">
+        <v>317.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>24.4</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28">
+        <v>20.4</v>
+      </c>
+      <c r="M28">
+        <v>5.0266944</v>
+      </c>
+      <c r="N28">
+        <v>15.3733056</v>
+      </c>
+      <c r="O28">
+        <v>2.767195007999999</v>
+      </c>
+      <c r="P28">
+        <v>12.606110592</v>
+      </c>
+      <c r="Q28">
+        <v>16.606110592</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1783505855094073</v>
+      </c>
+      <c r="T28">
+        <v>1.516764721943604</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.04821600000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.058333046862765</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1453446255347263</v>
+      </c>
+      <c r="C29">
+        <v>244.5175281169771</v>
+      </c>
+      <c r="D29">
+        <v>273.5935281169771</v>
+      </c>
+      <c r="E29">
+        <v>77.67600000000002</v>
+      </c>
+      <c r="F29">
+        <v>88.77600000000001</v>
+      </c>
+      <c r="G29">
+        <v>59.7</v>
+      </c>
+      <c r="H29">
+        <v>317.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>24.4</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29">
+        <v>20.4</v>
+      </c>
+      <c r="M29">
+        <v>5.592888</v>
+      </c>
+      <c r="N29">
+        <v>14.807112</v>
+      </c>
+      <c r="O29">
+        <v>2.665280159999999</v>
+      </c>
+      <c r="P29">
+        <v>12.14183184</v>
+      </c>
+      <c r="Q29">
+        <v>16.14183184</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1799951034722278</v>
+      </c>
+      <c r="T29">
+        <v>1.534638862861776</v>
+      </c>
+      <c r="U29">
+        <v>0.063</v>
+      </c>
+      <c r="V29">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.05166</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>3.647489454464312</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1452782177924912</v>
+      </c>
+      <c r="C30">
+        <v>241.400161405823</v>
+      </c>
+      <c r="D30">
+        <v>273.764161405823</v>
+      </c>
+      <c r="E30">
+        <v>80.96400000000001</v>
+      </c>
+      <c r="F30">
+        <v>92.06400000000001</v>
+      </c>
+      <c r="G30">
+        <v>59.7</v>
+      </c>
+      <c r="H30">
+        <v>317.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>24.4</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>20.4</v>
+      </c>
+      <c r="M30">
+        <v>5.800032000000001</v>
+      </c>
+      <c r="N30">
+        <v>14.599968</v>
+      </c>
+      <c r="O30">
+        <v>2.627994239999999</v>
+      </c>
+      <c r="P30">
+        <v>11.97197376</v>
+      </c>
+      <c r="Q30">
+        <v>15.97197376</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1816853024895711</v>
+      </c>
+      <c r="T30">
+        <v>1.553009507694343</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.05166</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.517221973947729</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.146900190050256</v>
+      </c>
+      <c r="C31">
+        <v>234.0045102096127</v>
+      </c>
+      <c r="D31">
+        <v>269.6565102096127</v>
+      </c>
+      <c r="E31">
+        <v>84.252</v>
+      </c>
+      <c r="F31">
+        <v>95.35199999999999</v>
+      </c>
+      <c r="G31">
+        <v>59.7</v>
+      </c>
+      <c r="H31">
+        <v>317.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>24.4</v>
+      </c>
+      <c r="K31">
+        <v>4</v>
+      </c>
+      <c r="L31">
+        <v>20.4</v>
+      </c>
+      <c r="M31">
+        <v>6.684175199999999</v>
+      </c>
+      <c r="N31">
+        <v>13.7158248</v>
+      </c>
+      <c r="O31">
+        <v>2.468848463999999</v>
+      </c>
+      <c r="P31">
+        <v>11.246976336</v>
+      </c>
+      <c r="Q31">
+        <v>15.246976336</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1834231127468395</v>
+      </c>
+      <c r="T31">
+        <v>1.571897635479939</v>
+      </c>
+      <c r="U31">
+        <v>0.0701</v>
+      </c>
+      <c r="V31">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.057482</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.051984633795955</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1521318023080209</v>
+      </c>
+      <c r="C32">
+        <v>218.2686511315005</v>
+      </c>
+      <c r="D32">
+        <v>257.2086511315005</v>
+      </c>
+      <c r="E32">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="F32">
+        <v>98.64</v>
+      </c>
+      <c r="G32">
+        <v>59.7</v>
+      </c>
+      <c r="H32">
+        <v>317.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>24.4</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32">
+        <v>20.4</v>
+      </c>
+      <c r="M32">
+        <v>9.015696</v>
+      </c>
+      <c r="N32">
+        <v>11.384304</v>
+      </c>
+      <c r="O32">
+        <v>2.049174719999999</v>
+      </c>
+      <c r="P32">
+        <v>9.33512928</v>
+      </c>
+      <c r="Q32">
+        <v>13.33512928</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1852105747257441</v>
+      </c>
+      <c r="T32">
+        <v>1.591325424059409</v>
+      </c>
+      <c r="U32">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.262720482145804</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1522982745657858</v>
+      </c>
+      <c r="C33">
+        <v>214.6033933711132</v>
+      </c>
+      <c r="D33">
+        <v>256.8313933711132</v>
+      </c>
+      <c r="E33">
+        <v>90.828</v>
+      </c>
+      <c r="F33">
+        <v>101.928</v>
+      </c>
+      <c r="G33">
+        <v>59.7</v>
+      </c>
+      <c r="H33">
+        <v>317.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>24.4</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33">
+        <v>20.4</v>
+      </c>
+      <c r="M33">
+        <v>9.316219200000001</v>
+      </c>
+      <c r="N33">
+        <v>11.0837808</v>
+      </c>
+      <c r="O33">
+        <v>1.995080543999999</v>
+      </c>
+      <c r="P33">
+        <v>9.088700255999999</v>
+      </c>
+      <c r="Q33">
+        <v>13.088700256</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.187049847196791</v>
+      </c>
+      <c r="T33">
+        <v>1.611316336945531</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.189729498850778</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1524647468235506</v>
+      </c>
+      <c r="C34">
+        <v>210.9392406666536</v>
+      </c>
+      <c r="D34">
+        <v>256.4552406666537</v>
+      </c>
+      <c r="E34">
+        <v>94.11600000000001</v>
+      </c>
+      <c r="F34">
+        <v>105.216</v>
+      </c>
+      <c r="G34">
+        <v>59.7</v>
+      </c>
+      <c r="H34">
+        <v>317.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>24.4</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>20.4</v>
+      </c>
+      <c r="M34">
+        <v>9.616742400000001</v>
+      </c>
+      <c r="N34">
+        <v>10.7832576</v>
+      </c>
+      <c r="O34">
+        <v>1.940986367999999</v>
+      </c>
+      <c r="P34">
+        <v>8.842271231999998</v>
+      </c>
+      <c r="Q34">
+        <v>12.842271232</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1889432159169862</v>
+      </c>
+      <c r="T34">
+        <v>1.631895217857716</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.121300452011691</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1526312190813155</v>
+      </c>
+      <c r="C35">
+        <v>207.2761881698609</v>
+      </c>
+      <c r="D35">
+        <v>256.0801881698609</v>
+      </c>
+      <c r="E35">
+        <v>97.40400000000001</v>
+      </c>
+      <c r="F35">
+        <v>108.504</v>
+      </c>
+      <c r="G35">
+        <v>59.7</v>
+      </c>
+      <c r="H35">
+        <v>317.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>24.4</v>
+      </c>
+      <c r="K35">
+        <v>4</v>
+      </c>
+      <c r="L35">
+        <v>20.4</v>
+      </c>
+      <c r="M35">
+        <v>9.917265600000002</v>
+      </c>
+      <c r="N35">
+        <v>10.4827344</v>
+      </c>
+      <c r="O35">
+        <v>1.886892191999999</v>
+      </c>
+      <c r="P35">
+        <v>8.595842207999997</v>
+      </c>
+      <c r="Q35">
+        <v>12.595842208</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.190893103106441</v>
+      </c>
+      <c r="T35">
+        <v>1.653088393722502</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.07494800000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.057018620132549</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1586803713390804</v>
+      </c>
+      <c r="C36">
+        <v>191.0664059703793</v>
+      </c>
+      <c r="D36">
+        <v>243.1584059703794</v>
+      </c>
+      <c r="E36">
+        <v>100.692</v>
+      </c>
+      <c r="F36">
+        <v>111.792</v>
+      </c>
+      <c r="G36">
+        <v>59.7</v>
+      </c>
+      <c r="H36">
+        <v>317.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>24.4</v>
+      </c>
+      <c r="K36">
+        <v>4</v>
+      </c>
+      <c r="L36">
+        <v>20.4</v>
+      </c>
+      <c r="M36">
+        <v>12.5766</v>
+      </c>
+      <c r="N36">
+        <v>7.823399999999996</v>
+      </c>
+      <c r="O36">
+        <v>1.408211999999999</v>
+      </c>
+      <c r="P36">
+        <v>6.415187999999997</v>
+      </c>
+      <c r="Q36">
+        <v>10.415188</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1929020777864854</v>
+      </c>
+      <c r="T36">
+        <v>1.674923787037737</v>
+      </c>
+      <c r="U36">
+        <v>0.1125</v>
+      </c>
+      <c r="V36">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.09225000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.6220600162206</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1590198635968452</v>
+      </c>
+      <c r="C37">
+        <v>187.091744101304</v>
+      </c>
+      <c r="D37">
+        <v>242.471744101304</v>
+      </c>
+      <c r="E37">
+        <v>103.98</v>
+      </c>
+      <c r="F37">
+        <v>115.08</v>
+      </c>
+      <c r="G37">
+        <v>59.7</v>
+      </c>
+      <c r="H37">
+        <v>317.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>24.4</v>
+      </c>
+      <c r="K37">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <v>20.4</v>
+      </c>
+      <c r="M37">
+        <v>12.9465</v>
+      </c>
+      <c r="N37">
+        <v>7.453499999999996</v>
+      </c>
+      <c r="O37">
+        <v>1.341629999999999</v>
+      </c>
+      <c r="P37">
+        <v>6.111869999999998</v>
+      </c>
+      <c r="Q37">
+        <v>10.11187</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1949728670720696</v>
+      </c>
+      <c r="T37">
+        <v>1.697431038608825</v>
+      </c>
+      <c r="U37">
+        <v>0.1125</v>
+      </c>
+      <c r="V37">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.09225000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.575715444328583</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1593593558546101</v>
+      </c>
+      <c r="C38">
+        <v>183.1209494789737</v>
+      </c>
+      <c r="D38">
+        <v>241.7889494789737</v>
+      </c>
+      <c r="E38">
+        <v>107.268</v>
+      </c>
+      <c r="F38">
+        <v>118.368</v>
+      </c>
+      <c r="G38">
+        <v>59.7</v>
+      </c>
+      <c r="H38">
+        <v>317.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>24.4</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>20.4</v>
+      </c>
+      <c r="M38">
+        <v>13.3164</v>
+      </c>
+      <c r="N38">
+        <v>7.083599999999999</v>
+      </c>
+      <c r="O38">
+        <v>1.275047999999999</v>
+      </c>
+      <c r="P38">
+        <v>5.808552</v>
+      </c>
+      <c r="Q38">
+        <v>9.808551999999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1971083685228283</v>
+      </c>
+      <c r="T38">
+        <v>1.72064164179151</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.09225000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.531945570875011</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1882016208935895</v>
+      </c>
+      <c r="C39">
+        <v>133.1551361951675</v>
+      </c>
+      <c r="D39">
+        <v>195.1111361951675</v>
+      </c>
+      <c r="E39">
+        <v>110.556</v>
+      </c>
+      <c r="F39">
+        <v>121.656</v>
+      </c>
+      <c r="G39">
+        <v>59.7</v>
+      </c>
+      <c r="H39">
+        <v>317.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>24.4</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <v>20.4</v>
+      </c>
+      <c r="M39">
+        <v>23.9175696</v>
+      </c>
+      <c r="N39">
+        <v>-3.517569600000002</v>
+      </c>
+      <c r="O39">
+        <v>-0.6331625280000001</v>
+      </c>
+      <c r="P39">
+        <v>-2.884407072000001</v>
+      </c>
+      <c r="Q39">
+        <v>1.115592927999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2009960382623307</v>
+      </c>
+      <c r="T39">
+        <v>1.762896429114115</v>
+      </c>
+      <c r="U39">
+        <v>0.1966</v>
+      </c>
+      <c r="V39">
+        <v>0.1535273048813454</v>
+      </c>
+      <c r="W39">
+        <v>0.1664165318603275</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8529294715630303</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1897796208935895</v>
+      </c>
+      <c r="C40">
+        <v>127.8278849962725</v>
+      </c>
+      <c r="D40">
+        <v>193.0718849962725</v>
+      </c>
+      <c r="E40">
+        <v>113.844</v>
+      </c>
+      <c r="F40">
+        <v>124.944</v>
+      </c>
+      <c r="G40">
+        <v>59.7</v>
+      </c>
+      <c r="H40">
+        <v>317.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>24.4</v>
+      </c>
+      <c r="K40">
+        <v>4</v>
+      </c>
+      <c r="L40">
+        <v>20.4</v>
+      </c>
+      <c r="M40">
+        <v>24.5639904</v>
+      </c>
+      <c r="N40">
+        <v>-4.163990400000003</v>
+      </c>
+      <c r="O40">
+        <v>-0.7495182720000003</v>
+      </c>
+      <c r="P40">
+        <v>-3.414472128000003</v>
+      </c>
+      <c r="Q40">
+        <v>0.5855278719999975</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2036121033955941</v>
+      </c>
+      <c r="T40">
+        <v>1.791330242486923</v>
+      </c>
+      <c r="U40">
+        <v>0.1966</v>
+      </c>
+      <c r="V40">
+        <v>0.1494871126476258</v>
+      </c>
+      <c r="W40">
+        <v>0.1672108336534767</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8304839591534768</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1913576208935895</v>
+      </c>
+      <c r="C41">
+        <v>122.5428203282503</v>
+      </c>
+      <c r="D41">
+        <v>191.0748203282502</v>
+      </c>
+      <c r="E41">
+        <v>117.132</v>
+      </c>
+      <c r="F41">
+        <v>128.232</v>
+      </c>
+      <c r="G41">
+        <v>59.7</v>
+      </c>
+      <c r="H41">
+        <v>317.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>24.4</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>20.4</v>
+      </c>
+      <c r="M41">
+        <v>25.2104112</v>
+      </c>
+      <c r="N41">
+        <v>-4.810411200000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.8658740159999998</v>
+      </c>
+      <c r="P41">
+        <v>-3.944537184000001</v>
+      </c>
+      <c r="Q41">
+        <v>0.05546281599999903</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2063139411561776</v>
+      </c>
+      <c r="T41">
+        <v>1.820696312035889</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.1456541097592251</v>
+      </c>
+      <c r="W41">
+        <v>0.1679644020213363</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8091894986623621</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2003107146451362</v>
+      </c>
+      <c r="C42">
+        <v>108.6628866369317</v>
+      </c>
+      <c r="D42">
+        <v>180.4828866369317</v>
+      </c>
+      <c r="E42">
+        <v>120.42</v>
+      </c>
+      <c r="F42">
+        <v>131.52</v>
+      </c>
+      <c r="G42">
+        <v>59.7</v>
+      </c>
+      <c r="H42">
+        <v>317.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>24.4</v>
+      </c>
+      <c r="K42">
+        <v>4</v>
+      </c>
+      <c r="L42">
+        <v>20.4</v>
+      </c>
+      <c r="M42">
+        <v>28.118976</v>
+      </c>
+      <c r="N42">
+        <v>-7.718976000000001</v>
+      </c>
+      <c r="O42">
+        <v>-1.38941568</v>
+      </c>
+      <c r="P42">
+        <v>-6.329560320000001</v>
+      </c>
+      <c r="Q42">
+        <v>-2.329560320000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.209930996428025</v>
+      </c>
+      <c r="T42">
+        <v>1.860009811249323</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1305879702020443</v>
+      </c>
+      <c r="W42">
+        <v>0.1858802919708029</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.7254887233446907</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2020607146451361</v>
+      </c>
+      <c r="C43">
+        <v>103.4402812892756</v>
+      </c>
+      <c r="D43">
+        <v>178.5482812892756</v>
+      </c>
+      <c r="E43">
+        <v>123.708</v>
+      </c>
+      <c r="F43">
+        <v>134.808</v>
+      </c>
+      <c r="G43">
+        <v>59.7</v>
+      </c>
+      <c r="H43">
+        <v>317.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>24.4</v>
+      </c>
+      <c r="K43">
+        <v>4</v>
+      </c>
+      <c r="L43">
+        <v>20.4</v>
+      </c>
+      <c r="M43">
+        <v>28.8219504</v>
+      </c>
+      <c r="N43">
+        <v>-8.421950400000004</v>
+      </c>
+      <c r="O43">
+        <v>-1.515951072</v>
+      </c>
+      <c r="P43">
+        <v>-6.905999328000004</v>
+      </c>
+      <c r="Q43">
+        <v>-2.905999328000004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2128315217912119</v>
+      </c>
+      <c r="T43">
+        <v>1.891535401270497</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.127402897758092</v>
+      </c>
+      <c r="W43">
+        <v>0.1865612604593199</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7077938764338445</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2038107146451362</v>
+      </c>
+      <c r="C44">
+        <v>98.25871036008965</v>
+      </c>
+      <c r="D44">
+        <v>176.6547103600896</v>
+      </c>
+      <c r="E44">
+        <v>126.996</v>
+      </c>
+      <c r="F44">
+        <v>138.096</v>
+      </c>
+      <c r="G44">
+        <v>59.7</v>
+      </c>
+      <c r="H44">
+        <v>317.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>24.4</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="L44">
+        <v>20.4</v>
+      </c>
+      <c r="M44">
+        <v>29.5249248</v>
+      </c>
+      <c r="N44">
+        <v>-9.124924800000002</v>
+      </c>
+      <c r="O44">
+        <v>-1.642486464</v>
+      </c>
+      <c r="P44">
+        <v>-7.482438336000002</v>
+      </c>
+      <c r="Q44">
+        <v>-3.482438336000002</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2158320652703707</v>
+      </c>
+      <c r="T44">
+        <v>1.924148080602747</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1243694954305184</v>
+      </c>
+      <c r="W44">
+        <v>0.1872098018769552</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.6909416412806578</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2055607146451362</v>
+      </c>
+      <c r="C45">
+        <v>93.11688199417011</v>
+      </c>
+      <c r="D45">
+        <v>174.8008819941701</v>
+      </c>
+      <c r="E45">
+        <v>130.284</v>
+      </c>
+      <c r="F45">
+        <v>141.384</v>
+      </c>
+      <c r="G45">
+        <v>59.7</v>
+      </c>
+      <c r="H45">
+        <v>317.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>24.4</v>
+      </c>
+      <c r="K45">
+        <v>4</v>
+      </c>
+      <c r="L45">
+        <v>20.4</v>
+      </c>
+      <c r="M45">
+        <v>30.2278992</v>
+      </c>
+      <c r="N45">
+        <v>-9.827899200000004</v>
+      </c>
+      <c r="O45">
+        <v>-1.769021856</v>
+      </c>
+      <c r="P45">
+        <v>-8.058877344000004</v>
+      </c>
+      <c r="Q45">
+        <v>-4.058877344000004</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2189378909768684</v>
+      </c>
+      <c r="T45">
+        <v>1.957905064472971</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.121477181583297</v>
+      </c>
+      <c r="W45">
+        <v>0.1878281785774911</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.674873231018317</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2073107146451362</v>
+      </c>
+      <c r="C46">
+        <v>88.01355800047642</v>
+      </c>
+      <c r="D46">
+        <v>172.9855580004764</v>
+      </c>
+      <c r="E46">
+        <v>133.572</v>
+      </c>
+      <c r="F46">
+        <v>144.672</v>
+      </c>
+      <c r="G46">
+        <v>59.7</v>
+      </c>
+      <c r="H46">
+        <v>317.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>24.4</v>
+      </c>
+      <c r="K46">
+        <v>4</v>
+      </c>
+      <c r="L46">
+        <v>20.4</v>
+      </c>
+      <c r="M46">
+        <v>30.9308736</v>
+      </c>
+      <c r="N46">
+        <v>-10.5308736</v>
+      </c>
+      <c r="O46">
+        <v>-1.895557247999999</v>
+      </c>
+      <c r="P46">
+        <v>-8.635316352</v>
+      </c>
+      <c r="Q46">
+        <v>-4.635316352</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2221546390300268</v>
+      </c>
+      <c r="T46">
+        <v>1.992867654909988</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.118716336547313</v>
+      </c>
+      <c r="W46">
+        <v>0.1884184472461845</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.659535203040628</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2090607146451362</v>
+      </c>
+      <c r="C47">
+        <v>82.94755109423389</v>
+      </c>
+      <c r="D47">
+        <v>171.2075510942339</v>
+      </c>
+      <c r="E47">
+        <v>136.86</v>
+      </c>
+      <c r="F47">
+        <v>147.96</v>
+      </c>
+      <c r="G47">
+        <v>59.7</v>
+      </c>
+      <c r="H47">
+        <v>317.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>24.4</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47">
+        <v>20.4</v>
+      </c>
+      <c r="M47">
+        <v>31.633848</v>
+      </c>
+      <c r="N47">
+        <v>-11.233848</v>
+      </c>
+      <c r="O47">
+        <v>-2.022092639999999</v>
+      </c>
+      <c r="P47">
+        <v>-9.211755360000002</v>
+      </c>
+      <c r="Q47">
+        <v>-5.211755360000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2254883597396636</v>
+      </c>
+      <c r="T47">
+        <v>2.029101612271988</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1160781957351505</v>
+      </c>
+      <c r="W47">
+        <v>0.1889824817518248</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6448788651952806</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2108107146451362</v>
+      </c>
+      <c r="C48">
+        <v>77.91772230738755</v>
+      </c>
+      <c r="D48">
+        <v>169.4657223073876</v>
+      </c>
+      <c r="E48">
+        <v>140.148</v>
+      </c>
+      <c r="F48">
+        <v>151.248</v>
+      </c>
+      <c r="G48">
+        <v>59.7</v>
+      </c>
+      <c r="H48">
+        <v>317.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>24.4</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48">
+        <v>20.4</v>
+      </c>
+      <c r="M48">
+        <v>32.3368224</v>
+      </c>
+      <c r="N48">
+        <v>-11.9368224</v>
+      </c>
+      <c r="O48">
+        <v>-2.148628032</v>
+      </c>
+      <c r="P48">
+        <v>-9.788194368000005</v>
+      </c>
+      <c r="Q48">
+        <v>-5.788194368000005</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2289455515866944</v>
+      </c>
+      <c r="T48">
+        <v>2.066677568054803</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1135547566974298</v>
+      </c>
+      <c r="W48">
+        <v>0.1895219930180895</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6308597594301658</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2125607146451362</v>
+      </c>
+      <c r="C49">
+        <v>72.92297855553556</v>
+      </c>
+      <c r="D49">
+        <v>167.7589785555356</v>
+      </c>
+      <c r="E49">
+        <v>143.436</v>
+      </c>
+      <c r="F49">
+        <v>154.536</v>
+      </c>
+      <c r="G49">
+        <v>59.7</v>
+      </c>
+      <c r="H49">
+        <v>317.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>24.4</v>
+      </c>
+      <c r="K49">
+        <v>4</v>
+      </c>
+      <c r="L49">
+        <v>20.4</v>
+      </c>
+      <c r="M49">
+        <v>33.0397968</v>
+      </c>
+      <c r="N49">
+        <v>-12.6397968</v>
+      </c>
+      <c r="O49">
+        <v>-2.275163423999999</v>
+      </c>
+      <c r="P49">
+        <v>-10.364633376</v>
+      </c>
+      <c r="Q49">
+        <v>-6.364633376</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2325332035034245</v>
+      </c>
+      <c r="T49">
+        <v>2.105671484433195</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.111138698044293</v>
+      </c>
+      <c r="W49">
+        <v>0.1900385463581301</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6174372113571837</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2143107146451362</v>
+      </c>
+      <c r="C50">
+        <v>67.96227035042239</v>
+      </c>
+      <c r="D50">
+        <v>166.0862703504224</v>
+      </c>
+      <c r="E50">
+        <v>146.724</v>
+      </c>
+      <c r="F50">
+        <v>157.824</v>
+      </c>
+      <c r="G50">
+        <v>59.7</v>
+      </c>
+      <c r="H50">
+        <v>317.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>24.4</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50">
+        <v>20.4</v>
+      </c>
+      <c r="M50">
+        <v>33.7427712</v>
+      </c>
+      <c r="N50">
+        <v>-13.3427712</v>
+      </c>
+      <c r="O50">
+        <v>-2.401698815999999</v>
+      </c>
+      <c r="P50">
+        <v>-10.941072384</v>
+      </c>
+      <c r="Q50">
+        <v>-6.941072384000002</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2362588420323365</v>
+      </c>
+      <c r="T50">
+        <v>2.146165166826141</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1088233085017036</v>
+      </c>
+      <c r="W50">
+        <v>0.1905335766423358</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6045739361205756</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2160607146451362</v>
+      </c>
+      <c r="C51">
+        <v>63.03458964793234</v>
+      </c>
+      <c r="D51">
+        <v>164.4465896479323</v>
+      </c>
+      <c r="E51">
+        <v>150.012</v>
+      </c>
+      <c r="F51">
+        <v>161.112</v>
+      </c>
+      <c r="G51">
+        <v>59.7</v>
+      </c>
+      <c r="H51">
+        <v>317.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>24.4</v>
+      </c>
+      <c r="K51">
+        <v>4</v>
+      </c>
+      <c r="L51">
+        <v>20.4</v>
+      </c>
+      <c r="M51">
+        <v>34.4457456</v>
+      </c>
+      <c r="N51">
+        <v>-14.0457456</v>
+      </c>
+      <c r="O51">
+        <v>-2.528234207999998</v>
+      </c>
+      <c r="P51">
+        <v>-11.517511392</v>
+      </c>
+      <c r="Q51">
+        <v>-7.517511391999998</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2401305840329706</v>
+      </c>
+      <c r="T51">
+        <v>2.188246836763908</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.10660242465473</v>
+      </c>
+      <c r="W51">
+        <v>0.1910084016088187</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5922356925262782</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2178107146451362</v>
+      </c>
+      <c r="C52">
+        <v>58.1389678223093</v>
+      </c>
+      <c r="D52">
+        <v>162.8389678223093</v>
+      </c>
+      <c r="E52">
+        <v>153.3</v>
+      </c>
+      <c r="F52">
+        <v>164.4</v>
+      </c>
+      <c r="G52">
+        <v>59.7</v>
+      </c>
+      <c r="H52">
+        <v>317.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>24.4</v>
+      </c>
+      <c r="K52">
+        <v>4</v>
+      </c>
+      <c r="L52">
+        <v>20.4</v>
+      </c>
+      <c r="M52">
+        <v>35.14872</v>
+      </c>
+      <c r="N52">
+        <v>-14.74872</v>
+      </c>
+      <c r="O52">
+        <v>-2.654769599999999</v>
+      </c>
+      <c r="P52">
+        <v>-12.0939504</v>
+      </c>
+      <c r="Q52">
+        <v>-8.093950400000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.24415719571363</v>
+      </c>
+      <c r="T52">
+        <v>2.232011773499187</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1044703761616354</v>
+      </c>
+      <c r="W52">
+        <v>0.1914642335766423</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5803909786757526</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2195607146451362</v>
+      </c>
+      <c r="C53">
+        <v>53.27447375805164</v>
+      </c>
+      <c r="D53">
+        <v>161.2624737580517</v>
+      </c>
+      <c r="E53">
+        <v>156.588</v>
+      </c>
+      <c r="F53">
+        <v>167.688</v>
+      </c>
+      <c r="G53">
+        <v>59.7</v>
+      </c>
+      <c r="H53">
+        <v>317.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>24.4</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+      <c r="L53">
+        <v>20.4</v>
+      </c>
+      <c r="M53">
+        <v>35.8516944</v>
+      </c>
+      <c r="N53">
+        <v>-15.4516944</v>
+      </c>
+      <c r="O53">
+        <v>-2.781304991999999</v>
+      </c>
+      <c r="P53">
+        <v>-12.670389408</v>
+      </c>
+      <c r="Q53">
+        <v>-8.670389408000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2483481588914592</v>
+      </c>
+      <c r="T53">
+        <v>2.277563034182843</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1024219374133681</v>
+      </c>
+      <c r="W53">
+        <v>0.1919021897810219</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5690107634076006</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2213107146451362</v>
+      </c>
+      <c r="C54">
+        <v>48.44021205157975</v>
+      </c>
+      <c r="D54">
+        <v>159.7162120515798</v>
+      </c>
+      <c r="E54">
+        <v>159.876</v>
+      </c>
+      <c r="F54">
+        <v>170.976</v>
+      </c>
+      <c r="G54">
+        <v>59.7</v>
+      </c>
+      <c r="H54">
+        <v>317.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>24.4</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54">
+        <v>20.4</v>
+      </c>
+      <c r="M54">
+        <v>36.55466879999999</v>
+      </c>
+      <c r="N54">
+        <v>-16.1546688</v>
+      </c>
+      <c r="O54">
+        <v>-2.907840383999998</v>
+      </c>
+      <c r="P54">
+        <v>-13.246828416</v>
+      </c>
+      <c r="Q54">
+        <v>-9.246828415999998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2527137455350312</v>
+      </c>
+      <c r="T54">
+        <v>2.325012264061653</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1004522847708033</v>
+      </c>
+      <c r="W54">
+        <v>0.1923233015160022</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5580682487266853</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2230607146451362</v>
+      </c>
+      <c r="C55">
+        <v>43.63532131538261</v>
+      </c>
+      <c r="D55">
+        <v>158.1993213153826</v>
+      </c>
+      <c r="E55">
+        <v>163.164</v>
+      </c>
+      <c r="F55">
+        <v>174.264</v>
+      </c>
+      <c r="G55">
+        <v>59.7</v>
+      </c>
+      <c r="H55">
+        <v>317.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>24.4</v>
+      </c>
+      <c r="K55">
+        <v>4</v>
+      </c>
+      <c r="L55">
+        <v>20.4</v>
+      </c>
+      <c r="M55">
+        <v>37.2576432</v>
+      </c>
+      <c r="N55">
+        <v>-16.85764320000001</v>
+      </c>
+      <c r="O55">
+        <v>-3.034375776</v>
+      </c>
+      <c r="P55">
+        <v>-13.823267424</v>
+      </c>
+      <c r="Q55">
+        <v>-9.823267424000004</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2572651018230107</v>
+      </c>
+      <c r="T55">
+        <v>2.374480610105518</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.09855695864305228</v>
+      </c>
+      <c r="W55">
+        <v>0.1927285222421154</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5475386591280684</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2248107146451362</v>
+      </c>
+      <c r="C56">
+        <v>38.85897257789145</v>
+      </c>
+      <c r="D56">
+        <v>156.7109725778915</v>
+      </c>
+      <c r="E56">
+        <v>166.452</v>
+      </c>
+      <c r="F56">
+        <v>177.552</v>
+      </c>
+      <c r="G56">
+        <v>59.7</v>
+      </c>
+      <c r="H56">
+        <v>317.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>24.4</v>
+      </c>
+      <c r="K56">
+        <v>4</v>
+      </c>
+      <c r="L56">
+        <v>20.4</v>
+      </c>
+      <c r="M56">
+        <v>37.96061760000001</v>
+      </c>
+      <c r="N56">
+        <v>-17.56061760000001</v>
+      </c>
+      <c r="O56">
+        <v>-3.160911168</v>
+      </c>
+      <c r="P56">
+        <v>-14.39970643200001</v>
+      </c>
+      <c r="Q56">
+        <v>-10.39970643200001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2620143431669891</v>
+      </c>
+      <c r="T56">
+        <v>2.426099753803464</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.09673182977929205</v>
+      </c>
+      <c r="W56">
+        <v>0.1931187347931873</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5373990543294005</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2265607146451362</v>
+      </c>
+      <c r="C57">
+        <v>34.11036777283607</v>
+      </c>
+      <c r="D57">
+        <v>155.2503677728361</v>
+      </c>
+      <c r="E57">
+        <v>169.74</v>
+      </c>
+      <c r="F57">
+        <v>180.84</v>
+      </c>
+      <c r="G57">
+        <v>59.7</v>
+      </c>
+      <c r="H57">
+        <v>317.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>24.4</v>
+      </c>
+      <c r="K57">
+        <v>4</v>
+      </c>
+      <c r="L57">
+        <v>20.4</v>
+      </c>
+      <c r="M57">
+        <v>38.66359200000001</v>
+      </c>
+      <c r="N57">
+        <v>-18.26359200000001</v>
+      </c>
+      <c r="O57">
+        <v>-3.287446560000001</v>
+      </c>
+      <c r="P57">
+        <v>-14.97614544000001</v>
+      </c>
+      <c r="Q57">
+        <v>-10.97614544000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2669746619040334</v>
+      </c>
+      <c r="T57">
+        <v>2.480013081665764</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.09497306923785037</v>
+      </c>
+      <c r="W57">
+        <v>0.1934947577969476</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5276281624325022</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2283107146451362</v>
+      </c>
+      <c r="C58">
+        <v>29.38873831230032</v>
+      </c>
+      <c r="D58">
+        <v>153.8167383123003</v>
+      </c>
+      <c r="E58">
+        <v>173.028</v>
+      </c>
+      <c r="F58">
+        <v>184.128</v>
+      </c>
+      <c r="G58">
+        <v>59.7</v>
+      </c>
+      <c r="H58">
+        <v>317.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>24.4</v>
+      </c>
+      <c r="K58">
+        <v>4</v>
+      </c>
+      <c r="L58">
+        <v>20.4</v>
+      </c>
+      <c r="M58">
+        <v>39.3665664</v>
+      </c>
+      <c r="N58">
+        <v>-18.9665664</v>
+      </c>
+      <c r="O58">
+        <v>-3.413981952</v>
+      </c>
+      <c r="P58">
+        <v>-15.552584448</v>
+      </c>
+      <c r="Q58">
+        <v>-11.552584448</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2721604496745795</v>
+      </c>
+      <c r="T58">
+        <v>2.536377015339985</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.09327712157288877</v>
+      </c>
+      <c r="W58">
+        <v>0.1938573514077164</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5182062309604933</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2300607146451362</v>
+      </c>
+      <c r="C59">
+        <v>24.69334373811418</v>
+      </c>
+      <c r="D59">
+        <v>152.4093437381142</v>
+      </c>
+      <c r="E59">
+        <v>176.316</v>
+      </c>
+      <c r="F59">
+        <v>187.416</v>
+      </c>
+      <c r="G59">
+        <v>59.7</v>
+      </c>
+      <c r="H59">
+        <v>317.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>24.4</v>
+      </c>
+      <c r="K59">
+        <v>4</v>
+      </c>
+      <c r="L59">
+        <v>20.4</v>
+      </c>
+      <c r="M59">
+        <v>40.06954080000001</v>
+      </c>
+      <c r="N59">
+        <v>-19.66954080000001</v>
+      </c>
+      <c r="O59">
+        <v>-3.540517344</v>
+      </c>
+      <c r="P59">
+        <v>-16.12902345600001</v>
+      </c>
+      <c r="Q59">
+        <v>-12.12902345600001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.277587436876314</v>
+      </c>
+      <c r="T59">
+        <v>2.595362527324636</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.09164068084353985</v>
+      </c>
+      <c r="W59">
+        <v>0.1942072224356512</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5091148935752214</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2318107146451362</v>
+      </c>
+      <c r="C60">
+        <v>20.02347044661289</v>
+      </c>
+      <c r="D60">
+        <v>151.0274704466129</v>
+      </c>
+      <c r="E60">
+        <v>179.604</v>
+      </c>
+      <c r="F60">
+        <v>190.704</v>
+      </c>
+      <c r="G60">
+        <v>59.7</v>
+      </c>
+      <c r="H60">
+        <v>317.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>24.4</v>
+      </c>
+      <c r="K60">
+        <v>4</v>
+      </c>
+      <c r="L60">
+        <v>20.4</v>
+      </c>
+      <c r="M60">
+        <v>40.77251519999999</v>
+      </c>
+      <c r="N60">
+        <v>-20.3725152</v>
+      </c>
+      <c r="O60">
+        <v>-3.667052735999998</v>
+      </c>
+      <c r="P60">
+        <v>-16.705462464</v>
+      </c>
+      <c r="Q60">
+        <v>-12.705462464</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2832728520400357</v>
+      </c>
+      <c r="T60">
+        <v>2.657156873213317</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.09006066910485815</v>
+      </c>
+      <c r="W60">
+        <v>0.1945450289453813</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5003370505825454</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2489031598627095</v>
+      </c>
+      <c r="C61">
+        <v>4.448988098397734</v>
+      </c>
+      <c r="D61">
+        <v>138.7409880983977</v>
+      </c>
+      <c r="E61">
+        <v>182.892</v>
+      </c>
+      <c r="F61">
+        <v>193.992</v>
+      </c>
+      <c r="G61">
+        <v>59.7</v>
+      </c>
+      <c r="H61">
+        <v>317.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>24.4</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>20.4</v>
+      </c>
+      <c r="M61">
+        <v>46.3252896</v>
+      </c>
+      <c r="N61">
+        <v>-25.9252896</v>
+      </c>
+      <c r="O61">
+        <v>-4.666552127999998</v>
+      </c>
+      <c r="P61">
+        <v>-21.258737472</v>
+      </c>
+      <c r="Q61">
+        <v>-17.258737472</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2906805928643617</v>
+      </c>
+      <c r="T61">
+        <v>2.737671045981741</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.07926555951848813</v>
+      </c>
+      <c r="W61">
+        <v>0.2198713843869851</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4403642195471563</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2509031598627095</v>
+      </c>
+      <c r="C62">
+        <v>-0.1472525538226535</v>
+      </c>
+      <c r="D62">
+        <v>137.4327474461773</v>
+      </c>
+      <c r="E62">
+        <v>186.18</v>
+      </c>
+      <c r="F62">
+        <v>197.28</v>
+      </c>
+      <c r="G62">
+        <v>59.7</v>
+      </c>
+      <c r="H62">
+        <v>317.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>24.4</v>
+      </c>
+      <c r="K62">
+        <v>4</v>
+      </c>
+      <c r="L62">
+        <v>20.4</v>
+      </c>
+      <c r="M62">
+        <v>47.110464</v>
+      </c>
+      <c r="N62">
+        <v>-26.710464</v>
+      </c>
+      <c r="O62">
+        <v>-4.807883519999999</v>
+      </c>
+      <c r="P62">
+        <v>-21.90258048</v>
+      </c>
+      <c r="Q62">
+        <v>-17.90258048</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2969776076859707</v>
+      </c>
+      <c r="T62">
+        <v>2.806112822131284</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07794446685984666</v>
+      </c>
+      <c r="W62">
+        <v>0.2201868613138686</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4330248158880371</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2529031598627094</v>
+      </c>
+      <c r="C63">
+        <v>-4.719051891808164</v>
+      </c>
+      <c r="D63">
+        <v>136.1489481081919</v>
+      </c>
+      <c r="E63">
+        <v>189.468</v>
+      </c>
+      <c r="F63">
+        <v>200.568</v>
+      </c>
+      <c r="G63">
+        <v>59.7</v>
+      </c>
+      <c r="H63">
+        <v>317.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>24.4</v>
+      </c>
+      <c r="K63">
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <v>20.4</v>
+      </c>
+      <c r="M63">
+        <v>47.8956384</v>
+      </c>
+      <c r="N63">
+        <v>-27.4956384</v>
+      </c>
+      <c r="O63">
+        <v>-4.949214911999999</v>
+      </c>
+      <c r="P63">
+        <v>-22.54642348800001</v>
+      </c>
+      <c r="Q63">
+        <v>-18.54642348800001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3035975463445853</v>
+      </c>
+      <c r="T63">
+        <v>2.878064432955163</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07666668871460326</v>
+      </c>
+      <c r="W63">
+        <v>0.2204919947349528</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4259260484144627</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2549031598627095</v>
+      </c>
+      <c r="C64">
+        <v>-9.267088516859701</v>
+      </c>
+      <c r="D64">
+        <v>134.8889114831403</v>
+      </c>
+      <c r="E64">
+        <v>192.756</v>
+      </c>
+      <c r="F64">
+        <v>203.856</v>
+      </c>
+      <c r="G64">
+        <v>59.7</v>
+      </c>
+      <c r="H64">
+        <v>317.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>24.4</v>
+      </c>
+      <c r="K64">
+        <v>4</v>
+      </c>
+      <c r="L64">
+        <v>20.4</v>
+      </c>
+      <c r="M64">
+        <v>48.6808128</v>
+      </c>
+      <c r="N64">
+        <v>-28.2808128</v>
+      </c>
+      <c r="O64">
+        <v>-5.090546303999998</v>
+      </c>
+      <c r="P64">
+        <v>-23.190266496</v>
+      </c>
+      <c r="Q64">
+        <v>-19.190266496</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3105659028273376</v>
+      </c>
+      <c r="T64">
+        <v>2.95380297066451</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07543012921920643</v>
+      </c>
+      <c r="W64">
+        <v>0.2207872851424535</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4190562734400359</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2569031598627095</v>
+      </c>
+      <c r="C65">
+        <v>-13.79201613925682</v>
+      </c>
+      <c r="D65">
+        <v>133.6519838607432</v>
+      </c>
+      <c r="E65">
+        <v>196.044</v>
+      </c>
+      <c r="F65">
+        <v>207.144</v>
+      </c>
+      <c r="G65">
+        <v>59.7</v>
+      </c>
+      <c r="H65">
+        <v>317.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>24.4</v>
+      </c>
+      <c r="K65">
+        <v>4</v>
+      </c>
+      <c r="L65">
+        <v>20.4</v>
+      </c>
+      <c r="M65">
+        <v>49.4659872</v>
+      </c>
+      <c r="N65">
+        <v>-29.0659872</v>
+      </c>
+      <c r="O65">
+        <v>-5.231877695999999</v>
+      </c>
+      <c r="P65">
+        <v>-23.834109504</v>
+      </c>
+      <c r="Q65">
+        <v>-19.834109504</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3179109272280765</v>
+      </c>
+      <c r="T65">
+        <v>3.033635483385172</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07423282558080634</v>
+      </c>
+      <c r="W65">
+        <v>0.2210732012513034</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4124045865600353</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2589031598627095</v>
+      </c>
+      <c r="C66">
+        <v>-18.29446470913757</v>
+      </c>
+      <c r="D66">
+        <v>132.4375352908625</v>
+      </c>
+      <c r="E66">
+        <v>199.332</v>
+      </c>
+      <c r="F66">
+        <v>210.432</v>
+      </c>
+      <c r="G66">
+        <v>59.7</v>
+      </c>
+      <c r="H66">
+        <v>317.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>24.4</v>
+      </c>
+      <c r="K66">
+        <v>4</v>
+      </c>
+      <c r="L66">
+        <v>20.4</v>
+      </c>
+      <c r="M66">
+        <v>50.2511616</v>
+      </c>
+      <c r="N66">
+        <v>-29.8511616</v>
+      </c>
+      <c r="O66">
+        <v>-5.373209087999999</v>
+      </c>
+      <c r="P66">
+        <v>-24.47795251200001</v>
+      </c>
+      <c r="Q66">
+        <v>-20.47795251200001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3256640085399675</v>
+      </c>
+      <c r="T66">
+        <v>3.117903135701428</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07307293768110623</v>
+      </c>
+      <c r="W66">
+        <v>0.2213501824817518</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4059607648950347</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2609031598627095</v>
+      </c>
+      <c r="C67">
+        <v>-22.7750414862777</v>
+      </c>
+      <c r="D67">
+        <v>131.2449585137223</v>
+      </c>
+      <c r="E67">
+        <v>202.62</v>
+      </c>
+      <c r="F67">
+        <v>213.72</v>
+      </c>
+      <c r="G67">
+        <v>59.7</v>
+      </c>
+      <c r="H67">
+        <v>317.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>24.4</v>
+      </c>
+      <c r="K67">
+        <v>4</v>
+      </c>
+      <c r="L67">
+        <v>20.4</v>
+      </c>
+      <c r="M67">
+        <v>51.03633600000001</v>
+      </c>
+      <c r="N67">
+        <v>-30.63633600000001</v>
+      </c>
+      <c r="O67">
+        <v>-5.514540479999999</v>
+      </c>
+      <c r="P67">
+        <v>-25.12179552000001</v>
+      </c>
+      <c r="Q67">
+        <v>-21.12179552000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3338601230696808</v>
+      </c>
+      <c r="T67">
+        <v>3.206986082435754</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07194873863985844</v>
+      </c>
+      <c r="W67">
+        <v>0.2216186412128018</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3997152146658803</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2629031598627095</v>
+      </c>
+      <c r="C68">
+        <v>-27.23433205258769</v>
+      </c>
+      <c r="D68">
+        <v>130.0736679474123</v>
+      </c>
+      <c r="E68">
+        <v>205.908</v>
+      </c>
+      <c r="F68">
+        <v>217.008</v>
+      </c>
+      <c r="G68">
+        <v>59.7</v>
+      </c>
+      <c r="H68">
+        <v>317.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>24.4</v>
+      </c>
+      <c r="K68">
+        <v>4</v>
+      </c>
+      <c r="L68">
+        <v>20.4</v>
+      </c>
+      <c r="M68">
+        <v>51.82151040000001</v>
+      </c>
+      <c r="N68">
+        <v>-31.42151040000001</v>
+      </c>
+      <c r="O68">
+        <v>-5.655871872</v>
+      </c>
+      <c r="P68">
+        <v>-25.76563852800001</v>
+      </c>
+      <c r="Q68">
+        <v>-21.76563852800001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.342538361983495</v>
+      </c>
+      <c r="T68">
+        <v>3.301309202507394</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07085860623622421</v>
+      </c>
+      <c r="W68">
+        <v>0.2218789648307897</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3936589235345791</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2649031598627095</v>
+      </c>
+      <c r="C69">
+        <v>-31.6729012708719</v>
+      </c>
+      <c r="D69">
+        <v>128.9230987291281</v>
+      </c>
+      <c r="E69">
+        <v>209.196</v>
+      </c>
+      <c r="F69">
+        <v>220.296</v>
+      </c>
+      <c r="G69">
+        <v>59.7</v>
+      </c>
+      <c r="H69">
+        <v>317.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>24.4</v>
+      </c>
+      <c r="K69">
+        <v>4</v>
+      </c>
+      <c r="L69">
+        <v>20.4</v>
+      </c>
+      <c r="M69">
+        <v>52.60668480000001</v>
+      </c>
+      <c r="N69">
+        <v>-32.20668480000001</v>
+      </c>
+      <c r="O69">
+        <v>-5.797203264</v>
+      </c>
+      <c r="P69">
+        <v>-26.40948153600001</v>
+      </c>
+      <c r="Q69">
+        <v>-22.40948153600001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3517425547708736</v>
+      </c>
+      <c r="T69">
+        <v>3.401348875310648</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06980101509837011</v>
+      </c>
+      <c r="W69">
+        <v>0.2221315175945092</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3877834172131674</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2669031598627095</v>
+      </c>
+      <c r="C70">
+        <v>-36.09129419315079</v>
+      </c>
+      <c r="D70">
+        <v>127.7927058068492</v>
+      </c>
+      <c r="E70">
+        <v>212.484</v>
+      </c>
+      <c r="F70">
+        <v>223.584</v>
+      </c>
+      <c r="G70">
+        <v>59.7</v>
+      </c>
+      <c r="H70">
+        <v>317.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>24.4</v>
+      </c>
+      <c r="K70">
+        <v>4</v>
+      </c>
+      <c r="L70">
+        <v>20.4</v>
+      </c>
+      <c r="M70">
+        <v>53.39185920000001</v>
+      </c>
+      <c r="N70">
+        <v>-32.99185920000001</v>
+      </c>
+      <c r="O70">
+        <v>-5.938534656000001</v>
+      </c>
+      <c r="P70">
+        <v>-27.05332454400001</v>
+      </c>
+      <c r="Q70">
+        <v>-23.05332454400001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3615220096074634</v>
+      </c>
+      <c r="T70">
+        <v>3.507641027664106</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06877452958221761</v>
+      </c>
+      <c r="W70">
+        <v>0.2223766423357664</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3820807199012091</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2689031598627095</v>
+      </c>
+      <c r="C71">
+        <v>-40.49003692161304</v>
+      </c>
+      <c r="D71">
+        <v>126.681963078387</v>
+      </c>
+      <c r="E71">
+        <v>215.772</v>
+      </c>
+      <c r="F71">
+        <v>226.872</v>
+      </c>
+      <c r="G71">
+        <v>59.7</v>
+      </c>
+      <c r="H71">
+        <v>317.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>24.4</v>
+      </c>
+      <c r="K71">
+        <v>4</v>
+      </c>
+      <c r="L71">
+        <v>20.4</v>
+      </c>
+      <c r="M71">
+        <v>54.17703360000001</v>
+      </c>
+      <c r="N71">
+        <v>-33.77703360000001</v>
+      </c>
+      <c r="O71">
+        <v>-6.079866048</v>
+      </c>
+      <c r="P71">
+        <v>-27.69716755200001</v>
+      </c>
+      <c r="Q71">
+        <v>-23.69716755200001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3719323970141558</v>
+      </c>
+      <c r="T71">
+        <v>3.620790738233916</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06777779726943185</v>
+      </c>
+      <c r="W71">
+        <v>0.2226146620120597</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3765433181635104</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2709031598627095</v>
+      </c>
+      <c r="C72">
+        <v>-44.86963742505577</v>
+      </c>
+      <c r="D72">
+        <v>125.5903625749443</v>
+      </c>
+      <c r="E72">
+        <v>219.06</v>
+      </c>
+      <c r="F72">
+        <v>230.16</v>
+      </c>
+      <c r="G72">
+        <v>59.7</v>
+      </c>
+      <c r="H72">
+        <v>317.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>24.4</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>20.4</v>
+      </c>
+      <c r="M72">
+        <v>54.96220800000001</v>
+      </c>
+      <c r="N72">
+        <v>-34.56220800000001</v>
+      </c>
+      <c r="O72">
+        <v>-6.22119744</v>
+      </c>
+      <c r="P72">
+        <v>-28.34101056000001</v>
+      </c>
+      <c r="Q72">
+        <v>-24.34101056000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.383036810247961</v>
+      </c>
+      <c r="T72">
+        <v>3.741483762841713</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06680954302272568</v>
+      </c>
+      <c r="W72">
+        <v>0.2228458811261731</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3711641279040317</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2729031598627095</v>
+      </c>
+      <c r="C73">
+        <v>-49.23058631347399</v>
+      </c>
+      <c r="D73">
+        <v>124.517413686526</v>
+      </c>
+      <c r="E73">
+        <v>222.348</v>
+      </c>
+      <c r="F73">
+        <v>233.448</v>
+      </c>
+      <c r="G73">
+        <v>59.7</v>
+      </c>
+      <c r="H73">
+        <v>317.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>24.4</v>
+      </c>
+      <c r="K73">
+        <v>4</v>
+      </c>
+      <c r="L73">
+        <v>20.4</v>
+      </c>
+      <c r="M73">
+        <v>55.74738240000001</v>
+      </c>
+      <c r="N73">
+        <v>-35.34738240000001</v>
+      </c>
+      <c r="O73">
+        <v>-6.362528831999999</v>
+      </c>
+      <c r="P73">
+        <v>-28.98485356800001</v>
+      </c>
+      <c r="Q73">
+        <v>-24.98485356800001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3949070450840975</v>
+      </c>
+      <c r="T73">
+        <v>3.870500444319013</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06586856354353236</v>
+      </c>
+      <c r="W73">
+        <v>0.2230705870258045</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3659364641307356</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2749031598627094</v>
+      </c>
+      <c r="C74">
+        <v>-53.57335757328198</v>
+      </c>
+      <c r="D74">
+        <v>123.462642426718</v>
+      </c>
+      <c r="E74">
+        <v>225.636</v>
+      </c>
+      <c r="F74">
+        <v>236.736</v>
+      </c>
+      <c r="G74">
+        <v>59.7</v>
+      </c>
+      <c r="H74">
+        <v>317.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>24.4</v>
+      </c>
+      <c r="K74">
+        <v>4</v>
+      </c>
+      <c r="L74">
+        <v>20.4</v>
+      </c>
+      <c r="M74">
+        <v>56.5325568</v>
+      </c>
+      <c r="N74">
+        <v>-36.1325568</v>
+      </c>
+      <c r="O74">
+        <v>-6.503860223999999</v>
+      </c>
+      <c r="P74">
+        <v>-29.628696576</v>
+      </c>
+      <c r="Q74">
+        <v>-25.628696576</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4076251538371009</v>
+      </c>
+      <c r="T74">
+        <v>4.008732603044691</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06495372238320553</v>
+      </c>
+      <c r="W74">
+        <v>0.2232890510948905</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3608540132400309</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2769031598627095</v>
+      </c>
+      <c r="C75">
+        <v>-57.89840926548052</v>
+      </c>
+      <c r="D75">
+        <v>122.4255907345195</v>
+      </c>
+      <c r="E75">
+        <v>228.924</v>
+      </c>
+      <c r="F75">
+        <v>240.024</v>
+      </c>
+      <c r="G75">
+        <v>59.7</v>
+      </c>
+      <c r="H75">
+        <v>317.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>24.4</v>
+      </c>
+      <c r="K75">
+        <v>4</v>
+      </c>
+      <c r="L75">
+        <v>20.4</v>
+      </c>
+      <c r="M75">
+        <v>57.3177312</v>
+      </c>
+      <c r="N75">
+        <v>-36.91773120000001</v>
+      </c>
+      <c r="O75">
+        <v>-6.645191615999999</v>
+      </c>
+      <c r="P75">
+        <v>-30.27253958400001</v>
+      </c>
+      <c r="Q75">
+        <v>-26.27253958400001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4212853447199566</v>
+      </c>
+      <c r="T75">
+        <v>4.157204180935236</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06406394536425751</v>
+      </c>
+      <c r="W75">
+        <v>0.2235015298470153</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3559108075792086</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2789031598627095</v>
+      </c>
+      <c r="C76">
+        <v>-62.20618418893031</v>
+      </c>
+      <c r="D76">
+        <v>121.4058158110697</v>
+      </c>
+      <c r="E76">
+        <v>232.212</v>
+      </c>
+      <c r="F76">
+        <v>243.312</v>
+      </c>
+      <c r="G76">
+        <v>59.7</v>
+      </c>
+      <c r="H76">
+        <v>317.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>24.4</v>
+      </c>
+      <c r="K76">
+        <v>4</v>
+      </c>
+      <c r="L76">
+        <v>20.4</v>
+      </c>
+      <c r="M76">
+        <v>58.10290560000001</v>
+      </c>
+      <c r="N76">
+        <v>-37.70290560000001</v>
+      </c>
+      <c r="O76">
+        <v>-6.786523007999999</v>
+      </c>
+      <c r="P76">
+        <v>-30.91638259200001</v>
+      </c>
+      <c r="Q76">
+        <v>-26.91638259200001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.435996319516878</v>
+      </c>
+      <c r="T76">
+        <v>4.317096649432745</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06319821637284861</v>
+      </c>
+      <c r="W76">
+        <v>0.2237082659301638</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3511012020713814</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2809031598627095</v>
+      </c>
+      <c r="C77">
+        <v>-66.49711051075045</v>
+      </c>
+      <c r="D77">
+        <v>120.4028894892496</v>
+      </c>
+      <c r="E77">
+        <v>235.5</v>
+      </c>
+      <c r="F77">
+        <v>246.6</v>
+      </c>
+      <c r="G77">
+        <v>59.7</v>
+      </c>
+      <c r="H77">
+        <v>317.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>24.4</v>
+      </c>
+      <c r="K77">
+        <v>4</v>
+      </c>
+      <c r="L77">
+        <v>20.4</v>
+      </c>
+      <c r="M77">
+        <v>58.88808000000001</v>
+      </c>
+      <c r="N77">
+        <v>-38.48808000000001</v>
+      </c>
+      <c r="O77">
+        <v>-6.927854399999999</v>
+      </c>
+      <c r="P77">
+        <v>-31.56022560000001</v>
+      </c>
+      <c r="Q77">
+        <v>-27.56022560000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4518841722975531</v>
+      </c>
+      <c r="T77">
+        <v>4.489780515410055</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06235557348787731</v>
+      </c>
+      <c r="W77">
+        <v>0.2239094890510949</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3464198527104296</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2829031598627095</v>
+      </c>
+      <c r="C78">
+        <v>-70.77160236572658</v>
+      </c>
+      <c r="D78">
+        <v>119.4163976342734</v>
+      </c>
+      <c r="E78">
+        <v>238.788</v>
+      </c>
+      <c r="F78">
+        <v>249.888</v>
+      </c>
+      <c r="G78">
+        <v>59.7</v>
+      </c>
+      <c r="H78">
+        <v>317.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>24.4</v>
+      </c>
+      <c r="K78">
+        <v>4</v>
+      </c>
+      <c r="L78">
+        <v>20.4</v>
+      </c>
+      <c r="M78">
+        <v>59.6732544</v>
+      </c>
+      <c r="N78">
+        <v>-39.27325440000001</v>
+      </c>
+      <c r="O78">
+        <v>-7.069185791999999</v>
+      </c>
+      <c r="P78">
+        <v>-32.20406860800001</v>
+      </c>
+      <c r="Q78">
+        <v>-28.20406860800001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4690960128099512</v>
+      </c>
+      <c r="T78">
+        <v>4.676854703552141</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0615351054156684</v>
+      </c>
+      <c r="W78">
+        <v>0.2241054168267384</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3418616967537135</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2849031598627095</v>
+      </c>
+      <c r="C79">
+        <v>-75.03006042649176</v>
+      </c>
+      <c r="D79">
+        <v>118.4459395735083</v>
+      </c>
+      <c r="E79">
+        <v>242.076</v>
+      </c>
+      <c r="F79">
+        <v>253.176</v>
+      </c>
+      <c r="G79">
+        <v>59.7</v>
+      </c>
+      <c r="H79">
+        <v>317.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>24.4</v>
+      </c>
+      <c r="K79">
+        <v>4</v>
+      </c>
+      <c r="L79">
+        <v>20.4</v>
+      </c>
+      <c r="M79">
+        <v>60.45842880000001</v>
+      </c>
+      <c r="N79">
+        <v>-40.05842880000001</v>
+      </c>
+      <c r="O79">
+        <v>-7.210517183999999</v>
+      </c>
+      <c r="P79">
+        <v>-32.84791161600001</v>
+      </c>
+      <c r="Q79">
+        <v>-28.84791161600001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4878045351060361</v>
+      </c>
+      <c r="T79">
+        <v>4.880196212402234</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.0607359482024779</v>
+      </c>
+      <c r="W79">
+        <v>0.2242962555692483</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3374219344582107</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2869031598627094</v>
+      </c>
+      <c r="C80">
+        <v>-79.27287244612944</v>
+      </c>
+      <c r="D80">
+        <v>117.4911275538706</v>
+      </c>
+      <c r="E80">
+        <v>245.364</v>
+      </c>
+      <c r="F80">
+        <v>256.464</v>
+      </c>
+      <c r="G80">
+        <v>59.7</v>
+      </c>
+      <c r="H80">
+        <v>317.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>24.4</v>
+      </c>
+      <c r="K80">
+        <v>4</v>
+      </c>
+      <c r="L80">
+        <v>20.4</v>
+      </c>
+      <c r="M80">
+        <v>61.2436032</v>
+      </c>
+      <c r="N80">
+        <v>-40.8436032</v>
+      </c>
+      <c r="O80">
+        <v>-7.351848575999998</v>
+      </c>
+      <c r="P80">
+        <v>-33.49175462400001</v>
+      </c>
+      <c r="Q80">
+        <v>-29.49175462400001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5082138321563103</v>
+      </c>
+      <c r="T80">
+        <v>5.102023312965971</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05995728219988204</v>
+      </c>
+      <c r="W80">
+        <v>0.2244822010106682</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3330960122215669</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2889031598627094</v>
+      </c>
+      <c r="C81">
+        <v>-83.50041377474253</v>
+      </c>
+      <c r="D81">
+        <v>116.5515862252575</v>
+      </c>
+      <c r="E81">
+        <v>248.652</v>
+      </c>
+      <c r="F81">
+        <v>259.752</v>
+      </c>
+      <c r="G81">
+        <v>59.7</v>
+      </c>
+      <c r="H81">
+        <v>317.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>24.4</v>
+      </c>
+      <c r="K81">
+        <v>4</v>
+      </c>
+      <c r="L81">
+        <v>20.4</v>
+      </c>
+      <c r="M81">
+        <v>62.02877760000001</v>
+      </c>
+      <c r="N81">
+        <v>-41.62877760000001</v>
+      </c>
+      <c r="O81">
+        <v>-7.493179967999999</v>
+      </c>
+      <c r="P81">
+        <v>-34.13559763200001</v>
+      </c>
+      <c r="Q81">
+        <v>-30.13559763200001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5305668717828014</v>
+      </c>
+      <c r="T81">
+        <v>5.34497680405959</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05919832926064302</v>
+      </c>
+      <c r="W81">
+        <v>0.2246634389725584</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3288796070035724</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2909031598627094</v>
+      </c>
+      <c r="C82">
+        <v>-87.71304785143343</v>
+      </c>
+      <c r="D82">
+        <v>115.6269521485666</v>
+      </c>
+      <c r="E82">
+        <v>251.94</v>
+      </c>
+      <c r="F82">
+        <v>263.04</v>
+      </c>
+      <c r="G82">
+        <v>59.7</v>
+      </c>
+      <c r="H82">
+        <v>317.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>24.4</v>
+      </c>
+      <c r="K82">
+        <v>4</v>
+      </c>
+      <c r="L82">
+        <v>20.4</v>
+      </c>
+      <c r="M82">
+        <v>62.81395200000001</v>
+      </c>
+      <c r="N82">
+        <v>-42.41395200000001</v>
+      </c>
+      <c r="O82">
+        <v>-7.634511359999999</v>
+      </c>
+      <c r="P82">
+        <v>-34.77944064000001</v>
+      </c>
+      <c r="Q82">
+        <v>-30.77944064000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5551552153719415</v>
+      </c>
+      <c r="T82">
+        <v>5.612225644262569</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05845835014488497</v>
+      </c>
+      <c r="W82">
+        <v>0.2248401459854015</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3247686119160278</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2929031598627095</v>
+      </c>
+      <c r="C83">
+        <v>-91.91112667305097</v>
+      </c>
+      <c r="D83">
+        <v>114.7168733269491</v>
+      </c>
+      <c r="E83">
+        <v>255.228</v>
+      </c>
+      <c r="F83">
+        <v>266.328</v>
+      </c>
+      <c r="G83">
+        <v>59.7</v>
+      </c>
+      <c r="H83">
+        <v>317.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>24.4</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+      <c r="L83">
+        <v>20.4</v>
+      </c>
+      <c r="M83">
+        <v>63.59912640000001</v>
+      </c>
+      <c r="N83">
+        <v>-43.19912640000001</v>
+      </c>
+      <c r="O83">
+        <v>-7.775842751999999</v>
+      </c>
+      <c r="P83">
+        <v>-35.42328364800001</v>
+      </c>
+      <c r="Q83">
+        <v>-31.42328364800001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5823318056546753</v>
+      </c>
+      <c r="T83">
+        <v>5.907605941329021</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05773664211840491</v>
+      </c>
+      <c r="W83">
+        <v>0.2250124898621249</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3207591228800274</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2949031598627094</v>
+      </c>
+      <c r="C84">
+        <v>-96.09499124097309</v>
+      </c>
+      <c r="D84">
+        <v>113.821008759027</v>
+      </c>
+      <c r="E84">
+        <v>258.516</v>
+      </c>
+      <c r="F84">
+        <v>269.616</v>
+      </c>
+      <c r="G84">
+        <v>59.7</v>
+      </c>
+      <c r="H84">
+        <v>317.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>24.4</v>
+      </c>
+      <c r="K84">
+        <v>4</v>
+      </c>
+      <c r="L84">
+        <v>20.4</v>
+      </c>
+      <c r="M84">
+        <v>64.38430080000002</v>
+      </c>
+      <c r="N84">
+        <v>-43.98430080000002</v>
+      </c>
+      <c r="O84">
+        <v>-7.917174144000001</v>
+      </c>
+      <c r="P84">
+        <v>-36.06712665600002</v>
+      </c>
+      <c r="Q84">
+        <v>-32.06712665600002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.612528017079935</v>
+      </c>
+      <c r="T84">
+        <v>6.235806271402856</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05703253672671704</v>
+      </c>
+      <c r="W84">
+        <v>0.22518063022966</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3168474262595392</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2969031598627095</v>
+      </c>
+      <c r="C85">
+        <v>-100.264971987118</v>
+      </c>
+      <c r="D85">
+        <v>112.9390280128821</v>
+      </c>
+      <c r="E85">
+        <v>261.804</v>
+      </c>
+      <c r="F85">
+        <v>272.9040000000001</v>
+      </c>
+      <c r="G85">
+        <v>59.7</v>
+      </c>
+      <c r="H85">
+        <v>317.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>24.4</v>
+      </c>
+      <c r="K85">
+        <v>4</v>
+      </c>
+      <c r="L85">
+        <v>20.4</v>
+      </c>
+      <c r="M85">
+        <v>65.16947520000002</v>
+      </c>
+      <c r="N85">
+        <v>-44.76947520000002</v>
+      </c>
+      <c r="O85">
+        <v>-8.058505536000002</v>
+      </c>
+      <c r="P85">
+        <v>-36.71096966400002</v>
+      </c>
+      <c r="Q85">
+        <v>-32.71096966400002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6462767239669902</v>
+      </c>
+      <c r="T85">
+        <v>6.602618405014789</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0563453977300096</v>
+      </c>
+      <c r="W85">
+        <v>0.2253447190220737</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3130299873889424</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2989031598627094</v>
+      </c>
+      <c r="C86">
+        <v>-104.4213891803</v>
+      </c>
+      <c r="D86">
+        <v>112.0706108197</v>
+      </c>
+      <c r="E86">
+        <v>265.092</v>
+      </c>
+      <c r="F86">
+        <v>276.192</v>
+      </c>
+      <c r="G86">
+        <v>59.7</v>
+      </c>
+      <c r="H86">
+        <v>317.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>24.4</v>
+      </c>
+      <c r="K86">
+        <v>4</v>
+      </c>
+      <c r="L86">
+        <v>20.4</v>
+      </c>
+      <c r="M86">
+        <v>65.95464960000001</v>
+      </c>
+      <c r="N86">
+        <v>-45.55464960000001</v>
+      </c>
+      <c r="O86">
+        <v>-8.199836928</v>
+      </c>
+      <c r="P86">
+        <v>-37.35481267200001</v>
+      </c>
+      <c r="Q86">
+        <v>-33.35481267200001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6842440192149266</v>
+      </c>
+      <c r="T86">
+        <v>7.015282055328209</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05567461918560474</v>
+      </c>
+      <c r="W86">
+        <v>0.2255049009384776</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3093034399200264</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3009031598627095</v>
+      </c>
+      <c r="C87">
+        <v>-108.5645533139823</v>
+      </c>
+      <c r="D87">
+        <v>111.2154466860177</v>
+      </c>
+      <c r="E87">
+        <v>268.38</v>
+      </c>
+      <c r="F87">
+        <v>279.48</v>
+      </c>
+      <c r="G87">
+        <v>59.7</v>
+      </c>
+      <c r="H87">
+        <v>317.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>24.4</v>
+      </c>
+      <c r="K87">
+        <v>4</v>
+      </c>
+      <c r="L87">
+        <v>20.4</v>
+      </c>
+      <c r="M87">
+        <v>66.73982400000001</v>
+      </c>
+      <c r="N87">
+        <v>-46.33982400000001</v>
+      </c>
+      <c r="O87">
+        <v>-8.34116832</v>
+      </c>
+      <c r="P87">
+        <v>-37.99865568000001</v>
+      </c>
+      <c r="Q87">
+        <v>-33.99865568000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7272736204959218</v>
+      </c>
+      <c r="T87">
+        <v>7.482967525683424</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05501962366577409</v>
+      </c>
+      <c r="W87">
+        <v>0.2256613138686132</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3056645759209673</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3029031598627095</v>
+      </c>
+      <c r="C88">
+        <v>-112.6947654764103</v>
+      </c>
+      <c r="D88">
+        <v>110.3732345235897</v>
+      </c>
+      <c r="E88">
+        <v>271.668</v>
+      </c>
+      <c r="F88">
+        <v>282.768</v>
+      </c>
+      <c r="G88">
+        <v>59.7</v>
+      </c>
+      <c r="H88">
+        <v>317.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>24.4</v>
+      </c>
+      <c r="K88">
+        <v>4</v>
+      </c>
+      <c r="L88">
+        <v>20.4</v>
+      </c>
+      <c r="M88">
+        <v>67.52499840000002</v>
+      </c>
+      <c r="N88">
+        <v>-47.12499840000002</v>
+      </c>
+      <c r="O88">
+        <v>-8.482499712000001</v>
+      </c>
+      <c r="P88">
+        <v>-38.64249868800002</v>
+      </c>
+      <c r="Q88">
+        <v>-34.64249868800002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.776450307674202</v>
+      </c>
+      <c r="T88">
+        <v>8.017465206089383</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05437986059989299</v>
+      </c>
+      <c r="W88">
+        <v>0.2258140892887456</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3021103366660723</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3049031598627094</v>
+      </c>
+      <c r="C89">
+        <v>-116.8123177040541</v>
+      </c>
+      <c r="D89">
+        <v>109.5436822959458</v>
+      </c>
+      <c r="E89">
+        <v>274.956</v>
+      </c>
+      <c r="F89">
+        <v>286.056</v>
+      </c>
+      <c r="G89">
+        <v>59.7</v>
+      </c>
+      <c r="H89">
+        <v>317.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>24.4</v>
+      </c>
+      <c r="K89">
+        <v>4</v>
+      </c>
+      <c r="L89">
+        <v>20.4</v>
+      </c>
+      <c r="M89">
+        <v>68.3101728</v>
+      </c>
+      <c r="N89">
+        <v>-47.91017280000001</v>
+      </c>
+      <c r="O89">
+        <v>-8.623831103999997</v>
+      </c>
+      <c r="P89">
+        <v>-39.28634169600001</v>
+      </c>
+      <c r="Q89">
+        <v>-35.28634169600001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8331926390337558</v>
+      </c>
+      <c r="T89">
+        <v>8.634193298865489</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05375480473092872</v>
+      </c>
+      <c r="W89">
+        <v>0.2259633526302542</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2986378040607152</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3069031598627095</v>
+      </c>
+      <c r="C90">
+        <v>-120.9174933192319</v>
+      </c>
+      <c r="D90">
+        <v>108.7265066807681</v>
+      </c>
+      <c r="E90">
+        <v>278.244</v>
+      </c>
+      <c r="F90">
+        <v>289.344</v>
+      </c>
+      <c r="G90">
+        <v>59.7</v>
+      </c>
+      <c r="H90">
+        <v>317.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>24.4</v>
+      </c>
+      <c r="K90">
+        <v>4</v>
+      </c>
+      <c r="L90">
+        <v>20.4</v>
+      </c>
+      <c r="M90">
+        <v>69.09534720000001</v>
+      </c>
+      <c r="N90">
+        <v>-48.69534720000001</v>
+      </c>
+      <c r="O90">
+        <v>-8.765162495999999</v>
+      </c>
+      <c r="P90">
+        <v>-39.93018470400001</v>
+      </c>
+      <c r="Q90">
+        <v>-35.93018470400001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8993920256199024</v>
+      </c>
+      <c r="T90">
+        <v>9.353709407104281</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05314395467716816</v>
+      </c>
+      <c r="W90">
+        <v>0.2261092236230923</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2952441926509344</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3089031598627094</v>
+      </c>
+      <c r="C91">
+        <v>-125.0105672527322</v>
+      </c>
+      <c r="D91">
+        <v>107.9214327472678</v>
+      </c>
+      <c r="E91">
+        <v>281.532</v>
+      </c>
+      <c r="F91">
+        <v>292.632</v>
+      </c>
+      <c r="G91">
+        <v>59.7</v>
+      </c>
+      <c r="H91">
+        <v>317.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>24.4</v>
+      </c>
+      <c r="K91">
+        <v>4</v>
+      </c>
+      <c r="L91">
+        <v>20.4</v>
+      </c>
+      <c r="M91">
+        <v>69.88052160000001</v>
+      </c>
+      <c r="N91">
+        <v>-49.48052160000001</v>
+      </c>
+      <c r="O91">
+        <v>-8.906493887999998</v>
+      </c>
+      <c r="P91">
+        <v>-40.57402771200001</v>
+      </c>
+      <c r="Q91">
+        <v>-36.57402771200001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9776276643126207</v>
+      </c>
+      <c r="T91">
+        <v>10.20404662593194</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05254683159090784</v>
+      </c>
+      <c r="W91">
+        <v>0.2262518166160912</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2919268421717104</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3109031598627094</v>
+      </c>
+      <c r="C92">
+        <v>-129.0918063522099</v>
+      </c>
+      <c r="D92">
+        <v>107.1281936477901</v>
+      </c>
+      <c r="E92">
+        <v>284.82</v>
+      </c>
+      <c r="F92">
+        <v>295.92</v>
+      </c>
+      <c r="G92">
+        <v>59.7</v>
+      </c>
+      <c r="H92">
+        <v>317.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>24.4</v>
+      </c>
+      <c r="K92">
+        <v>4</v>
+      </c>
+      <c r="L92">
+        <v>20.4</v>
+      </c>
+      <c r="M92">
+        <v>70.66569600000001</v>
+      </c>
+      <c r="N92">
+        <v>-50.26569600000001</v>
+      </c>
+      <c r="O92">
+        <v>-9.04782528</v>
+      </c>
+      <c r="P92">
+        <v>-41.21787072000001</v>
+      </c>
+      <c r="Q92">
+        <v>-37.21787072000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.071510430743883</v>
+      </c>
+      <c r="T92">
+        <v>11.22445128852514</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05196297790656442</v>
+      </c>
+      <c r="W92">
+        <v>0.2263912408759124</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2886832105920246</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3129031598627094</v>
+      </c>
+      <c r="C93">
+        <v>-133.1614696770796</v>
+      </c>
+      <c r="D93">
+        <v>106.3465303229204</v>
+      </c>
+      <c r="E93">
+        <v>288.108</v>
+      </c>
+      <c r="F93">
+        <v>299.208</v>
+      </c>
+      <c r="G93">
+        <v>59.7</v>
+      </c>
+      <c r="H93">
+        <v>317.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>24.4</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+      <c r="L93">
+        <v>20.4</v>
+      </c>
+      <c r="M93">
+        <v>71.45087040000001</v>
+      </c>
+      <c r="N93">
+        <v>-51.05087040000002</v>
+      </c>
+      <c r="O93">
+        <v>-9.189156671999999</v>
+      </c>
+      <c r="P93">
+        <v>-41.86171372800001</v>
+      </c>
+      <c r="Q93">
+        <v>-37.86171372800001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.18625603415987</v>
+      </c>
+      <c r="T93">
+        <v>12.47161254280571</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05139195617132745</v>
+      </c>
+      <c r="W93">
+        <v>0.226527600866287</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2855108676184859</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3149031598627094</v>
+      </c>
+      <c r="C94">
+        <v>-137.219808780593</v>
+      </c>
+      <c r="D94">
+        <v>105.5761912194071</v>
+      </c>
+      <c r="E94">
+        <v>291.396</v>
+      </c>
+      <c r="F94">
+        <v>302.496</v>
+      </c>
+      <c r="G94">
+        <v>59.7</v>
+      </c>
+      <c r="H94">
+        <v>317.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>24.4</v>
+      </c>
+      <c r="K94">
+        <v>4</v>
+      </c>
+      <c r="L94">
+        <v>20.4</v>
+      </c>
+      <c r="M94">
+        <v>72.23604480000002</v>
+      </c>
+      <c r="N94">
+        <v>-51.83604480000002</v>
+      </c>
+      <c r="O94">
+        <v>-9.330488064000001</v>
+      </c>
+      <c r="P94">
+        <v>-42.50555673600002</v>
+      </c>
+      <c r="Q94">
+        <v>-38.50555673600002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.329688038429854</v>
+      </c>
+      <c r="T94">
+        <v>14.03056411065643</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05083334795207389</v>
+      </c>
+      <c r="W94">
+        <v>0.2266609965090448</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2824074886226328</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3169031598627094</v>
+      </c>
+      <c r="C95">
+        <v>-141.2670679797443</v>
+      </c>
+      <c r="D95">
+        <v>104.8169320202557</v>
+      </c>
+      <c r="E95">
+        <v>294.684</v>
+      </c>
+      <c r="F95">
+        <v>305.784</v>
+      </c>
+      <c r="G95">
+        <v>59.7</v>
+      </c>
+      <c r="H95">
+        <v>317.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>24.4</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95">
+        <v>20.4</v>
+      </c>
+      <c r="M95">
+        <v>73.02121920000002</v>
+      </c>
+      <c r="N95">
+        <v>-52.62121920000002</v>
+      </c>
+      <c r="O95">
+        <v>-9.471819456</v>
+      </c>
+      <c r="P95">
+        <v>-43.14939974400002</v>
+      </c>
+      <c r="Q95">
+        <v>-39.14939974400002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.514100615348405</v>
+      </c>
+      <c r="T95">
+        <v>16.03493041217878</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05028675281280427</v>
+      </c>
+      <c r="W95">
+        <v>0.2267915234283024</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2793708489600238</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3189031598627095</v>
+      </c>
+      <c r="C96">
+        <v>-145.3034846136132</v>
+      </c>
+      <c r="D96">
+        <v>104.0685153863868</v>
+      </c>
+      <c r="E96">
+        <v>297.972</v>
+      </c>
+      <c r="F96">
+        <v>309.072</v>
+      </c>
+      <c r="G96">
+        <v>59.7</v>
+      </c>
+      <c r="H96">
+        <v>317.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>24.4</v>
+      </c>
+      <c r="K96">
+        <v>4</v>
+      </c>
+      <c r="L96">
+        <v>20.4</v>
+      </c>
+      <c r="M96">
+        <v>73.80639360000001</v>
+      </c>
+      <c r="N96">
+        <v>-53.40639360000001</v>
+      </c>
+      <c r="O96">
+        <v>-9.613150847999998</v>
+      </c>
+      <c r="P96">
+        <v>-43.79324275200001</v>
+      </c>
+      <c r="Q96">
+        <v>-39.79324275200001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.759984051239806</v>
+      </c>
+      <c r="T96">
+        <v>18.70741881420858</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04975178735734892</v>
+      </c>
+      <c r="W96">
+        <v>0.2269192731790651</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2763988186519385</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3209031598627095</v>
+      </c>
+      <c r="C97">
+        <v>-149.3292892907182</v>
+      </c>
+      <c r="D97">
+        <v>103.3307107092818</v>
+      </c>
+      <c r="E97">
+        <v>301.26</v>
+      </c>
+      <c r="F97">
+        <v>312.36</v>
+      </c>
+      <c r="G97">
+        <v>59.7</v>
+      </c>
+      <c r="H97">
+        <v>317.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>24.4</v>
+      </c>
+      <c r="K97">
+        <v>4</v>
+      </c>
+      <c r="L97">
+        <v>20.4</v>
+      </c>
+      <c r="M97">
+        <v>74.59156800000001</v>
+      </c>
+      <c r="N97">
+        <v>-54.19156800000001</v>
+      </c>
+      <c r="O97">
+        <v>-9.754482239999998</v>
+      </c>
+      <c r="P97">
+        <v>-44.43708576000002</v>
+      </c>
+      <c r="Q97">
+        <v>-40.43708576000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.104220861487769</v>
+      </c>
+      <c r="T97">
+        <v>22.44890257705031</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04922808433253472</v>
+      </c>
+      <c r="W97">
+        <v>0.2270443334613907</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2734893574029708</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3229031598627095</v>
+      </c>
+      <c r="C98">
+        <v>-153.3447061259213</v>
+      </c>
+      <c r="D98">
+        <v>102.6032938740787</v>
+      </c>
+      <c r="E98">
+        <v>304.548</v>
+      </c>
+      <c r="F98">
+        <v>315.648</v>
+      </c>
+      <c r="G98">
+        <v>59.7</v>
+      </c>
+      <c r="H98">
+        <v>317.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>24.4</v>
+      </c>
+      <c r="K98">
+        <v>4</v>
+      </c>
+      <c r="L98">
+        <v>20.4</v>
+      </c>
+      <c r="M98">
+        <v>75.37674240000001</v>
+      </c>
+      <c r="N98">
+        <v>-54.97674240000001</v>
+      </c>
+      <c r="O98">
+        <v>-9.895813631999999</v>
+      </c>
+      <c r="P98">
+        <v>-45.08092876800001</v>
+      </c>
+      <c r="Q98">
+        <v>-41.08092876800001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.620576076859705</v>
+      </c>
+      <c r="T98">
+        <v>28.06112822131282</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04871529178740415</v>
+      </c>
+      <c r="W98">
+        <v>0.2271667883211679</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2706405099300231</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3249031598627095</v>
+      </c>
+      <c r="C99">
+        <v>-157.3499529673985</v>
+      </c>
+      <c r="D99">
+        <v>101.8860470326015</v>
+      </c>
+      <c r="E99">
+        <v>307.836</v>
+      </c>
+      <c r="F99">
+        <v>318.936</v>
+      </c>
+      <c r="G99">
+        <v>59.7</v>
+      </c>
+      <c r="H99">
+        <v>317.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>24.4</v>
+      </c>
+      <c r="K99">
+        <v>4</v>
+      </c>
+      <c r="L99">
+        <v>20.4</v>
+      </c>
+      <c r="M99">
+        <v>76.1619168</v>
+      </c>
+      <c r="N99">
+        <v>-55.7619168</v>
+      </c>
+      <c r="O99">
+        <v>-10.037145024</v>
+      </c>
+      <c r="P99">
+        <v>-45.724771776</v>
+      </c>
+      <c r="Q99">
+        <v>-41.724771776</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.481168102479606</v>
+      </c>
+      <c r="T99">
+        <v>37.41483762841709</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04821307228444122</v>
+      </c>
+      <c r="W99">
+        <v>0.2272867183384754</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2678504015802291</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3269031598627095</v>
+      </c>
+      <c r="C100">
+        <v>-161.3452416141537</v>
+      </c>
+      <c r="D100">
+        <v>101.1787583858463</v>
+      </c>
+      <c r="E100">
+        <v>311.124</v>
+      </c>
+      <c r="F100">
+        <v>322.224</v>
+      </c>
+      <c r="G100">
+        <v>59.7</v>
+      </c>
+      <c r="H100">
+        <v>317.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>24.4</v>
+      </c>
+      <c r="K100">
+        <v>4</v>
+      </c>
+      <c r="L100">
+        <v>20.4</v>
+      </c>
+      <c r="M100">
+        <v>76.9470912</v>
+      </c>
+      <c r="N100">
+        <v>-56.5470912</v>
+      </c>
+      <c r="O100">
+        <v>-10.178476416</v>
+      </c>
+      <c r="P100">
+        <v>-46.36861478400001</v>
+      </c>
+      <c r="Q100">
+        <v>-42.36861478400001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.202352153719409</v>
+      </c>
+      <c r="T100">
+        <v>56.12225644262563</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04772110215908978</v>
+      </c>
+      <c r="W100">
+        <v>0.2274042008044094</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2651172342171656</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3289031598627095</v>
+      </c>
+      <c r="C101">
+        <v>-165.3307780245377</v>
+      </c>
+      <c r="D101">
+        <v>100.4812219754623</v>
+      </c>
+      <c r="E101">
+        <v>314.412</v>
+      </c>
+      <c r="F101">
+        <v>325.512</v>
+      </c>
+      <c r="G101">
+        <v>59.7</v>
+      </c>
+      <c r="H101">
+        <v>317.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>24.4</v>
+      </c>
+      <c r="K101">
+        <v>4</v>
+      </c>
+      <c r="L101">
+        <v>20.4</v>
+      </c>
+      <c r="M101">
+        <v>77.73226560000001</v>
+      </c>
+      <c r="N101">
+        <v>-57.33226560000001</v>
+      </c>
+      <c r="O101">
+        <v>-10.319807808</v>
+      </c>
+      <c r="P101">
+        <v>-47.01245779200001</v>
+      </c>
+      <c r="Q101">
+        <v>-43.01245779200001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.36590430743882</v>
+      </c>
+      <c r="T101">
+        <v>112.2445128852513</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04723907082414948</v>
+      </c>
+      <c r="W101">
+        <v>0.2275193098871931</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2624392823563861</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/croatia/croatia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_telecom_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.115338751039929</v>
+        <v>0.1151680412880571</v>
       </c>
       <c r="C2">
-        <v>267.7843637261835</v>
+        <v>265.4223966637711</v>
       </c>
       <c r="D2">
-        <v>197.7843637261835</v>
+        <v>198.1073966637711</v>
       </c>
       <c r="E2">
-        <v>-16.6</v>
+        <v>-13.915</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.685</v>
       </c>
       <c r="G2">
         <v>70</v>
@@ -1451,28 +1451,28 @@
         <v>28.732</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1350555</v>
       </c>
       <c r="N2">
-        <v>28.732</v>
+        <v>28.5969445</v>
       </c>
       <c r="O2">
-        <v>5.17176</v>
+        <v>5.14745001</v>
       </c>
       <c r="P2">
-        <v>23.56024</v>
+        <v>23.44949449</v>
       </c>
       <c r="Q2">
-        <v>23.22824</v>
+        <v>23.11749449</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.115338751039929</v>
+        <v>0.115914728573795</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.182235052088355</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>212.7421689601682</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1151680412880571</v>
+        <v>0.1149973315361852</v>
       </c>
       <c r="C3">
-        <v>265.4223966637711</v>
+        <v>263.0614865199801</v>
       </c>
       <c r="D3">
-        <v>198.1073966637711</v>
+        <v>198.4314865199801</v>
       </c>
       <c r="E3">
-        <v>-13.915</v>
+        <v>-11.23</v>
       </c>
       <c r="F3">
-        <v>2.685</v>
+        <v>5.37</v>
       </c>
       <c r="G3">
         <v>70</v>
@@ -1533,28 +1533,28 @@
         <v>28.732</v>
       </c>
       <c r="M3">
-        <v>0.1350555</v>
+        <v>0.270111</v>
       </c>
       <c r="N3">
-        <v>28.5969445</v>
+        <v>28.461889</v>
       </c>
       <c r="O3">
-        <v>5.14745001</v>
+        <v>5.12314002</v>
       </c>
       <c r="P3">
-        <v>23.44949449</v>
+        <v>23.33874898</v>
       </c>
       <c r="Q3">
-        <v>23.11749449</v>
+        <v>23.00674898</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.115914728573795</v>
+        <v>0.1165024607512094</v>
       </c>
       <c r="T3">
-        <v>1.182235052088355</v>
+        <v>1.192145060948307</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>212.7421689601682</v>
+        <v>106.3710844800841</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1149973315361852</v>
+        <v>0.1148266217843133</v>
       </c>
       <c r="C4">
-        <v>263.0614865199801</v>
+        <v>260.7016384904454</v>
       </c>
       <c r="D4">
-        <v>198.4314865199801</v>
+        <v>198.7566384904454</v>
       </c>
       <c r="E4">
-        <v>-11.23</v>
+        <v>-8.545000000000002</v>
       </c>
       <c r="F4">
-        <v>5.37</v>
+        <v>8.055</v>
       </c>
       <c r="G4">
         <v>70</v>
@@ -1615,28 +1615,28 @@
         <v>28.732</v>
       </c>
       <c r="M4">
-        <v>0.270111</v>
+        <v>0.4051665</v>
       </c>
       <c r="N4">
-        <v>28.461889</v>
+        <v>28.3268335</v>
       </c>
       <c r="O4">
-        <v>5.12314002</v>
+        <v>5.098830029999999</v>
       </c>
       <c r="P4">
-        <v>23.33874898</v>
+        <v>23.22800347</v>
       </c>
       <c r="Q4">
-        <v>23.00674898</v>
+        <v>22.89600347</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1165024607512094</v>
+        <v>0.1171023111178488</v>
       </c>
       <c r="T4">
-        <v>1.192145060948307</v>
+        <v>1.202259399887847</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.3710844800841</v>
+        <v>70.91405632005608</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1148266217843133</v>
+        <v>0.1146559120324415</v>
       </c>
       <c r="C5">
-        <v>260.7016384904454</v>
+        <v>258.3428578049119</v>
       </c>
       <c r="D5">
-        <v>198.7566384904454</v>
+        <v>199.0828578049119</v>
       </c>
       <c r="E5">
-        <v>-8.545000000000002</v>
+        <v>-5.860000000000001</v>
       </c>
       <c r="F5">
-        <v>8.055</v>
+        <v>10.74</v>
       </c>
       <c r="G5">
         <v>70</v>
@@ -1697,28 +1697,28 @@
         <v>28.732</v>
       </c>
       <c r="M5">
-        <v>0.4051665</v>
+        <v>0.540222</v>
       </c>
       <c r="N5">
-        <v>28.3268335</v>
+        <v>28.191778</v>
       </c>
       <c r="O5">
-        <v>5.098830029999999</v>
+        <v>5.074520039999999</v>
       </c>
       <c r="P5">
-        <v>23.22800347</v>
+        <v>23.11725796</v>
       </c>
       <c r="Q5">
-        <v>22.89600347</v>
+        <v>22.78525796</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1171023111178488</v>
+        <v>0.1177146583671265</v>
       </c>
       <c r="T5">
-        <v>1.202259399887847</v>
+        <v>1.212584454221959</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.91405632005608</v>
+        <v>53.18554224004206</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1146559120324415</v>
+        <v>0.1144852022805696</v>
       </c>
       <c r="C6">
-        <v>258.3428578049119</v>
+        <v>255.9851497275154</v>
       </c>
       <c r="D6">
-        <v>199.0828578049119</v>
+        <v>199.4101497275155</v>
       </c>
       <c r="E6">
-        <v>-5.860000000000001</v>
+        <v>-3.175000000000001</v>
       </c>
       <c r="F6">
-        <v>10.74</v>
+        <v>13.425</v>
       </c>
       <c r="G6">
         <v>70</v>
@@ -1779,28 +1779,28 @@
         <v>28.732</v>
       </c>
       <c r="M6">
-        <v>0.540222</v>
+        <v>0.6752775</v>
       </c>
       <c r="N6">
-        <v>28.191778</v>
+        <v>28.0567225</v>
       </c>
       <c r="O6">
-        <v>5.074520039999999</v>
+        <v>5.05021005</v>
       </c>
       <c r="P6">
-        <v>23.11725796</v>
+        <v>23.00651245</v>
       </c>
       <c r="Q6">
-        <v>22.78525796</v>
+        <v>22.67451245</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1177146583671265</v>
+        <v>0.1183398971374417</v>
       </c>
       <c r="T6">
-        <v>1.212584454221959</v>
+        <v>1.223126878121001</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.18554224004206</v>
+        <v>42.54843379203365</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1144852022805696</v>
+        <v>0.1143144925286977</v>
       </c>
       <c r="C7">
-        <v>255.9851497275154</v>
+        <v>253.6285195570659</v>
       </c>
       <c r="D7">
-        <v>199.4101497275155</v>
+        <v>199.738519557066</v>
       </c>
       <c r="E7">
-        <v>-3.175000000000001</v>
+        <v>-0.4899999999999984</v>
       </c>
       <c r="F7">
-        <v>13.425</v>
+        <v>16.11</v>
       </c>
       <c r="G7">
         <v>70</v>
@@ -1861,28 +1861,28 @@
         <v>28.732</v>
       </c>
       <c r="M7">
-        <v>0.6752775</v>
+        <v>0.8103330000000001</v>
       </c>
       <c r="N7">
-        <v>28.0567225</v>
+        <v>27.921667</v>
       </c>
       <c r="O7">
-        <v>5.05021005</v>
+        <v>5.02590006</v>
       </c>
       <c r="P7">
-        <v>23.00651245</v>
+        <v>22.89576694</v>
       </c>
       <c r="Q7">
-        <v>22.67451245</v>
+        <v>22.56376694</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1183398971374417</v>
+        <v>0.1189784388603167</v>
       </c>
       <c r="T7">
-        <v>1.223126878121001</v>
+        <v>1.233893608911512</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.54843379203365</v>
+        <v>35.45702816002803</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1143144925286977</v>
+        <v>0.1141437827768259</v>
       </c>
       <c r="C8">
-        <v>253.6285195570659</v>
+        <v>251.272972627333</v>
       </c>
       <c r="D8">
-        <v>199.738519557066</v>
+        <v>200.067972627333</v>
       </c>
       <c r="E8">
-        <v>-0.490000000000002</v>
+        <v>2.194999999999997</v>
       </c>
       <c r="F8">
-        <v>16.11</v>
+        <v>18.795</v>
       </c>
       <c r="G8">
         <v>70</v>
@@ -1943,28 +1943,28 @@
         <v>28.732</v>
       </c>
       <c r="M8">
-        <v>0.810333</v>
+        <v>0.9453884999999999</v>
       </c>
       <c r="N8">
-        <v>27.921667</v>
+        <v>27.7866115</v>
       </c>
       <c r="O8">
-        <v>5.02590006</v>
+        <v>5.00159007</v>
       </c>
       <c r="P8">
-        <v>22.89576694</v>
+        <v>22.78502143</v>
       </c>
       <c r="Q8">
-        <v>22.56376694</v>
+        <v>22.45302143</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1189784388603167</v>
+        <v>0.1196307126632536</v>
       </c>
       <c r="T8">
-        <v>1.233893608911512</v>
+        <v>1.244891882299668</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.45702816002804</v>
+        <v>30.39173842288118</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1141437827768259</v>
+        <v>0.113973073024954</v>
       </c>
       <c r="C9">
-        <v>251.2729726273331</v>
+        <v>248.9185143073352</v>
       </c>
       <c r="D9">
-        <v>200.0679726273331</v>
+        <v>200.3985143073351</v>
       </c>
       <c r="E9">
-        <v>2.195</v>
+        <v>4.879999999999999</v>
       </c>
       <c r="F9">
-        <v>18.795</v>
+        <v>21.48</v>
       </c>
       <c r="G9">
         <v>70</v>
@@ -2025,28 +2025,28 @@
         <v>28.732</v>
       </c>
       <c r="M9">
-        <v>0.9453885000000001</v>
+        <v>1.080444</v>
       </c>
       <c r="N9">
-        <v>27.7866115</v>
+        <v>27.651556</v>
       </c>
       <c r="O9">
-        <v>5.00159007</v>
+        <v>4.97728008</v>
       </c>
       <c r="P9">
-        <v>22.78502143</v>
+        <v>22.67427592</v>
       </c>
       <c r="Q9">
-        <v>22.45302143</v>
+        <v>22.34227592</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1196307126632536</v>
+        <v>0.1202971663314717</v>
       </c>
       <c r="T9">
-        <v>1.244891882299668</v>
+        <v>1.256129248587566</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.39173842288117</v>
+        <v>26.59277112002103</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.113973073024954</v>
+        <v>0.1138023632730821</v>
       </c>
       <c r="C10">
-        <v>248.9185143073352</v>
+        <v>246.5651500016309</v>
       </c>
       <c r="D10">
-        <v>200.3985143073351</v>
+        <v>200.7301500016309</v>
       </c>
       <c r="E10">
-        <v>4.879999999999999</v>
+        <v>7.564999999999998</v>
       </c>
       <c r="F10">
-        <v>21.48</v>
+        <v>24.165</v>
       </c>
       <c r="G10">
         <v>70</v>
@@ -2107,28 +2107,28 @@
         <v>28.732</v>
       </c>
       <c r="M10">
-        <v>1.080444</v>
+        <v>1.2154995</v>
       </c>
       <c r="N10">
-        <v>27.651556</v>
+        <v>27.5165005</v>
       </c>
       <c r="O10">
-        <v>4.97728008</v>
+        <v>4.95297009</v>
       </c>
       <c r="P10">
-        <v>22.67427592</v>
+        <v>22.56353041</v>
       </c>
       <c r="Q10">
-        <v>22.34227592</v>
+        <v>22.23153041</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1202971663314717</v>
+        <v>0.1209782673330573</v>
       </c>
       <c r="T10">
-        <v>1.256129248587566</v>
+        <v>1.267613589958715</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.59277112002103</v>
+        <v>23.63801877335203</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1138023632730821</v>
+        <v>0.1136316535212102</v>
       </c>
       <c r="C11">
-        <v>246.5651500016309</v>
+        <v>244.212885150614</v>
       </c>
       <c r="D11">
-        <v>200.7301500016309</v>
+        <v>201.062885150614</v>
       </c>
       <c r="E11">
-        <v>7.564999999999998</v>
+        <v>10.25</v>
       </c>
       <c r="F11">
-        <v>24.165</v>
+        <v>26.85</v>
       </c>
       <c r="G11">
         <v>70</v>
@@ -2189,28 +2189,28 @@
         <v>28.732</v>
       </c>
       <c r="M11">
-        <v>1.2154995</v>
+        <v>1.350555</v>
       </c>
       <c r="N11">
-        <v>27.5165005</v>
+        <v>27.381445</v>
       </c>
       <c r="O11">
-        <v>4.95297009</v>
+        <v>4.9286601</v>
       </c>
       <c r="P11">
-        <v>22.56353041</v>
+        <v>22.4527849</v>
       </c>
       <c r="Q11">
-        <v>22.23153041</v>
+        <v>22.1207849</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1209782673330573</v>
+        <v>0.1216745039124558</v>
       </c>
       <c r="T11">
-        <v>1.267613589958715</v>
+        <v>1.27935313891589</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.63801877335203</v>
+        <v>21.27421689601683</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1136316535212103</v>
+        <v>0.1134609437693384</v>
       </c>
       <c r="C12">
-        <v>244.212885150614</v>
+        <v>241.8617252308104</v>
       </c>
       <c r="D12">
-        <v>201.0628851506139</v>
+        <v>201.3967252308103</v>
       </c>
       <c r="E12">
-        <v>10.25</v>
+        <v>12.935</v>
       </c>
       <c r="F12">
-        <v>26.85</v>
+        <v>29.535</v>
       </c>
       <c r="G12">
         <v>70</v>
@@ -2271,28 +2271,28 @@
         <v>28.732</v>
       </c>
       <c r="M12">
-        <v>1.350555</v>
+        <v>1.4856105</v>
       </c>
       <c r="N12">
-        <v>27.381445</v>
+        <v>27.2463895</v>
       </c>
       <c r="O12">
-        <v>4.9286601</v>
+        <v>4.904350109999999</v>
       </c>
       <c r="P12">
-        <v>22.4527849</v>
+        <v>22.34203939</v>
       </c>
       <c r="Q12">
-        <v>22.1207849</v>
+        <v>22.01003939</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1216745039124558</v>
+        <v>0.1223863862576836</v>
       </c>
       <c r="T12">
-        <v>1.27935313891589</v>
+        <v>1.291356497961989</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.27421689601682</v>
+        <v>19.34019717819711</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1134609437693384</v>
+        <v>0.1132902340174665</v>
       </c>
       <c r="C13">
-        <v>241.8617252308104</v>
+        <v>239.5116757551789</v>
       </c>
       <c r="D13">
-        <v>201.3967252308103</v>
+        <v>201.7316757551789</v>
       </c>
       <c r="E13">
-        <v>12.935</v>
+        <v>15.62</v>
       </c>
       <c r="F13">
-        <v>29.535</v>
+        <v>32.22</v>
       </c>
       <c r="G13">
         <v>70</v>
@@ -2353,28 +2353,28 @@
         <v>28.732</v>
       </c>
       <c r="M13">
-        <v>1.4856105</v>
+        <v>1.620666</v>
       </c>
       <c r="N13">
-        <v>27.2463895</v>
+        <v>27.111334</v>
       </c>
       <c r="O13">
-        <v>4.904350109999999</v>
+        <v>4.880040119999999</v>
       </c>
       <c r="P13">
-        <v>22.34203939</v>
+        <v>22.23129388</v>
       </c>
       <c r="Q13">
-        <v>22.01003939</v>
+        <v>21.89929388</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1223863862576836</v>
+        <v>0.123114447747121</v>
       </c>
       <c r="T13">
-        <v>1.291356497961989</v>
+        <v>1.303632660622773</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.34019717819711</v>
+        <v>17.72851408001402</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1132902340174665</v>
+        <v>0.1131195242655946</v>
       </c>
       <c r="C14">
-        <v>239.5116757551789</v>
+        <v>237.1627422734149</v>
       </c>
       <c r="D14">
-        <v>201.7316757551789</v>
+        <v>202.0677422734149</v>
       </c>
       <c r="E14">
-        <v>15.62</v>
+        <v>18.305</v>
       </c>
       <c r="F14">
-        <v>32.22</v>
+        <v>34.905</v>
       </c>
       <c r="G14">
         <v>70</v>
@@ -2435,28 +2435,28 @@
         <v>28.732</v>
       </c>
       <c r="M14">
-        <v>1.620666</v>
+        <v>1.7557215</v>
       </c>
       <c r="N14">
-        <v>27.111334</v>
+        <v>26.9762785</v>
       </c>
       <c r="O14">
-        <v>4.880040119999999</v>
+        <v>4.85573013</v>
       </c>
       <c r="P14">
-        <v>22.23129388</v>
+        <v>22.12054837</v>
       </c>
       <c r="Q14">
-        <v>21.89929388</v>
+        <v>21.78854837</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.123114447747121</v>
+        <v>0.1238592462822927</v>
       </c>
       <c r="T14">
-        <v>1.303632660622773</v>
+        <v>1.316191033919437</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.72851408001402</v>
+        <v>16.36478222770525</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1131195242655946</v>
+        <v>0.1129488145137228</v>
       </c>
       <c r="C15">
-        <v>237.1627422734149</v>
+        <v>234.8149303722564</v>
       </c>
       <c r="D15">
-        <v>202.0677422734149</v>
+        <v>202.4049303722564</v>
       </c>
       <c r="E15">
-        <v>18.305</v>
+        <v>20.99</v>
       </c>
       <c r="F15">
-        <v>34.905</v>
+        <v>37.59</v>
       </c>
       <c r="G15">
         <v>70</v>
@@ -2517,28 +2517,28 @@
         <v>28.732</v>
       </c>
       <c r="M15">
-        <v>1.7557215</v>
+        <v>1.890777</v>
       </c>
       <c r="N15">
-        <v>26.9762785</v>
+        <v>26.841223</v>
       </c>
       <c r="O15">
-        <v>4.85573013</v>
+        <v>4.83142014</v>
       </c>
       <c r="P15">
-        <v>22.12054837</v>
+        <v>22.00980286</v>
       </c>
       <c r="Q15">
-        <v>21.78854837</v>
+        <v>21.67780286</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1238592462822927</v>
+        <v>0.1246213657136311</v>
       </c>
       <c r="T15">
-        <v>1.316191033919437</v>
+        <v>1.329041462409047</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.36478222770525</v>
+        <v>15.19586921144059</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1129488145137228</v>
+        <v>0.1127781047618509</v>
       </c>
       <c r="C16">
-        <v>234.8149303722564</v>
+        <v>232.468245675794</v>
       </c>
       <c r="D16">
-        <v>202.4049303722564</v>
+        <v>202.743245675794</v>
       </c>
       <c r="E16">
-        <v>20.99</v>
+        <v>23.675</v>
       </c>
       <c r="F16">
-        <v>37.59</v>
+        <v>40.27500000000001</v>
       </c>
       <c r="G16">
         <v>70</v>
@@ -2599,28 +2599,28 @@
         <v>28.732</v>
       </c>
       <c r="M16">
-        <v>1.890777</v>
+        <v>2.0258325</v>
       </c>
       <c r="N16">
-        <v>26.841223</v>
+        <v>26.7061675</v>
       </c>
       <c r="O16">
-        <v>4.83142014</v>
+        <v>4.80711015</v>
       </c>
       <c r="P16">
-        <v>22.00980286</v>
+        <v>21.89905735</v>
       </c>
       <c r="Q16">
-        <v>21.67780286</v>
+        <v>21.56705735</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1246213657136311</v>
+        <v>0.1254014173668834</v>
       </c>
       <c r="T16">
-        <v>1.329041462409047</v>
+        <v>1.342194253921942</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.19586921144059</v>
+        <v>14.18281126401121</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1127781047618509</v>
+        <v>0.112607395009979</v>
       </c>
       <c r="C17">
-        <v>232.468245675794</v>
+        <v>230.1226938457833</v>
       </c>
       <c r="D17">
-        <v>202.743245675794</v>
+        <v>203.0826938457833</v>
       </c>
       <c r="E17">
-        <v>23.675</v>
+        <v>26.36</v>
       </c>
       <c r="F17">
-        <v>40.275</v>
+        <v>42.96</v>
       </c>
       <c r="G17">
         <v>70</v>
@@ -2681,28 +2681,28 @@
         <v>28.732</v>
       </c>
       <c r="M17">
-        <v>2.0258325</v>
+        <v>2.160888</v>
       </c>
       <c r="N17">
-        <v>26.7061675</v>
+        <v>26.571112</v>
       </c>
       <c r="O17">
-        <v>4.80711015</v>
+        <v>4.78280016</v>
       </c>
       <c r="P17">
-        <v>21.89905735</v>
+        <v>21.78831184</v>
       </c>
       <c r="Q17">
-        <v>21.56705735</v>
+        <v>21.45631184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1254014173668834</v>
+        <v>0.1262000416785464</v>
       </c>
       <c r="T17">
-        <v>1.342194253921942</v>
+        <v>1.355660207137524</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.18281126401122</v>
+        <v>13.29638556001052</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.112607395009979</v>
+        <v>0.1126457852581071</v>
       </c>
       <c r="C18">
-        <v>230.1226938457833</v>
+        <v>227.3612576454264</v>
       </c>
       <c r="D18">
-        <v>203.0826938457833</v>
+        <v>203.0062576454264</v>
       </c>
       <c r="E18">
-        <v>26.36</v>
+        <v>29.045</v>
       </c>
       <c r="F18">
-        <v>42.96</v>
+        <v>45.645</v>
       </c>
       <c r="G18">
         <v>70</v>
@@ -2763,45 +2763,45 @@
         <v>28.732</v>
       </c>
       <c r="M18">
-        <v>2.160888</v>
+        <v>2.364411</v>
       </c>
       <c r="N18">
-        <v>26.571112</v>
+        <v>26.367589</v>
       </c>
       <c r="O18">
-        <v>4.78280016</v>
+        <v>4.74616602</v>
       </c>
       <c r="P18">
-        <v>21.78831184</v>
+        <v>21.62142298</v>
       </c>
       <c r="Q18">
-        <v>21.45631184</v>
+        <v>21.28942298</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1262000416785464</v>
+        <v>0.1270179099495267</v>
       </c>
       <c r="T18">
-        <v>1.355660207137524</v>
+        <v>1.369450641153482</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.29638556001052</v>
+        <v>12.15186361423627</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1126457852581071</v>
+        <v>0.1124873755062353</v>
       </c>
       <c r="C19">
-        <v>227.3612576454264</v>
+        <v>224.992028180033</v>
       </c>
       <c r="D19">
-        <v>203.0062576454264</v>
+        <v>203.3220281800331</v>
       </c>
       <c r="E19">
-        <v>29.045</v>
+        <v>31.73</v>
       </c>
       <c r="F19">
-        <v>45.645</v>
+        <v>48.33000000000001</v>
       </c>
       <c r="G19">
         <v>70</v>
@@ -2845,28 +2845,28 @@
         <v>28.732</v>
       </c>
       <c r="M19">
-        <v>2.364411</v>
+        <v>2.503494</v>
       </c>
       <c r="N19">
-        <v>26.367589</v>
+        <v>26.228506</v>
       </c>
       <c r="O19">
-        <v>4.74616602</v>
+        <v>4.72113108</v>
       </c>
       <c r="P19">
-        <v>21.62142298</v>
+        <v>21.50737492</v>
       </c>
       <c r="Q19">
-        <v>21.28942298</v>
+        <v>21.17537492</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1270179099495267</v>
+        <v>0.1278557262271162</v>
       </c>
       <c r="T19">
-        <v>1.369450641153482</v>
+        <v>1.38357742721861</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.15186361423627</v>
+        <v>11.47676008011203</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1124873755062353</v>
+        <v>0.1123289657543634</v>
       </c>
       <c r="C20">
-        <v>224.9920281800332</v>
+        <v>222.6237825894329</v>
       </c>
       <c r="D20">
-        <v>203.3220281800331</v>
+        <v>203.6387825894329</v>
       </c>
       <c r="E20">
-        <v>31.73</v>
+        <v>34.415</v>
       </c>
       <c r="F20">
-        <v>48.33</v>
+        <v>51.015</v>
       </c>
       <c r="G20">
         <v>70</v>
@@ -2927,28 +2927,28 @@
         <v>28.732</v>
       </c>
       <c r="M20">
-        <v>2.503494</v>
+        <v>2.642577</v>
       </c>
       <c r="N20">
-        <v>26.228506</v>
+        <v>26.089423</v>
       </c>
       <c r="O20">
-        <v>4.72113108</v>
+        <v>4.69609614</v>
       </c>
       <c r="P20">
-        <v>21.50737492</v>
+        <v>21.39332686</v>
       </c>
       <c r="Q20">
-        <v>21.17537492</v>
+        <v>21.06132686</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1278557262271162</v>
+        <v>0.1287142293263746</v>
       </c>
       <c r="T20">
-        <v>1.38357742721861</v>
+        <v>1.39805302281621</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.47676008011203</v>
+        <v>10.87272007589561</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1123289657543634</v>
+        <v>0.1121705560024915</v>
       </c>
       <c r="C21">
-        <v>222.6237825894329</v>
+        <v>220.256525479122</v>
       </c>
       <c r="D21">
-        <v>203.6387825894329</v>
+        <v>203.956525479122</v>
       </c>
       <c r="E21">
-        <v>34.415</v>
+        <v>37.1</v>
       </c>
       <c r="F21">
-        <v>51.015</v>
+        <v>53.7</v>
       </c>
       <c r="G21">
         <v>70</v>
@@ -3009,28 +3009,28 @@
         <v>28.732</v>
       </c>
       <c r="M21">
-        <v>2.642577</v>
+        <v>2.78166</v>
       </c>
       <c r="N21">
-        <v>26.089423</v>
+        <v>25.95034</v>
       </c>
       <c r="O21">
-        <v>4.69609614</v>
+        <v>4.6710612</v>
       </c>
       <c r="P21">
-        <v>21.39332686</v>
+        <v>21.2792788</v>
       </c>
       <c r="Q21">
-        <v>21.06132686</v>
+        <v>20.9472788</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1287142293263746</v>
+        <v>0.1295941950031144</v>
       </c>
       <c r="T21">
-        <v>1.39805302281621</v>
+        <v>1.41289050830375</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.87272007589561</v>
+        <v>10.32908407210083</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1121705560024915</v>
+        <v>0.1120121462506196</v>
       </c>
       <c r="C22">
-        <v>220.256525479122</v>
+        <v>217.8902614833859</v>
       </c>
       <c r="D22">
-        <v>203.956525479122</v>
+        <v>204.2752614833859</v>
       </c>
       <c r="E22">
-        <v>37.1</v>
+        <v>39.785</v>
       </c>
       <c r="F22">
-        <v>53.7</v>
+        <v>56.38500000000001</v>
       </c>
       <c r="G22">
         <v>70</v>
@@ -3091,28 +3091,28 @@
         <v>28.732</v>
       </c>
       <c r="M22">
-        <v>2.78166</v>
+        <v>2.920743</v>
       </c>
       <c r="N22">
-        <v>25.95034</v>
+        <v>25.811257</v>
       </c>
       <c r="O22">
-        <v>4.6710612</v>
+        <v>4.646026259999999</v>
       </c>
       <c r="P22">
-        <v>21.2792788</v>
+        <v>21.16523074</v>
       </c>
       <c r="Q22">
-        <v>20.9472788</v>
+        <v>20.83323074</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1295941950031144</v>
+        <v>0.1304964382919236</v>
       </c>
       <c r="T22">
-        <v>1.41289050830375</v>
+        <v>1.428103626335278</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.32908407210083</v>
+        <v>9.837222925810314</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1120121462506196</v>
+        <v>0.1121604164987478</v>
       </c>
       <c r="C23">
-        <v>217.8902614833859</v>
+        <v>214.906897359464</v>
       </c>
       <c r="D23">
-        <v>204.2752614833859</v>
+        <v>203.976897359464</v>
       </c>
       <c r="E23">
-        <v>39.785</v>
+        <v>42.47</v>
       </c>
       <c r="F23">
-        <v>56.385</v>
+        <v>59.07</v>
       </c>
       <c r="G23">
         <v>70</v>
@@ -3173,45 +3173,45 @@
         <v>28.732</v>
       </c>
       <c r="M23">
-        <v>2.920743</v>
+        <v>3.160245</v>
       </c>
       <c r="N23">
-        <v>25.811257</v>
+        <v>25.571755</v>
       </c>
       <c r="O23">
-        <v>4.646026259999999</v>
+        <v>4.6029159</v>
       </c>
       <c r="P23">
-        <v>21.16523074</v>
+        <v>20.9688391</v>
       </c>
       <c r="Q23">
-        <v>20.83323074</v>
+        <v>20.6368391</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1304964382919236</v>
+        <v>0.1314218160240356</v>
       </c>
       <c r="T23">
-        <v>1.428103626335278</v>
+        <v>1.443706824316333</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.18</v>
       </c>
       <c r="W23">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.837222925810316</v>
+        <v>9.091700168816025</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1121604164987478</v>
+        <v>0.1120159467468759</v>
       </c>
       <c r="C24">
-        <v>214.906897359464</v>
+        <v>212.5126028477758</v>
       </c>
       <c r="D24">
-        <v>203.976897359464</v>
+        <v>204.2676028477758</v>
       </c>
       <c r="E24">
-        <v>42.47</v>
+        <v>45.155</v>
       </c>
       <c r="F24">
-        <v>59.07</v>
+        <v>61.755</v>
       </c>
       <c r="G24">
         <v>70</v>
@@ -3255,28 +3255,28 @@
         <v>28.732</v>
       </c>
       <c r="M24">
-        <v>3.160245</v>
+        <v>3.3038925</v>
       </c>
       <c r="N24">
-        <v>25.571755</v>
+        <v>25.4281075</v>
       </c>
       <c r="O24">
-        <v>4.6029159</v>
+        <v>4.57705935</v>
       </c>
       <c r="P24">
-        <v>20.9688391</v>
+        <v>20.85104815</v>
       </c>
       <c r="Q24">
-        <v>20.6368391</v>
+        <v>20.51904815</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1314218160240356</v>
+        <v>0.1323712295413973</v>
       </c>
       <c r="T24">
-        <v>1.443706824316333</v>
+        <v>1.459715300167026</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.091700168816025</v>
+        <v>8.696408857128372</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1120159467468759</v>
+        <v>0.111871476995004</v>
       </c>
       <c r="C25">
-        <v>212.5126028477758</v>
+        <v>210.1191381388364</v>
       </c>
       <c r="D25">
-        <v>204.2676028477758</v>
+        <v>204.5591381388363</v>
       </c>
       <c r="E25">
-        <v>45.155</v>
+        <v>47.84000000000001</v>
       </c>
       <c r="F25">
-        <v>61.755</v>
+        <v>64.44000000000001</v>
       </c>
       <c r="G25">
         <v>70</v>
@@ -3337,28 +3337,28 @@
         <v>28.732</v>
       </c>
       <c r="M25">
-        <v>3.3038925</v>
+        <v>3.44754</v>
       </c>
       <c r="N25">
-        <v>25.4281075</v>
+        <v>25.28446</v>
       </c>
       <c r="O25">
-        <v>4.57705935</v>
+        <v>4.5512028</v>
       </c>
       <c r="P25">
-        <v>20.85104815</v>
+        <v>20.7332572</v>
       </c>
       <c r="Q25">
-        <v>20.51904815</v>
+        <v>20.4012572</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1323712295413973</v>
+        <v>0.1333456276250053</v>
       </c>
       <c r="T25">
-        <v>1.459715300167026</v>
+        <v>1.476145051697999</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.696408857128372</v>
+        <v>8.334058488081356</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.111871476995004</v>
+        <v>0.1117270072431322</v>
       </c>
       <c r="C26">
-        <v>210.1191381388364</v>
+        <v>207.7265067906627</v>
       </c>
       <c r="D26">
-        <v>204.5591381388364</v>
+        <v>204.8515067906627</v>
       </c>
       <c r="E26">
-        <v>47.84</v>
+        <v>50.525</v>
       </c>
       <c r="F26">
-        <v>64.44</v>
+        <v>67.125</v>
       </c>
       <c r="G26">
         <v>70</v>
@@ -3419,28 +3419,28 @@
         <v>28.732</v>
       </c>
       <c r="M26">
-        <v>3.44754</v>
+        <v>3.5911875</v>
       </c>
       <c r="N26">
-        <v>25.28446</v>
+        <v>25.1408125</v>
       </c>
       <c r="O26">
-        <v>4.5512028</v>
+        <v>4.525346249999999</v>
       </c>
       <c r="P26">
-        <v>20.7332572</v>
+        <v>20.61546625</v>
       </c>
       <c r="Q26">
-        <v>20.4012572</v>
+        <v>20.28346625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1333456276250053</v>
+        <v>0.1343460096575095</v>
       </c>
       <c r="T26">
-        <v>1.476145051697999</v>
+        <v>1.493012929936466</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.334058488081357</v>
+        <v>8.000696148558102</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1117270072431322</v>
+        <v>0.1115825374912603</v>
       </c>
       <c r="C27">
-        <v>207.7265067906627</v>
+        <v>205.3347123816425</v>
       </c>
       <c r="D27">
-        <v>204.8515067906627</v>
+        <v>205.1447123816425</v>
       </c>
       <c r="E27">
-        <v>50.525</v>
+        <v>53.21</v>
       </c>
       <c r="F27">
-        <v>67.125</v>
+        <v>69.81</v>
       </c>
       <c r="G27">
         <v>70</v>
@@ -3501,28 +3501,28 @@
         <v>28.732</v>
       </c>
       <c r="M27">
-        <v>3.5911875</v>
+        <v>3.734835</v>
       </c>
       <c r="N27">
-        <v>25.1408125</v>
+        <v>24.997165</v>
       </c>
       <c r="O27">
-        <v>4.525346249999999</v>
+        <v>4.4994897</v>
       </c>
       <c r="P27">
-        <v>20.61546625</v>
+        <v>20.4976753</v>
       </c>
       <c r="Q27">
-        <v>20.28346625</v>
+        <v>20.1656753</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1343460096575095</v>
+        <v>0.1353734290422436</v>
       </c>
       <c r="T27">
-        <v>1.493012929936466</v>
+        <v>1.510336696775972</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.000696148558102</v>
+        <v>7.692977065921252</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1115825374912603</v>
+        <v>0.1116151877393884</v>
       </c>
       <c r="C28">
-        <v>205.3347123816425</v>
+        <v>202.5833743608723</v>
       </c>
       <c r="D28">
-        <v>205.1447123816425</v>
+        <v>205.0783743608723</v>
       </c>
       <c r="E28">
-        <v>53.21</v>
+        <v>55.895</v>
       </c>
       <c r="F28">
-        <v>69.81</v>
+        <v>72.495</v>
       </c>
       <c r="G28">
         <v>70</v>
@@ -3583,45 +3583,45 @@
         <v>28.732</v>
       </c>
       <c r="M28">
-        <v>3.734835</v>
+        <v>3.9364785</v>
       </c>
       <c r="N28">
-        <v>24.997165</v>
+        <v>24.7955215</v>
       </c>
       <c r="O28">
-        <v>4.4994897</v>
+        <v>4.46319387</v>
       </c>
       <c r="P28">
-        <v>20.4976753</v>
+        <v>20.33232763</v>
       </c>
       <c r="Q28">
-        <v>20.1656753</v>
+        <v>20.00032763</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1353734290422436</v>
+        <v>0.1364289969032718</v>
       </c>
       <c r="T28">
-        <v>1.510336696775972</v>
+        <v>1.528135087364506</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.18</v>
       </c>
       <c r="W28">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.692977065921252</v>
+        <v>7.298909418659342</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1116151877393884</v>
+        <v>0.1114772779875165</v>
       </c>
       <c r="C29">
-        <v>202.5833743608723</v>
+        <v>200.1788687231788</v>
       </c>
       <c r="D29">
-        <v>205.0783743608723</v>
+        <v>205.3588687231788</v>
       </c>
       <c r="E29">
-        <v>55.895</v>
+        <v>58.58000000000001</v>
       </c>
       <c r="F29">
-        <v>72.495</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="G29">
         <v>70</v>
@@ -3665,28 +3665,28 @@
         <v>28.732</v>
       </c>
       <c r="M29">
-        <v>3.9364785</v>
+        <v>4.082274000000001</v>
       </c>
       <c r="N29">
-        <v>24.7955215</v>
+        <v>24.649726</v>
       </c>
       <c r="O29">
-        <v>4.46319387</v>
+        <v>4.43695068</v>
       </c>
       <c r="P29">
-        <v>20.33232763</v>
+        <v>20.21277532</v>
       </c>
       <c r="Q29">
-        <v>20.00032763</v>
+        <v>19.88077532</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1364289969032718</v>
+        <v>0.137513886093773</v>
       </c>
       <c r="T29">
-        <v>1.528135087364506</v>
+        <v>1.54642787769161</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.298909418659342</v>
+        <v>7.03823408227865</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1114772779875165</v>
+        <v>0.1113393682356447</v>
       </c>
       <c r="C30">
-        <v>200.1788687231788</v>
+        <v>197.7751314243693</v>
       </c>
       <c r="D30">
-        <v>205.3588687231788</v>
+        <v>205.6401314243693</v>
       </c>
       <c r="E30">
-        <v>58.58000000000001</v>
+        <v>61.26500000000001</v>
       </c>
       <c r="F30">
-        <v>75.18000000000001</v>
+        <v>77.86500000000001</v>
       </c>
       <c r="G30">
         <v>70</v>
@@ -3747,28 +3747,28 @@
         <v>28.732</v>
       </c>
       <c r="M30">
-        <v>4.082274000000001</v>
+        <v>4.2280695</v>
       </c>
       <c r="N30">
-        <v>24.649726</v>
+        <v>24.5039305</v>
       </c>
       <c r="O30">
-        <v>4.43695068</v>
+        <v>4.41070749</v>
       </c>
       <c r="P30">
-        <v>20.21277532</v>
+        <v>20.09322301</v>
       </c>
       <c r="Q30">
-        <v>19.88077532</v>
+        <v>19.76122301</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.137513886093773</v>
+        <v>0.1386293355431615</v>
       </c>
       <c r="T30">
-        <v>1.54642787769161</v>
+        <v>1.565235957887083</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.03823408227865</v>
+        <v>6.795536355303526</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1113393682356447</v>
+        <v>0.1112014584837728</v>
       </c>
       <c r="C31">
-        <v>197.7751314243693</v>
+        <v>195.3721656257604</v>
       </c>
       <c r="D31">
-        <v>205.6401314243693</v>
+        <v>205.9221656257604</v>
       </c>
       <c r="E31">
-        <v>61.26499999999999</v>
+        <v>63.95</v>
       </c>
       <c r="F31">
-        <v>77.86499999999999</v>
+        <v>80.55</v>
       </c>
       <c r="G31">
         <v>70</v>
@@ -3829,28 +3829,28 @@
         <v>28.732</v>
       </c>
       <c r="M31">
-        <v>4.2280695</v>
+        <v>4.373865</v>
       </c>
       <c r="N31">
-        <v>24.5039305</v>
+        <v>24.358135</v>
       </c>
       <c r="O31">
-        <v>4.41070749</v>
+        <v>4.384464299999999</v>
       </c>
       <c r="P31">
-        <v>20.09322301</v>
+        <v>19.9736707</v>
       </c>
       <c r="Q31">
-        <v>19.76122301</v>
+        <v>19.6416707</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1386293355431615</v>
+        <v>0.1397766549768183</v>
       </c>
       <c r="T31">
-        <v>1.565235957887083</v>
+        <v>1.584581411802427</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.795536355303526</v>
+        <v>6.569018476793407</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1112014584837728</v>
+        <v>0.1110635487319009</v>
       </c>
       <c r="C32">
-        <v>195.3721656257604</v>
+        <v>192.9699745060351</v>
       </c>
       <c r="D32">
-        <v>205.9221656257604</v>
+        <v>206.2049745060351</v>
       </c>
       <c r="E32">
-        <v>63.95</v>
+        <v>66.63499999999999</v>
       </c>
       <c r="F32">
-        <v>80.55</v>
+        <v>83.235</v>
       </c>
       <c r="G32">
         <v>70</v>
@@ -3911,28 +3911,28 @@
         <v>28.732</v>
       </c>
       <c r="M32">
-        <v>4.373865</v>
+        <v>4.5196605</v>
       </c>
       <c r="N32">
-        <v>24.358135</v>
+        <v>24.2123395</v>
       </c>
       <c r="O32">
-        <v>4.384464299999999</v>
+        <v>4.35822111</v>
       </c>
       <c r="P32">
-        <v>19.9736707</v>
+        <v>19.85411839</v>
       </c>
       <c r="Q32">
-        <v>19.6416707</v>
+        <v>19.52211839</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1397766549768183</v>
+        <v>0.1409572300462332</v>
       </c>
       <c r="T32">
-        <v>1.584581411802427</v>
+        <v>1.604487603512419</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.569018476793407</v>
+        <v>6.357114654961363</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1110635487319009</v>
+        <v>0.1109256389800291</v>
       </c>
       <c r="C33">
-        <v>192.9699745060351</v>
+        <v>190.5685612613627</v>
       </c>
       <c r="D33">
-        <v>206.2049745060351</v>
+        <v>206.4885612613627</v>
       </c>
       <c r="E33">
-        <v>66.63499999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="F33">
-        <v>83.235</v>
+        <v>85.92</v>
       </c>
       <c r="G33">
         <v>70</v>
@@ -3993,28 +3993,28 @@
         <v>28.732</v>
       </c>
       <c r="M33">
-        <v>4.5196605</v>
+        <v>4.665456</v>
       </c>
       <c r="N33">
-        <v>24.2123395</v>
+        <v>24.066544</v>
       </c>
       <c r="O33">
-        <v>4.35822111</v>
+        <v>4.33197792</v>
       </c>
       <c r="P33">
-        <v>19.85411839</v>
+        <v>19.73456608</v>
       </c>
       <c r="Q33">
-        <v>19.52211839</v>
+        <v>19.40256608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1409572300462332</v>
+        <v>0.1421725279118074</v>
       </c>
       <c r="T33">
-        <v>1.604487603512419</v>
+        <v>1.624979271449175</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.357114654961363</v>
+        <v>6.15845482199382</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1109256389800291</v>
+        <v>0.1110583292281572</v>
       </c>
       <c r="C34">
-        <v>190.5685612613627</v>
+        <v>187.6106932992907</v>
       </c>
       <c r="D34">
-        <v>206.4885612613627</v>
+        <v>206.2156932992907</v>
       </c>
       <c r="E34">
-        <v>69.31999999999999</v>
+        <v>72.005</v>
       </c>
       <c r="F34">
-        <v>85.92</v>
+        <v>88.605</v>
       </c>
       <c r="G34">
         <v>70</v>
@@ -4075,45 +4075,45 @@
         <v>28.732</v>
       </c>
       <c r="M34">
-        <v>4.665456</v>
+        <v>4.8998565</v>
       </c>
       <c r="N34">
-        <v>24.066544</v>
+        <v>23.8321435</v>
       </c>
       <c r="O34">
-        <v>4.33197792</v>
+        <v>4.28978583</v>
       </c>
       <c r="P34">
-        <v>19.73456608</v>
+        <v>19.54235767</v>
       </c>
       <c r="Q34">
-        <v>19.40256608</v>
+        <v>19.21035767</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1421725279118074</v>
+        <v>0.1434241033256077</v>
       </c>
       <c r="T34">
-        <v>1.624979271449175</v>
+        <v>1.646082630966132</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.18</v>
       </c>
       <c r="W34">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.15845482199382</v>
+        <v>5.863845196282789</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1110583292281572</v>
+        <v>0.1109286194762853</v>
       </c>
       <c r="C35">
-        <v>187.6106932992907</v>
+        <v>185.1924241571292</v>
       </c>
       <c r="D35">
-        <v>206.2156932992907</v>
+        <v>206.4824241571292</v>
       </c>
       <c r="E35">
-        <v>72.005</v>
+        <v>74.69</v>
       </c>
       <c r="F35">
-        <v>88.605</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G35">
         <v>70</v>
@@ -4157,28 +4157,28 @@
         <v>28.732</v>
       </c>
       <c r="M35">
-        <v>4.8998565</v>
+        <v>5.048337000000001</v>
       </c>
       <c r="N35">
-        <v>23.8321435</v>
+        <v>23.683663</v>
       </c>
       <c r="O35">
-        <v>4.28978583</v>
+        <v>4.26305934</v>
       </c>
       <c r="P35">
-        <v>19.54235767</v>
+        <v>19.42060366</v>
       </c>
       <c r="Q35">
-        <v>19.21035767</v>
+        <v>19.08860366</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1434241033256077</v>
+        <v>0.1447136052670989</v>
       </c>
       <c r="T35">
-        <v>1.646082630966132</v>
+        <v>1.667825486226028</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.863845196282789</v>
+        <v>5.691379161098</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1109286194762853</v>
+        <v>0.1107989097244134</v>
       </c>
       <c r="C36">
-        <v>185.1924241571292</v>
+        <v>182.7748459177009</v>
       </c>
       <c r="D36">
-        <v>206.4824241571292</v>
+        <v>206.7498459177009</v>
       </c>
       <c r="E36">
-        <v>74.69</v>
+        <v>77.375</v>
       </c>
       <c r="F36">
-        <v>91.29000000000001</v>
+        <v>93.97500000000001</v>
       </c>
       <c r="G36">
         <v>70</v>
@@ -4239,28 +4239,28 @@
         <v>28.732</v>
       </c>
       <c r="M36">
-        <v>5.048337000000001</v>
+        <v>5.196817500000001</v>
       </c>
       <c r="N36">
-        <v>23.683663</v>
+        <v>23.5351825</v>
       </c>
       <c r="O36">
-        <v>4.26305934</v>
+        <v>4.236332849999999</v>
       </c>
       <c r="P36">
-        <v>19.42060366</v>
+        <v>19.29884965</v>
       </c>
       <c r="Q36">
-        <v>19.08860366</v>
+        <v>18.96684965</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1447136052670989</v>
+        <v>0.1460427841914053</v>
       </c>
       <c r="T36">
-        <v>1.667825486226028</v>
+        <v>1.690237352416998</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.691379161098</v>
+        <v>5.528768327923771</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1107989097244134</v>
+        <v>0.1106691999725416</v>
       </c>
       <c r="C37">
-        <v>182.7748459177009</v>
+        <v>180.3579612689152</v>
       </c>
       <c r="D37">
-        <v>206.7498459177009</v>
+        <v>207.0179612689152</v>
       </c>
       <c r="E37">
-        <v>77.375</v>
+        <v>80.06</v>
       </c>
       <c r="F37">
-        <v>93.97500000000001</v>
+        <v>96.66000000000001</v>
       </c>
       <c r="G37">
         <v>70</v>
@@ -4321,28 +4321,28 @@
         <v>28.732</v>
       </c>
       <c r="M37">
-        <v>5.196817500000001</v>
+        <v>5.345298000000001</v>
       </c>
       <c r="N37">
-        <v>23.5351825</v>
+        <v>23.386702</v>
       </c>
       <c r="O37">
-        <v>4.236332849999999</v>
+        <v>4.20960636</v>
       </c>
       <c r="P37">
-        <v>19.29884965</v>
+        <v>19.17709564</v>
       </c>
       <c r="Q37">
-        <v>18.96684965</v>
+        <v>18.84509564</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1460427841914053</v>
+        <v>0.1474134999570962</v>
       </c>
       <c r="T37">
-        <v>1.690237352416998</v>
+        <v>1.713349589426435</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.528768327923771</v>
+        <v>5.37519142992589</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1106691999725416</v>
+        <v>0.1105394902206697</v>
       </c>
       <c r="C38">
-        <v>180.3579612689152</v>
+        <v>177.9417729126428</v>
       </c>
       <c r="D38">
-        <v>207.0179612689152</v>
+        <v>207.2867729126428</v>
       </c>
       <c r="E38">
-        <v>80.06</v>
+        <v>82.745</v>
       </c>
       <c r="F38">
-        <v>96.66</v>
+        <v>99.345</v>
       </c>
       <c r="G38">
         <v>70</v>
@@ -4403,28 +4403,28 @@
         <v>28.732</v>
       </c>
       <c r="M38">
-        <v>5.345298</v>
+        <v>5.4937785</v>
       </c>
       <c r="N38">
-        <v>23.386702</v>
+        <v>23.2382215</v>
       </c>
       <c r="O38">
-        <v>4.20960636</v>
+        <v>4.18287987</v>
       </c>
       <c r="P38">
-        <v>19.17709564</v>
+        <v>19.05534163</v>
       </c>
       <c r="Q38">
-        <v>18.84509564</v>
+        <v>18.72334163</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1474134999570962</v>
+        <v>0.1488277305089995</v>
       </c>
       <c r="T38">
-        <v>1.713349589426435</v>
+        <v>1.737195548245696</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.37519142992589</v>
+        <v>5.229915985873839</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1105394902206697</v>
+        <v>0.1104097804687978</v>
       </c>
       <c r="C39">
-        <v>177.9417729126428</v>
+        <v>175.5262835648059</v>
       </c>
       <c r="D39">
-        <v>207.2867729126428</v>
+        <v>207.5562835648059</v>
       </c>
       <c r="E39">
-        <v>82.745</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="F39">
-        <v>99.345</v>
+        <v>102.03</v>
       </c>
       <c r="G39">
         <v>70</v>
@@ -4485,28 +4485,28 @@
         <v>28.732</v>
       </c>
       <c r="M39">
-        <v>5.4937785</v>
+        <v>5.642259</v>
       </c>
       <c r="N39">
-        <v>23.2382215</v>
+        <v>23.089741</v>
       </c>
       <c r="O39">
-        <v>4.18287987</v>
+        <v>4.15615338</v>
       </c>
       <c r="P39">
-        <v>19.05534163</v>
+        <v>18.93358762</v>
       </c>
       <c r="Q39">
-        <v>18.72334163</v>
+        <v>18.60158762</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1488277305089995</v>
+        <v>0.1502875814012868</v>
       </c>
       <c r="T39">
-        <v>1.737195548245696</v>
+        <v>1.761810731542997</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.229915985873839</v>
+        <v>5.092286617824527</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1104097804687978</v>
+        <v>0.1102800707169259</v>
       </c>
       <c r="C40">
-        <v>175.5262835648059</v>
+        <v>173.1114959554698</v>
       </c>
       <c r="D40">
-        <v>207.5562835648059</v>
+        <v>207.8264959554698</v>
       </c>
       <c r="E40">
-        <v>85.43000000000001</v>
+        <v>88.11500000000001</v>
       </c>
       <c r="F40">
-        <v>102.03</v>
+        <v>104.715</v>
       </c>
       <c r="G40">
         <v>70</v>
@@ -4567,28 +4567,28 @@
         <v>28.732</v>
       </c>
       <c r="M40">
-        <v>5.642259</v>
+        <v>5.790739500000001</v>
       </c>
       <c r="N40">
-        <v>23.089741</v>
+        <v>22.9412605</v>
       </c>
       <c r="O40">
-        <v>4.15615338</v>
+        <v>4.12942689</v>
       </c>
       <c r="P40">
-        <v>18.93358762</v>
+        <v>18.81183361</v>
       </c>
       <c r="Q40">
-        <v>18.60158762</v>
+        <v>18.47983361</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1502875814012868</v>
+        <v>0.1517952962572557</v>
       </c>
       <c r="T40">
-        <v>1.761810731542997</v>
+        <v>1.787232970030374</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.092286617824527</v>
+        <v>4.961715166085436</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1102800707169259</v>
+        <v>0.1101503609650541</v>
       </c>
       <c r="C41">
-        <v>173.1114959554698</v>
+        <v>170.6974128289351</v>
       </c>
       <c r="D41">
-        <v>207.8264959554698</v>
+        <v>208.0974128289352</v>
       </c>
       <c r="E41">
-        <v>88.11500000000001</v>
+        <v>90.80000000000001</v>
       </c>
       <c r="F41">
-        <v>104.715</v>
+        <v>107.4</v>
       </c>
       <c r="G41">
         <v>70</v>
@@ -4649,28 +4649,28 @@
         <v>28.732</v>
       </c>
       <c r="M41">
-        <v>5.790739500000001</v>
+        <v>5.939220000000001</v>
       </c>
       <c r="N41">
-        <v>22.9412605</v>
+        <v>22.79278</v>
       </c>
       <c r="O41">
-        <v>4.12942689</v>
+        <v>4.1027004</v>
       </c>
       <c r="P41">
-        <v>18.81183361</v>
+        <v>18.6900796</v>
       </c>
       <c r="Q41">
-        <v>18.47983361</v>
+        <v>18.3580796</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1517952962572557</v>
+        <v>0.1533532682750901</v>
       </c>
       <c r="T41">
-        <v>1.787232970030374</v>
+        <v>1.81350261646733</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.961715166085436</v>
+        <v>4.837672286933301</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1101503609650541</v>
+        <v>0.1100206512131822</v>
       </c>
       <c r="C42">
-        <v>170.6974128289351</v>
+        <v>168.2840369438311</v>
       </c>
       <c r="D42">
-        <v>208.0974128289352</v>
+        <v>208.3690369438311</v>
       </c>
       <c r="E42">
-        <v>90.80000000000001</v>
+        <v>93.48500000000001</v>
       </c>
       <c r="F42">
-        <v>107.4</v>
+        <v>110.085</v>
       </c>
       <c r="G42">
         <v>70</v>
@@ -4731,28 +4731,28 @@
         <v>28.732</v>
       </c>
       <c r="M42">
-        <v>5.939220000000001</v>
+        <v>6.0877005</v>
       </c>
       <c r="N42">
-        <v>22.79278</v>
+        <v>22.6442995</v>
       </c>
       <c r="O42">
-        <v>4.1027004</v>
+        <v>4.07597391</v>
       </c>
       <c r="P42">
-        <v>18.6900796</v>
+        <v>18.56832559</v>
       </c>
       <c r="Q42">
-        <v>18.3580796</v>
+        <v>18.23632559</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1533532682750901</v>
+        <v>0.1549640529036986</v>
       </c>
       <c r="T42">
-        <v>1.81350261646733</v>
+        <v>1.840662759393675</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.837672286933301</v>
+        <v>4.719680279934927</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1100206512131822</v>
+        <v>0.1098909414613103</v>
       </c>
       <c r="C43">
-        <v>168.2840369438311</v>
+        <v>165.8713710732083</v>
       </c>
       <c r="D43">
-        <v>208.3690369438311</v>
+        <v>208.6413710732083</v>
       </c>
       <c r="E43">
-        <v>93.48500000000001</v>
+        <v>96.17000000000002</v>
       </c>
       <c r="F43">
-        <v>110.085</v>
+        <v>112.77</v>
       </c>
       <c r="G43">
         <v>70</v>
@@ -4813,28 +4813,28 @@
         <v>28.732</v>
       </c>
       <c r="M43">
-        <v>6.0877005</v>
+        <v>6.236181000000001</v>
       </c>
       <c r="N43">
-        <v>22.6442995</v>
+        <v>22.495819</v>
       </c>
       <c r="O43">
-        <v>4.07597391</v>
+        <v>4.049247419999999</v>
       </c>
       <c r="P43">
-        <v>18.56832559</v>
+        <v>18.44657158</v>
       </c>
       <c r="Q43">
-        <v>18.23632559</v>
+        <v>18.11457158</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1549640529036986</v>
+        <v>0.1566303818298454</v>
       </c>
       <c r="T43">
-        <v>1.840662759393675</v>
+        <v>1.868759458972652</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.719680279934927</v>
+        <v>4.607306939936477</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1098909414613103</v>
+        <v>0.1097612317094385</v>
       </c>
       <c r="C44">
-        <v>165.8713710732083</v>
+        <v>163.459418004634</v>
       </c>
       <c r="D44">
-        <v>208.6413710732083</v>
+        <v>208.914418004634</v>
       </c>
       <c r="E44">
-        <v>96.16999999999999</v>
+        <v>98.85499999999999</v>
       </c>
       <c r="F44">
-        <v>112.77</v>
+        <v>115.455</v>
       </c>
       <c r="G44">
         <v>70</v>
@@ -4895,28 +4895,28 @@
         <v>28.732</v>
       </c>
       <c r="M44">
-        <v>6.236181</v>
+        <v>6.3846615</v>
       </c>
       <c r="N44">
-        <v>22.495819</v>
+        <v>22.3473385</v>
       </c>
       <c r="O44">
-        <v>4.049247419999999</v>
+        <v>4.02252093</v>
       </c>
       <c r="P44">
-        <v>18.44657158</v>
+        <v>18.32481757</v>
       </c>
       <c r="Q44">
-        <v>18.11457158</v>
+        <v>17.99281757</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1566303818298454</v>
+        <v>0.1583551784376113</v>
       </c>
       <c r="T44">
-        <v>1.868759458972652</v>
+        <v>1.897842007659663</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.607306939936477</v>
+        <v>4.500160266914699</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1097612317094385</v>
+        <v>0.1105335219575666</v>
       </c>
       <c r="C45">
-        <v>163.459418004634</v>
+        <v>159.1591583948505</v>
       </c>
       <c r="D45">
-        <v>208.914418004634</v>
+        <v>207.2991583948504</v>
       </c>
       <c r="E45">
-        <v>98.85499999999999</v>
+        <v>101.54</v>
       </c>
       <c r="F45">
-        <v>115.455</v>
+        <v>118.14</v>
       </c>
       <c r="G45">
         <v>70</v>
@@ -4977,45 +4977,45 @@
         <v>28.732</v>
       </c>
       <c r="M45">
-        <v>6.3846615</v>
+        <v>6.828492000000001</v>
       </c>
       <c r="N45">
-        <v>22.3473385</v>
+        <v>21.903508</v>
       </c>
       <c r="O45">
-        <v>4.02252093</v>
+        <v>3.94263144</v>
       </c>
       <c r="P45">
-        <v>18.32481757</v>
+        <v>17.96087656</v>
       </c>
       <c r="Q45">
-        <v>17.99281757</v>
+        <v>17.62887656</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1583551784376113</v>
+        <v>0.1601415749242261</v>
       </c>
       <c r="T45">
-        <v>1.897842007659663</v>
+        <v>1.927963218799782</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.18</v>
       </c>
       <c r="W45">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.500160266914699</v>
+        <v>4.207664005464164</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1105335219575666</v>
+        <v>0.1104243122056947</v>
       </c>
       <c r="C46">
-        <v>159.1591583948505</v>
+        <v>156.7010546976593</v>
       </c>
       <c r="D46">
-        <v>207.2991583948504</v>
+        <v>207.5260546976594</v>
       </c>
       <c r="E46">
-        <v>101.54</v>
+        <v>104.225</v>
       </c>
       <c r="F46">
-        <v>118.14</v>
+        <v>120.825</v>
       </c>
       <c r="G46">
         <v>70</v>
@@ -5059,28 +5059,28 @@
         <v>28.732</v>
       </c>
       <c r="M46">
-        <v>6.828492000000001</v>
+        <v>6.983685</v>
       </c>
       <c r="N46">
-        <v>21.903508</v>
+        <v>21.748315</v>
       </c>
       <c r="O46">
-        <v>3.94263144</v>
+        <v>3.914696699999999</v>
       </c>
       <c r="P46">
-        <v>17.96087656</v>
+        <v>17.8336183</v>
       </c>
       <c r="Q46">
-        <v>17.62887656</v>
+        <v>17.5016183</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1601415749242261</v>
+        <v>0.1619929312830813</v>
       </c>
       <c r="T46">
-        <v>1.927963218799782</v>
+        <v>1.959179746708632</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.207664005464164</v>
+        <v>4.114160360898293</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1104243122056947</v>
+        <v>0.1103151024538229</v>
       </c>
       <c r="C47">
-        <v>156.7010546976593</v>
+        <v>154.2434482368601</v>
       </c>
       <c r="D47">
-        <v>207.5260546976594</v>
+        <v>207.7534482368601</v>
       </c>
       <c r="E47">
-        <v>104.225</v>
+        <v>106.91</v>
       </c>
       <c r="F47">
-        <v>120.825</v>
+        <v>123.51</v>
       </c>
       <c r="G47">
         <v>70</v>
@@ -5141,28 +5141,28 @@
         <v>28.732</v>
       </c>
       <c r="M47">
-        <v>6.983685</v>
+        <v>7.138878000000001</v>
       </c>
       <c r="N47">
-        <v>21.748315</v>
+        <v>21.593122</v>
       </c>
       <c r="O47">
-        <v>3.914696699999999</v>
+        <v>3.886761959999999</v>
       </c>
       <c r="P47">
-        <v>17.8336183</v>
+        <v>17.70636004</v>
       </c>
       <c r="Q47">
-        <v>17.5016183</v>
+        <v>17.37436004</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1619929312830813</v>
+        <v>0.1639128563959682</v>
       </c>
       <c r="T47">
-        <v>1.959179746708632</v>
+        <v>1.99155244231781</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.114160360898293</v>
+        <v>4.024722092183113</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1103151024538229</v>
+        <v>0.111554792701951</v>
       </c>
       <c r="C48">
-        <v>154.2434482368601</v>
+        <v>149.0061173435336</v>
       </c>
       <c r="D48">
-        <v>207.7534482368601</v>
+        <v>205.2011173435336</v>
       </c>
       <c r="E48">
-        <v>106.91</v>
+        <v>109.595</v>
       </c>
       <c r="F48">
-        <v>123.51</v>
+        <v>126.195</v>
       </c>
       <c r="G48">
         <v>70</v>
@@ -5223,45 +5223,45 @@
         <v>28.732</v>
       </c>
       <c r="M48">
-        <v>7.138878000000001</v>
+        <v>7.7357535</v>
       </c>
       <c r="N48">
-        <v>21.593122</v>
+        <v>20.9962465</v>
       </c>
       <c r="O48">
-        <v>3.886761959999999</v>
+        <v>3.779324369999999</v>
       </c>
       <c r="P48">
-        <v>17.70636004</v>
+        <v>17.21692213</v>
       </c>
       <c r="Q48">
-        <v>17.37436004</v>
+        <v>16.88492213</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1639128563959682</v>
+        <v>0.165905231513115</v>
       </c>
       <c r="T48">
-        <v>1.99155244231781</v>
+        <v>2.025146749082052</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.18</v>
       </c>
       <c r="W48">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.024722092183113</v>
+        <v>3.714182464578272</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.111554792701951</v>
+        <v>0.1114742829500791</v>
       </c>
       <c r="C49">
-        <v>149.0061173435336</v>
+        <v>146.4849688366338</v>
       </c>
       <c r="D49">
-        <v>205.2011173435336</v>
+        <v>205.3649688366339</v>
       </c>
       <c r="E49">
-        <v>109.595</v>
+        <v>112.28</v>
       </c>
       <c r="F49">
-        <v>126.195</v>
+        <v>128.88</v>
       </c>
       <c r="G49">
         <v>70</v>
@@ -5305,28 +5305,28 @@
         <v>28.732</v>
       </c>
       <c r="M49">
-        <v>7.7357535</v>
+        <v>7.900344000000001</v>
       </c>
       <c r="N49">
-        <v>20.9962465</v>
+        <v>20.831656</v>
       </c>
       <c r="O49">
-        <v>3.779324369999999</v>
+        <v>3.749698079999999</v>
       </c>
       <c r="P49">
-        <v>17.21692213</v>
+        <v>17.08195792</v>
       </c>
       <c r="Q49">
-        <v>16.88492213</v>
+        <v>16.74995792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.165905231513115</v>
+        <v>0.1679742364424598</v>
       </c>
       <c r="T49">
-        <v>2.025146749082052</v>
+        <v>2.060033144567995</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.714182464578272</v>
+        <v>3.636803663232892</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1114742829500791</v>
+        <v>0.1113937731982072</v>
       </c>
       <c r="C50">
-        <v>146.4849688366339</v>
+        <v>143.9640822071219</v>
       </c>
       <c r="D50">
-        <v>205.3649688366339</v>
+        <v>205.5290822071219</v>
       </c>
       <c r="E50">
-        <v>112.28</v>
+        <v>114.965</v>
       </c>
       <c r="F50">
-        <v>128.88</v>
+        <v>131.565</v>
       </c>
       <c r="G50">
         <v>70</v>
@@ -5387,28 +5387,28 @@
         <v>28.732</v>
       </c>
       <c r="M50">
-        <v>7.900344</v>
+        <v>8.0649345</v>
       </c>
       <c r="N50">
-        <v>20.831656</v>
+        <v>20.6670655</v>
       </c>
       <c r="O50">
-        <v>3.749698079999999</v>
+        <v>3.72007179</v>
       </c>
       <c r="P50">
-        <v>17.08195792</v>
+        <v>16.94699371</v>
       </c>
       <c r="Q50">
-        <v>16.74995792</v>
+        <v>16.61499371</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1679742364424598</v>
+        <v>0.1701243788200142</v>
       </c>
       <c r="T50">
-        <v>2.060033144567995</v>
+        <v>2.096287633994563</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.636803663232892</v>
+        <v>3.562583180309772</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1113937731982072</v>
+        <v>0.1124612634463353</v>
       </c>
       <c r="C51">
-        <v>143.9640822071219</v>
+        <v>139.1241737235243</v>
       </c>
       <c r="D51">
-        <v>205.5290822071219</v>
+        <v>203.3741737235243</v>
       </c>
       <c r="E51">
-        <v>114.965</v>
+        <v>117.65</v>
       </c>
       <c r="F51">
-        <v>131.565</v>
+        <v>134.25</v>
       </c>
       <c r="G51">
         <v>70</v>
@@ -5469,45 +5469,45 @@
         <v>28.732</v>
       </c>
       <c r="M51">
-        <v>8.0649345</v>
+        <v>8.605425</v>
       </c>
       <c r="N51">
-        <v>20.6670655</v>
+        <v>20.126575</v>
       </c>
       <c r="O51">
-        <v>3.72007179</v>
+        <v>3.6227835</v>
       </c>
       <c r="P51">
-        <v>16.94699371</v>
+        <v>16.5037915</v>
       </c>
       <c r="Q51">
-        <v>16.61499371</v>
+        <v>16.1717915</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1701243788200142</v>
+        <v>0.1723605268926707</v>
       </c>
       <c r="T51">
-        <v>2.096287633994563</v>
+        <v>2.133992302998195</v>
       </c>
       <c r="U51">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.18</v>
       </c>
       <c r="W51">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.562583180309772</v>
+        <v>3.338824055755526</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1124612634463353</v>
+        <v>0.1124037136944635</v>
       </c>
       <c r="C52">
-        <v>139.1241737235243</v>
+        <v>136.5541945383705</v>
       </c>
       <c r="D52">
-        <v>203.3741737235243</v>
+        <v>203.4891945383705</v>
       </c>
       <c r="E52">
-        <v>117.65</v>
+        <v>120.335</v>
       </c>
       <c r="F52">
-        <v>134.25</v>
+        <v>136.935</v>
       </c>
       <c r="G52">
         <v>70</v>
@@ -5551,28 +5551,28 @@
         <v>28.732</v>
       </c>
       <c r="M52">
-        <v>8.605425</v>
+        <v>8.777533500000001</v>
       </c>
       <c r="N52">
-        <v>20.126575</v>
+        <v>19.9544665</v>
       </c>
       <c r="O52">
-        <v>3.6227835</v>
+        <v>3.59180397</v>
       </c>
       <c r="P52">
-        <v>16.5037915</v>
+        <v>16.36266253</v>
       </c>
       <c r="Q52">
-        <v>16.1717915</v>
+        <v>16.03066253</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1723605268926707</v>
+        <v>0.1746879463152316</v>
       </c>
       <c r="T52">
-        <v>2.133992302998195</v>
+        <v>2.173235938083607</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.338824055755526</v>
+        <v>3.273356917407379</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1124037136944635</v>
+        <v>0.1123461639425916</v>
       </c>
       <c r="C53">
-        <v>136.5541945383705</v>
+        <v>133.9843455297687</v>
       </c>
       <c r="D53">
-        <v>203.4891945383705</v>
+        <v>203.6043455297688</v>
       </c>
       <c r="E53">
-        <v>120.335</v>
+        <v>123.02</v>
       </c>
       <c r="F53">
-        <v>136.935</v>
+        <v>139.62</v>
       </c>
       <c r="G53">
         <v>70</v>
@@ -5633,28 +5633,28 @@
         <v>28.732</v>
       </c>
       <c r="M53">
-        <v>8.777533500000001</v>
+        <v>8.949642000000001</v>
       </c>
       <c r="N53">
-        <v>19.9544665</v>
+        <v>19.782358</v>
       </c>
       <c r="O53">
-        <v>3.59180397</v>
+        <v>3.56082444</v>
       </c>
       <c r="P53">
-        <v>16.36266253</v>
+        <v>16.22153356</v>
       </c>
       <c r="Q53">
-        <v>16.03066253</v>
+        <v>15.88953356</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1746879463152316</v>
+        <v>0.1771123415470659</v>
       </c>
       <c r="T53">
-        <v>2.173235938083607</v>
+        <v>2.214114724630911</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.273356917407379</v>
+        <v>3.210407745918775</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1123461639425916</v>
+        <v>0.1122886141907198</v>
       </c>
       <c r="C54">
-        <v>133.9843455297687</v>
+        <v>131.4146269188382</v>
       </c>
       <c r="D54">
-        <v>203.6043455297688</v>
+        <v>203.7196269188382</v>
       </c>
       <c r="E54">
-        <v>123.02</v>
+        <v>125.705</v>
       </c>
       <c r="F54">
-        <v>139.62</v>
+        <v>142.305</v>
       </c>
       <c r="G54">
         <v>70</v>
@@ -5715,28 +5715,28 @@
         <v>28.732</v>
       </c>
       <c r="M54">
-        <v>8.949642000000001</v>
+        <v>9.121750500000001</v>
       </c>
       <c r="N54">
-        <v>19.782358</v>
+        <v>19.6102495</v>
       </c>
       <c r="O54">
-        <v>3.56082444</v>
+        <v>3.52984491</v>
       </c>
       <c r="P54">
-        <v>16.22153356</v>
+        <v>16.08040459</v>
       </c>
       <c r="Q54">
-        <v>15.88953356</v>
+        <v>15.74840459</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1771123415470659</v>
+        <v>0.1796399025334463</v>
       </c>
       <c r="T54">
-        <v>2.214114724630911</v>
+        <v>2.256733034010015</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.210407745918775</v>
+        <v>3.149834014863704</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1122886141907198</v>
+        <v>0.1122310644388479</v>
       </c>
       <c r="C55">
-        <v>131.4146269188382</v>
+        <v>128.8450389271987</v>
       </c>
       <c r="D55">
-        <v>203.7196269188382</v>
+        <v>203.8350389271988</v>
       </c>
       <c r="E55">
-        <v>125.705</v>
+        <v>128.39</v>
       </c>
       <c r="F55">
-        <v>142.305</v>
+        <v>144.99</v>
       </c>
       <c r="G55">
         <v>70</v>
@@ -5797,28 +5797,28 @@
         <v>28.732</v>
       </c>
       <c r="M55">
-        <v>9.121750500000001</v>
+        <v>9.293859000000001</v>
       </c>
       <c r="N55">
-        <v>19.6102495</v>
+        <v>19.438141</v>
       </c>
       <c r="O55">
-        <v>3.52984491</v>
+        <v>3.498865379999999</v>
       </c>
       <c r="P55">
-        <v>16.08040459</v>
+        <v>15.93927562</v>
       </c>
       <c r="Q55">
-        <v>15.74840459</v>
+        <v>15.60727562</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1796399025334463</v>
+        <v>0.1822773574757562</v>
       </c>
       <c r="T55">
-        <v>2.256733034010015</v>
+        <v>2.301204313362124</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.149834014863704</v>
+        <v>3.091503755329191</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1122310644388479</v>
+        <v>0.112173514686976</v>
       </c>
       <c r="C56">
-        <v>128.8450389271987</v>
+        <v>126.2755817769732</v>
       </c>
       <c r="D56">
-        <v>203.8350389271988</v>
+        <v>203.9505817769732</v>
       </c>
       <c r="E56">
-        <v>128.39</v>
+        <v>131.075</v>
       </c>
       <c r="F56">
-        <v>144.99</v>
+        <v>147.675</v>
       </c>
       <c r="G56">
         <v>70</v>
@@ -5879,28 +5879,28 @@
         <v>28.732</v>
       </c>
       <c r="M56">
-        <v>9.293859000000001</v>
+        <v>9.465967500000001</v>
       </c>
       <c r="N56">
-        <v>19.438141</v>
+        <v>19.2660325</v>
       </c>
       <c r="O56">
-        <v>3.498865379999999</v>
+        <v>3.46788585</v>
       </c>
       <c r="P56">
-        <v>15.93927562</v>
+        <v>15.79814665</v>
       </c>
       <c r="Q56">
-        <v>15.60727562</v>
+        <v>15.46614665</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1822773574757562</v>
+        <v>0.1850320326377244</v>
       </c>
       <c r="T56">
-        <v>2.301204313362124</v>
+        <v>2.347652094018771</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.091503755329191</v>
+        <v>3.035294596141387</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.112173514686976</v>
+        <v>0.1156977249351041</v>
       </c>
       <c r="C57">
-        <v>126.2755817769732</v>
+        <v>116.7485048591225</v>
       </c>
       <c r="D57">
-        <v>203.9505817769732</v>
+        <v>197.1085048591225</v>
       </c>
       <c r="E57">
-        <v>131.075</v>
+        <v>133.76</v>
       </c>
       <c r="F57">
-        <v>147.675</v>
+        <v>150.36</v>
       </c>
       <c r="G57">
         <v>70</v>
@@ -5961,45 +5961,45 @@
         <v>28.732</v>
       </c>
       <c r="M57">
-        <v>9.465967500000001</v>
+        <v>10.810884</v>
       </c>
       <c r="N57">
-        <v>19.2660325</v>
+        <v>17.921116</v>
       </c>
       <c r="O57">
-        <v>3.46788585</v>
+        <v>3.22580088</v>
       </c>
       <c r="P57">
-        <v>15.79814665</v>
+        <v>14.69531512</v>
       </c>
       <c r="Q57">
-        <v>15.46614665</v>
+        <v>14.36331512</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1850320326377244</v>
+        <v>0.1879119203070548</v>
       </c>
       <c r="T57">
-        <v>2.347652094018771</v>
+        <v>2.396211137432538</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.18</v>
       </c>
       <c r="W57">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.035294596141387</v>
+        <v>2.657692007425109</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1156977249351041</v>
+        <v>0.1157041351832322</v>
       </c>
       <c r="C58">
-        <v>116.7485048591225</v>
+        <v>114.0514779259439</v>
       </c>
       <c r="D58">
-        <v>197.1085048591225</v>
+        <v>197.0964779259439</v>
       </c>
       <c r="E58">
-        <v>133.76</v>
+        <v>136.445</v>
       </c>
       <c r="F58">
-        <v>150.36</v>
+        <v>153.045</v>
       </c>
       <c r="G58">
         <v>70</v>
@@ -6043,28 +6043,28 @@
         <v>28.732</v>
       </c>
       <c r="M58">
-        <v>10.810884</v>
+        <v>11.0039355</v>
       </c>
       <c r="N58">
-        <v>17.921116</v>
+        <v>17.7280645</v>
       </c>
       <c r="O58">
-        <v>3.22580088</v>
+        <v>3.191051609999999</v>
       </c>
       <c r="P58">
-        <v>14.69531512</v>
+        <v>14.53701289</v>
       </c>
       <c r="Q58">
-        <v>14.36331512</v>
+        <v>14.20501289</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1879119203070548</v>
+        <v>0.190925756240075</v>
       </c>
       <c r="T58">
-        <v>2.396211137432538</v>
+        <v>2.447028741005086</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.657692007425109</v>
+        <v>2.611065831856247</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1157041351832322</v>
+        <v>0.1157105454313604</v>
       </c>
       <c r="C59">
-        <v>114.0514779259439</v>
+        <v>111.3544524603661</v>
       </c>
       <c r="D59">
-        <v>197.0964779259439</v>
+        <v>197.0844524603661</v>
       </c>
       <c r="E59">
-        <v>136.445</v>
+        <v>139.13</v>
       </c>
       <c r="F59">
-        <v>153.045</v>
+        <v>155.73</v>
       </c>
       <c r="G59">
         <v>70</v>
@@ -6125,28 +6125,28 @@
         <v>28.732</v>
       </c>
       <c r="M59">
-        <v>11.0039355</v>
+        <v>11.196987</v>
       </c>
       <c r="N59">
-        <v>17.7280645</v>
+        <v>17.535013</v>
       </c>
       <c r="O59">
-        <v>3.191051609999999</v>
+        <v>3.15630234</v>
       </c>
       <c r="P59">
-        <v>14.53701289</v>
+        <v>14.37871066</v>
       </c>
       <c r="Q59">
-        <v>14.20501289</v>
+        <v>14.04671066</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.190925756240075</v>
+        <v>0.1940831081699057</v>
       </c>
       <c r="T59">
-        <v>2.447028741005086</v>
+        <v>2.50026623046204</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.611065831856247</v>
+        <v>2.566047455444934</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1157105454313604</v>
+        <v>0.1157169556794885</v>
       </c>
       <c r="C60">
-        <v>111.3544524603661</v>
+        <v>108.6574284621205</v>
       </c>
       <c r="D60">
-        <v>197.0844524603661</v>
+        <v>197.0724284621205</v>
       </c>
       <c r="E60">
-        <v>139.13</v>
+        <v>141.815</v>
       </c>
       <c r="F60">
-        <v>155.73</v>
+        <v>158.415</v>
       </c>
       <c r="G60">
         <v>70</v>
@@ -6207,28 +6207,28 @@
         <v>28.732</v>
       </c>
       <c r="M60">
-        <v>11.196987</v>
+        <v>11.3900385</v>
       </c>
       <c r="N60">
-        <v>17.535013</v>
+        <v>17.3419615</v>
       </c>
       <c r="O60">
-        <v>3.15630234</v>
+        <v>3.121553069999999</v>
       </c>
       <c r="P60">
-        <v>14.37871066</v>
+        <v>14.22040843</v>
       </c>
       <c r="Q60">
-        <v>14.04671066</v>
+        <v>13.88840843</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1940831081699056</v>
+        <v>0.1973944772670451</v>
       </c>
       <c r="T60">
-        <v>2.50026623046204</v>
+        <v>2.556100670624211</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.566047455444934</v>
+        <v>2.522555125691629</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1157169556794885</v>
+        <v>0.1176421659276166</v>
       </c>
       <c r="C61">
-        <v>108.6574284621205</v>
+        <v>102.4264171257035</v>
       </c>
       <c r="D61">
-        <v>197.0724284621205</v>
+        <v>193.5264171257034</v>
       </c>
       <c r="E61">
-        <v>141.815</v>
+        <v>144.5</v>
       </c>
       <c r="F61">
-        <v>158.415</v>
+        <v>161.1</v>
       </c>
       <c r="G61">
         <v>70</v>
@@ -6289,45 +6289,45 @@
         <v>28.732</v>
       </c>
       <c r="M61">
-        <v>11.3900385</v>
+        <v>12.21138</v>
       </c>
       <c r="N61">
-        <v>17.3419615</v>
+        <v>16.52062</v>
       </c>
       <c r="O61">
-        <v>3.121553069999999</v>
+        <v>2.9737116</v>
       </c>
       <c r="P61">
-        <v>14.22040843</v>
+        <v>13.5469084</v>
       </c>
       <c r="Q61">
-        <v>13.88840843</v>
+        <v>13.2149084</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1973944772670451</v>
+        <v>0.2008714148190416</v>
       </c>
       <c r="T61">
-        <v>2.556100670624211</v>
+        <v>2.614726832794491</v>
       </c>
       <c r="U61">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.18</v>
       </c>
       <c r="W61">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.522555125691629</v>
+        <v>2.352887224867296</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1176421659276166</v>
+        <v>0.1176805561757448</v>
       </c>
       <c r="C62">
-        <v>102.4264171257035</v>
+        <v>99.67200402203369</v>
       </c>
       <c r="D62">
-        <v>193.5264171257034</v>
+        <v>193.4570040220337</v>
       </c>
       <c r="E62">
-        <v>144.5</v>
+        <v>147.185</v>
       </c>
       <c r="F62">
-        <v>161.1</v>
+        <v>163.785</v>
       </c>
       <c r="G62">
         <v>70</v>
@@ -6371,28 +6371,28 @@
         <v>28.732</v>
       </c>
       <c r="M62">
-        <v>12.21138</v>
+        <v>12.414903</v>
       </c>
       <c r="N62">
-        <v>16.52062</v>
+        <v>16.317097</v>
       </c>
       <c r="O62">
-        <v>2.9737116</v>
+        <v>2.937077459999999</v>
       </c>
       <c r="P62">
-        <v>13.5469084</v>
+        <v>13.38001954</v>
       </c>
       <c r="Q62">
-        <v>13.2149084</v>
+        <v>13.04801954</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2008714148190416</v>
+        <v>0.204526656860884</v>
       </c>
       <c r="T62">
-        <v>2.614726832794491</v>
+        <v>2.676359464819658</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.352887224867296</v>
+        <v>2.31431530314816</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1176805561757448</v>
+        <v>0.1177189464238729</v>
       </c>
       <c r="C63">
-        <v>99.67200402203369</v>
+        <v>96.91764069401202</v>
       </c>
       <c r="D63">
-        <v>193.4570040220337</v>
+        <v>193.387640694012</v>
       </c>
       <c r="E63">
-        <v>147.185</v>
+        <v>149.87</v>
       </c>
       <c r="F63">
-        <v>163.785</v>
+        <v>166.47</v>
       </c>
       <c r="G63">
         <v>70</v>
@@ -6453,28 +6453,28 @@
         <v>28.732</v>
       </c>
       <c r="M63">
-        <v>12.414903</v>
+        <v>12.618426</v>
       </c>
       <c r="N63">
-        <v>16.317097</v>
+        <v>16.113574</v>
       </c>
       <c r="O63">
-        <v>2.937077459999999</v>
+        <v>2.90044332</v>
       </c>
       <c r="P63">
-        <v>13.38001954</v>
+        <v>13.21313068</v>
       </c>
       <c r="Q63">
-        <v>13.04801954</v>
+        <v>12.88113068</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.204526656860884</v>
+        <v>0.2083742800628234</v>
       </c>
       <c r="T63">
-        <v>2.676359464819658</v>
+        <v>2.74123591958299</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.31431530314816</v>
+        <v>2.276987636968351</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1177189464238729</v>
+        <v>0.117757336672001</v>
       </c>
       <c r="C64">
-        <v>96.91764069401202</v>
+        <v>94.16332708811709</v>
       </c>
       <c r="D64">
-        <v>193.387640694012</v>
+        <v>193.3183270881171</v>
       </c>
       <c r="E64">
-        <v>149.87</v>
+        <v>152.555</v>
       </c>
       <c r="F64">
-        <v>166.47</v>
+        <v>169.155</v>
       </c>
       <c r="G64">
         <v>70</v>
@@ -6535,28 +6535,28 @@
         <v>28.732</v>
       </c>
       <c r="M64">
-        <v>12.618426</v>
+        <v>12.821949</v>
       </c>
       <c r="N64">
-        <v>16.113574</v>
+        <v>15.910051</v>
       </c>
       <c r="O64">
-        <v>2.90044332</v>
+        <v>2.86380918</v>
       </c>
       <c r="P64">
-        <v>13.21313068</v>
+        <v>13.04624182</v>
       </c>
       <c r="Q64">
-        <v>12.88113068</v>
+        <v>12.71424182</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2083742800628234</v>
+        <v>0.2124298828973001</v>
       </c>
       <c r="T64">
-        <v>2.74123591958299</v>
+        <v>2.809619209738936</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.276987636968351</v>
+        <v>2.240844976064091</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.117757336672001</v>
+        <v>0.1177957269201292</v>
       </c>
       <c r="C65">
-        <v>94.16332708811709</v>
+        <v>91.40906315090402</v>
       </c>
       <c r="D65">
-        <v>193.3183270881171</v>
+        <v>193.249063150904</v>
       </c>
       <c r="E65">
-        <v>152.555</v>
+        <v>155.24</v>
       </c>
       <c r="F65">
-        <v>169.155</v>
+        <v>171.84</v>
       </c>
       <c r="G65">
         <v>70</v>
@@ -6617,28 +6617,28 @@
         <v>28.732</v>
       </c>
       <c r="M65">
-        <v>12.821949</v>
+        <v>13.025472</v>
       </c>
       <c r="N65">
-        <v>15.910051</v>
+        <v>15.706528</v>
       </c>
       <c r="O65">
-        <v>2.86380918</v>
+        <v>2.82717504</v>
       </c>
       <c r="P65">
-        <v>13.04624182</v>
+        <v>12.87935296</v>
       </c>
       <c r="Q65">
-        <v>12.71424182</v>
+        <v>12.54735296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2124298828973001</v>
+        <v>0.2167107970003588</v>
       </c>
       <c r="T65">
-        <v>2.809619209738936</v>
+        <v>2.881801571570212</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.240844976064091</v>
+        <v>2.20583177331309</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1177957269201292</v>
+        <v>0.1178341171682573</v>
       </c>
       <c r="C66">
-        <v>91.40906315090402</v>
+        <v>88.65484882900464</v>
       </c>
       <c r="D66">
-        <v>193.249063150904</v>
+        <v>193.1798488290047</v>
       </c>
       <c r="E66">
-        <v>155.24</v>
+        <v>157.925</v>
       </c>
       <c r="F66">
-        <v>171.84</v>
+        <v>174.525</v>
       </c>
       <c r="G66">
         <v>70</v>
@@ -6699,28 +6699,28 @@
         <v>28.732</v>
       </c>
       <c r="M66">
-        <v>13.025472</v>
+        <v>13.228995</v>
       </c>
       <c r="N66">
-        <v>15.706528</v>
+        <v>15.503005</v>
       </c>
       <c r="O66">
-        <v>2.82717504</v>
+        <v>2.790540899999999</v>
       </c>
       <c r="P66">
-        <v>12.87935296</v>
+        <v>12.7124641</v>
       </c>
       <c r="Q66">
-        <v>12.54735296</v>
+        <v>12.3804641</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2167107970003588</v>
+        <v>0.2212363347664494</v>
       </c>
       <c r="T66">
-        <v>2.881801571570212</v>
+        <v>2.958108639791846</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.20583177331309</v>
+        <v>2.171895899877504</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1178341171682573</v>
+        <v>0.1178725074163854</v>
       </c>
       <c r="C67">
-        <v>88.65484882900464</v>
+        <v>85.90068406912727</v>
       </c>
       <c r="D67">
-        <v>193.1798488290047</v>
+        <v>193.1106840691273</v>
       </c>
       <c r="E67">
-        <v>157.925</v>
+        <v>160.61</v>
       </c>
       <c r="F67">
-        <v>174.525</v>
+        <v>177.21</v>
       </c>
       <c r="G67">
         <v>70</v>
@@ -6781,28 +6781,28 @@
         <v>28.732</v>
       </c>
       <c r="M67">
-        <v>13.228995</v>
+        <v>13.432518</v>
       </c>
       <c r="N67">
-        <v>15.503005</v>
+        <v>15.299482</v>
       </c>
       <c r="O67">
-        <v>2.790540899999999</v>
+        <v>2.75390676</v>
       </c>
       <c r="P67">
-        <v>12.7124641</v>
+        <v>12.54557524</v>
       </c>
       <c r="Q67">
-        <v>12.3804641</v>
+        <v>12.21357524</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2212363347664494</v>
+        <v>0.2260280806364277</v>
       </c>
       <c r="T67">
-        <v>2.958108639791846</v>
+        <v>3.038904359085341</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.171895899877504</v>
+        <v>2.138988386242996</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1178725074163854</v>
+        <v>0.1179108976645135</v>
       </c>
       <c r="C68">
-        <v>85.90068406912727</v>
+        <v>83.14656881805635</v>
       </c>
       <c r="D68">
-        <v>193.1106840691273</v>
+        <v>193.0415688180564</v>
       </c>
       <c r="E68">
-        <v>160.61</v>
+        <v>163.295</v>
       </c>
       <c r="F68">
-        <v>177.21</v>
+        <v>179.895</v>
       </c>
       <c r="G68">
         <v>70</v>
@@ -6863,28 +6863,28 @@
         <v>28.732</v>
       </c>
       <c r="M68">
-        <v>13.432518</v>
+        <v>13.636041</v>
       </c>
       <c r="N68">
-        <v>15.299482</v>
+        <v>15.095959</v>
       </c>
       <c r="O68">
-        <v>2.75390676</v>
+        <v>2.717272619999999</v>
       </c>
       <c r="P68">
-        <v>12.54557524</v>
+        <v>12.37868638</v>
       </c>
       <c r="Q68">
-        <v>12.21357524</v>
+        <v>12.04668638</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2260280806364277</v>
+        <v>0.2311102353470107</v>
       </c>
       <c r="T68">
-        <v>3.038904359085341</v>
+        <v>3.124596788639048</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.138988386242996</v>
+        <v>2.107063186448324</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1179108976645135</v>
+        <v>0.1179492879126417</v>
       </c>
       <c r="C69">
-        <v>83.14656881805635</v>
+        <v>80.39250302265262</v>
       </c>
       <c r="D69">
-        <v>193.0415688180564</v>
+        <v>192.9725030226526</v>
       </c>
       <c r="E69">
-        <v>163.295</v>
+        <v>165.98</v>
       </c>
       <c r="F69">
-        <v>179.895</v>
+        <v>182.58</v>
       </c>
       <c r="G69">
         <v>70</v>
@@ -6945,28 +6945,28 @@
         <v>28.732</v>
       </c>
       <c r="M69">
-        <v>13.636041</v>
+        <v>13.839564</v>
       </c>
       <c r="N69">
-        <v>15.095959</v>
+        <v>14.892436</v>
       </c>
       <c r="O69">
-        <v>2.717272619999999</v>
+        <v>2.680638479999999</v>
       </c>
       <c r="P69">
-        <v>12.37868638</v>
+        <v>12.21179752</v>
       </c>
       <c r="Q69">
-        <v>12.04668638</v>
+        <v>11.87979752</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2311102353470107</v>
+        <v>0.2365100247270052</v>
       </c>
       <c r="T69">
-        <v>3.124596788639048</v>
+        <v>3.215644995039863</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.107063186448324</v>
+        <v>2.076076963118202</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1179492879126417</v>
+        <v>0.1179876781607698</v>
       </c>
       <c r="C70">
-        <v>80.39250302265262</v>
+        <v>77.63848662985274</v>
       </c>
       <c r="D70">
-        <v>192.9725030226526</v>
+        <v>192.9034866298528</v>
       </c>
       <c r="E70">
-        <v>165.98</v>
+        <v>168.665</v>
       </c>
       <c r="F70">
-        <v>182.58</v>
+        <v>185.265</v>
       </c>
       <c r="G70">
         <v>70</v>
@@ -7027,28 +7027,28 @@
         <v>28.732</v>
       </c>
       <c r="M70">
-        <v>13.839564</v>
+        <v>14.043087</v>
       </c>
       <c r="N70">
-        <v>14.892436</v>
+        <v>14.688913</v>
       </c>
       <c r="O70">
-        <v>2.680638479999999</v>
+        <v>2.64400434</v>
       </c>
       <c r="P70">
-        <v>12.21179752</v>
+        <v>12.04490866</v>
       </c>
       <c r="Q70">
-        <v>11.87979752</v>
+        <v>11.71290866</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2365100247270052</v>
+        <v>0.2422581876153865</v>
       </c>
       <c r="T70">
-        <v>3.215644995039863</v>
+        <v>3.312567279272987</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.076076963118202</v>
+        <v>2.045988891188953</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1179876781607698</v>
+        <v>0.1180260684088979</v>
       </c>
       <c r="C71">
-        <v>77.63848662985274</v>
+        <v>74.88451958666943</v>
       </c>
       <c r="D71">
-        <v>192.9034866298528</v>
+        <v>192.8345195866694</v>
       </c>
       <c r="E71">
-        <v>168.665</v>
+        <v>171.35</v>
       </c>
       <c r="F71">
-        <v>185.265</v>
+        <v>187.95</v>
       </c>
       <c r="G71">
         <v>70</v>
@@ -7109,28 +7109,28 @@
         <v>28.732</v>
       </c>
       <c r="M71">
-        <v>14.043087</v>
+        <v>14.24661</v>
       </c>
       <c r="N71">
-        <v>14.688913</v>
+        <v>14.48539</v>
       </c>
       <c r="O71">
-        <v>2.64400434</v>
+        <v>2.607370199999999</v>
       </c>
       <c r="P71">
-        <v>12.04490866</v>
+        <v>11.8780198</v>
       </c>
       <c r="Q71">
-        <v>11.71290866</v>
+        <v>11.5460198</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2422581876153865</v>
+        <v>0.2483895613629931</v>
       </c>
       <c r="T71">
-        <v>3.312567279272987</v>
+        <v>3.415951049121653</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.045988891188953</v>
+        <v>2.016760478457682</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1180260684088979</v>
+        <v>0.126331698657026</v>
       </c>
       <c r="C72">
-        <v>74.88451958666943</v>
+        <v>58.35487922616463</v>
       </c>
       <c r="D72">
-        <v>192.8345195866694</v>
+        <v>178.9898792261646</v>
       </c>
       <c r="E72">
-        <v>171.35</v>
+        <v>174.035</v>
       </c>
       <c r="F72">
-        <v>187.95</v>
+        <v>190.635</v>
       </c>
       <c r="G72">
         <v>70</v>
@@ -7191,45 +7191,45 @@
         <v>28.732</v>
       </c>
       <c r="M72">
-        <v>14.24661</v>
+        <v>17.15715</v>
       </c>
       <c r="N72">
-        <v>14.48539</v>
+        <v>11.57485</v>
       </c>
       <c r="O72">
-        <v>2.607370199999999</v>
+        <v>2.083473</v>
       </c>
       <c r="P72">
-        <v>11.8780198</v>
+        <v>9.491376999999998</v>
       </c>
       <c r="Q72">
-        <v>11.5460198</v>
+        <v>9.159376999999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2483895613629931</v>
+        <v>0.2549437884725037</v>
       </c>
       <c r="T72">
-        <v>3.415951049121653</v>
+        <v>3.526464734132296</v>
       </c>
       <c r="U72">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
         <v>0.18</v>
       </c>
       <c r="W72">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.016760478457682</v>
+        <v>1.674637104647333</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.126331698657026</v>
+        <v>0.1264865289051542</v>
       </c>
       <c r="C73">
-        <v>58.35487922616466</v>
+        <v>55.4306425682957</v>
       </c>
       <c r="D73">
-        <v>178.9898792261646</v>
+        <v>178.7506425682957</v>
       </c>
       <c r="E73">
-        <v>174.035</v>
+        <v>176.72</v>
       </c>
       <c r="F73">
-        <v>190.635</v>
+        <v>193.32</v>
       </c>
       <c r="G73">
         <v>70</v>
@@ -7273,28 +7273,28 @@
         <v>28.732</v>
       </c>
       <c r="M73">
-        <v>17.15715</v>
+        <v>17.3988</v>
       </c>
       <c r="N73">
-        <v>11.57485</v>
+        <v>11.3332</v>
       </c>
       <c r="O73">
-        <v>2.083473</v>
+        <v>2.039976</v>
       </c>
       <c r="P73">
-        <v>9.491377000000002</v>
+        <v>9.293224000000002</v>
       </c>
       <c r="Q73">
-        <v>9.159377000000001</v>
+        <v>8.961224000000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2549437884725036</v>
+        <v>0.2619661746612649</v>
       </c>
       <c r="T73">
-        <v>3.526464734132295</v>
+        <v>3.644872253786555</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.674637104647334</v>
+        <v>1.651378255971677</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1264865289051542</v>
+        <v>0.1266413591532823</v>
       </c>
       <c r="C74">
-        <v>55.4306425682957</v>
+        <v>52.50704458097064</v>
       </c>
       <c r="D74">
-        <v>178.7506425682957</v>
+        <v>178.5120445809706</v>
       </c>
       <c r="E74">
-        <v>176.72</v>
+        <v>179.405</v>
       </c>
       <c r="F74">
-        <v>193.32</v>
+        <v>196.005</v>
       </c>
       <c r="G74">
         <v>70</v>
@@ -7355,28 +7355,28 @@
         <v>28.732</v>
       </c>
       <c r="M74">
-        <v>17.3988</v>
+        <v>17.64045</v>
       </c>
       <c r="N74">
-        <v>11.3332</v>
+        <v>11.09155</v>
       </c>
       <c r="O74">
-        <v>2.039976</v>
+        <v>1.996479</v>
       </c>
       <c r="P74">
-        <v>9.293224000000002</v>
+        <v>9.095071000000001</v>
       </c>
       <c r="Q74">
-        <v>8.961224000000001</v>
+        <v>8.763071</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2619661746612649</v>
+        <v>0.2695087376047492</v>
       </c>
       <c r="T74">
-        <v>3.644872253786555</v>
+        <v>3.772050700822613</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.651378255971677</v>
+        <v>1.628756636026859</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1266413591532823</v>
+        <v>0.1267961894014104</v>
       </c>
       <c r="C75">
-        <v>52.50704458097064</v>
+        <v>49.58408271008909</v>
       </c>
       <c r="D75">
-        <v>178.5120445809706</v>
+        <v>178.2740827100891</v>
       </c>
       <c r="E75">
-        <v>179.405</v>
+        <v>182.09</v>
       </c>
       <c r="F75">
-        <v>196.005</v>
+        <v>198.69</v>
       </c>
       <c r="G75">
         <v>70</v>
@@ -7437,28 +7437,28 @@
         <v>28.732</v>
       </c>
       <c r="M75">
-        <v>17.64045</v>
+        <v>17.8821</v>
       </c>
       <c r="N75">
-        <v>11.09155</v>
+        <v>10.8499</v>
       </c>
       <c r="O75">
-        <v>1.996479</v>
+        <v>1.952982</v>
       </c>
       <c r="P75">
-        <v>9.095071000000001</v>
+        <v>8.896918000000001</v>
       </c>
       <c r="Q75">
-        <v>8.763071</v>
+        <v>8.564918</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2695087376047492</v>
+        <v>0.2776314976977324</v>
       </c>
       <c r="T75">
-        <v>3.772050700822613</v>
+        <v>3.909012105322982</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.628756636026859</v>
+        <v>1.606746411215685</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1267961894014104</v>
+        <v>0.1269510196495386</v>
       </c>
       <c r="C76">
-        <v>49.58408271008909</v>
+        <v>46.66175441515094</v>
       </c>
       <c r="D76">
-        <v>178.2740827100891</v>
+        <v>178.0367544151509</v>
       </c>
       <c r="E76">
-        <v>182.09</v>
+        <v>184.775</v>
       </c>
       <c r="F76">
-        <v>198.69</v>
+        <v>201.375</v>
       </c>
       <c r="G76">
         <v>70</v>
@@ -7519,28 +7519,28 @@
         <v>28.732</v>
       </c>
       <c r="M76">
-        <v>17.8821</v>
+        <v>18.12375</v>
       </c>
       <c r="N76">
-        <v>10.8499</v>
+        <v>10.60825</v>
       </c>
       <c r="O76">
-        <v>1.952982</v>
+        <v>1.909485</v>
       </c>
       <c r="P76">
-        <v>8.896918000000001</v>
+        <v>8.698765000000002</v>
       </c>
       <c r="Q76">
-        <v>8.564918</v>
+        <v>8.366765000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2776314976977324</v>
+        <v>0.2864040785981542</v>
       </c>
       <c r="T76">
-        <v>3.909012105322982</v>
+        <v>4.056930422183381</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.606746411215685</v>
+        <v>1.585323125732809</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1269510196495386</v>
+        <v>0.1271058498976667</v>
       </c>
       <c r="C77">
-        <v>46.66175441515094</v>
+        <v>43.74005716916665</v>
       </c>
       <c r="D77">
-        <v>178.0367544151509</v>
+        <v>177.8000571691666</v>
       </c>
       <c r="E77">
-        <v>184.775</v>
+        <v>187.46</v>
       </c>
       <c r="F77">
-        <v>201.375</v>
+        <v>204.06</v>
       </c>
       <c r="G77">
         <v>70</v>
@@ -7601,28 +7601,28 @@
         <v>28.732</v>
       </c>
       <c r="M77">
-        <v>18.12375</v>
+        <v>18.3654</v>
       </c>
       <c r="N77">
-        <v>10.60825</v>
+        <v>10.3666</v>
       </c>
       <c r="O77">
-        <v>1.909485</v>
+        <v>1.865988</v>
       </c>
       <c r="P77">
-        <v>8.698765000000002</v>
+        <v>8.500611999999999</v>
       </c>
       <c r="Q77">
-        <v>8.366765000000001</v>
+        <v>8.168611999999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2864040785981542</v>
+        <v>0.2959077079069445</v>
       </c>
       <c r="T77">
-        <v>4.056930422183381</v>
+        <v>4.217175265448813</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.585323125732809</v>
+        <v>1.564463610920535</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1271058498976667</v>
+        <v>0.1272606801457948</v>
       </c>
       <c r="C78">
-        <v>43.74005716916665</v>
+        <v>40.81898845856696</v>
       </c>
       <c r="D78">
-        <v>177.8000571691666</v>
+        <v>177.563988458567</v>
       </c>
       <c r="E78">
-        <v>187.46</v>
+        <v>190.145</v>
       </c>
       <c r="F78">
-        <v>204.06</v>
+        <v>206.745</v>
       </c>
       <c r="G78">
         <v>70</v>
@@ -7683,28 +7683,28 @@
         <v>28.732</v>
       </c>
       <c r="M78">
-        <v>18.3654</v>
+        <v>18.60705</v>
       </c>
       <c r="N78">
-        <v>10.3666</v>
+        <v>10.12495</v>
       </c>
       <c r="O78">
-        <v>1.865988</v>
+        <v>1.822491</v>
       </c>
       <c r="P78">
-        <v>8.500611999999999</v>
+        <v>8.302458999999999</v>
       </c>
       <c r="Q78">
-        <v>8.168611999999998</v>
+        <v>7.970458999999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2959077079069445</v>
+        <v>0.3062377397643253</v>
       </c>
       <c r="T78">
-        <v>4.217175265448813</v>
+        <v>4.39135444291124</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.564463610920535</v>
+        <v>1.544145901687801</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1272606801457948</v>
+        <v>0.127415510393923</v>
       </c>
       <c r="C79">
-        <v>40.81898845856696</v>
+        <v>37.89854578311434</v>
       </c>
       <c r="D79">
-        <v>177.563988458567</v>
+        <v>177.3285457831144</v>
       </c>
       <c r="E79">
-        <v>190.145</v>
+        <v>192.83</v>
       </c>
       <c r="F79">
-        <v>206.745</v>
+        <v>209.43</v>
       </c>
       <c r="G79">
         <v>70</v>
@@ -7765,28 +7765,28 @@
         <v>28.732</v>
       </c>
       <c r="M79">
-        <v>18.60705</v>
+        <v>18.8487</v>
       </c>
       <c r="N79">
-        <v>10.12495</v>
+        <v>9.883299999999998</v>
       </c>
       <c r="O79">
-        <v>1.822491</v>
+        <v>1.778994</v>
       </c>
       <c r="P79">
-        <v>8.302458999999999</v>
+        <v>8.104305999999999</v>
       </c>
       <c r="Q79">
-        <v>7.970458999999999</v>
+        <v>7.772305999999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3062377397643253</v>
+        <v>0.3175068654269225</v>
       </c>
       <c r="T79">
-        <v>4.39135444291124</v>
+        <v>4.581368091052068</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.544145901687801</v>
+        <v>1.52434915935847</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.127415510393923</v>
+        <v>0.1275703406420511</v>
       </c>
       <c r="C80">
-        <v>37.89854578311434</v>
+        <v>34.97872665581454</v>
       </c>
       <c r="D80">
-        <v>177.3285457831144</v>
+        <v>177.0937266558145</v>
       </c>
       <c r="E80">
-        <v>192.83</v>
+        <v>195.515</v>
       </c>
       <c r="F80">
-        <v>209.43</v>
+        <v>212.115</v>
       </c>
       <c r="G80">
         <v>70</v>
@@ -7847,28 +7847,28 @@
         <v>28.732</v>
       </c>
       <c r="M80">
-        <v>18.8487</v>
+        <v>19.09035</v>
       </c>
       <c r="N80">
-        <v>9.883299999999998</v>
+        <v>9.641649999999998</v>
       </c>
       <c r="O80">
-        <v>1.778994</v>
+        <v>1.735497</v>
       </c>
       <c r="P80">
-        <v>8.104305999999999</v>
+        <v>7.906152999999999</v>
       </c>
       <c r="Q80">
-        <v>7.772305999999999</v>
+        <v>7.574152999999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3175068654269225</v>
+        <v>0.3298492411526242</v>
       </c>
       <c r="T80">
-        <v>4.581368091052068</v>
+        <v>4.789478277111072</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.52434915935847</v>
+        <v>1.505053600379249</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1275703406420511</v>
+        <v>0.1677528728114454</v>
       </c>
       <c r="C81">
-        <v>34.97872665581454</v>
+        <v>-13.00106057503399</v>
       </c>
       <c r="D81">
-        <v>177.0937266558145</v>
+        <v>131.798939424966</v>
       </c>
       <c r="E81">
-        <v>195.515</v>
+        <v>198.2</v>
       </c>
       <c r="F81">
-        <v>212.115</v>
+        <v>214.8</v>
       </c>
       <c r="G81">
         <v>70</v>
@@ -7929,45 +7929,45 @@
         <v>28.732</v>
       </c>
       <c r="M81">
-        <v>19.09035</v>
+        <v>31.53264</v>
       </c>
       <c r="N81">
-        <v>9.641649999999998</v>
+        <v>-2.800640000000005</v>
       </c>
       <c r="O81">
-        <v>1.735497</v>
+        <v>-0.5041152000000009</v>
       </c>
       <c r="P81">
-        <v>7.906152999999999</v>
+        <v>-2.296524800000004</v>
       </c>
       <c r="Q81">
-        <v>7.574152999999999</v>
+        <v>-2.628524800000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3298492411526242</v>
+        <v>0.3478727439454952</v>
       </c>
       <c r="T81">
-        <v>4.789478277111072</v>
+        <v>5.093380427152457</v>
       </c>
       <c r="U81">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.18</v>
+        <v>0.164012908529067</v>
       </c>
       <c r="W81">
-        <v>0.0738</v>
+        <v>0.122722905027933</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.505053600379249</v>
+        <v>0.9111828251614833</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1677528728114454</v>
+        <v>0.1687628728114454</v>
       </c>
       <c r="C82">
-        <v>-13.00106057503399</v>
+        <v>-16.52795567946379</v>
       </c>
       <c r="D82">
-        <v>131.798939424966</v>
+        <v>130.9570443205362</v>
       </c>
       <c r="E82">
-        <v>198.2</v>
+        <v>200.885</v>
       </c>
       <c r="F82">
-        <v>214.8</v>
+        <v>217.485</v>
       </c>
       <c r="G82">
         <v>70</v>
@@ -8011,37 +8011,37 @@
         <v>28.732</v>
       </c>
       <c r="M82">
-        <v>31.53264</v>
+        <v>31.92679800000001</v>
       </c>
       <c r="N82">
-        <v>-2.800640000000005</v>
+        <v>-3.194798000000006</v>
       </c>
       <c r="O82">
-        <v>-0.5041152000000009</v>
+        <v>-0.575063640000001</v>
       </c>
       <c r="P82">
-        <v>-2.296524800000004</v>
+        <v>-2.619734360000005</v>
       </c>
       <c r="Q82">
-        <v>-2.628524800000004</v>
+        <v>-2.951734360000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3478727439454952</v>
+        <v>0.3637713094163106</v>
       </c>
       <c r="T82">
-        <v>5.093380427152457</v>
+        <v>5.361453081213112</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.164012908529067</v>
+        <v>0.1619880578064859</v>
       </c>
       <c r="W82">
-        <v>0.122722905027933</v>
+        <v>0.1230201531140079</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9111828251614833</v>
+        <v>0.8999336544804774</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1687628728114454</v>
+        <v>0.1697728728114454</v>
       </c>
       <c r="C83">
-        <v>-16.52795567946379</v>
+        <v>-20.0441634662304</v>
       </c>
       <c r="D83">
-        <v>130.9570443205362</v>
+        <v>130.1258365337696</v>
       </c>
       <c r="E83">
-        <v>200.885</v>
+        <v>203.57</v>
       </c>
       <c r="F83">
-        <v>217.485</v>
+        <v>220.17</v>
       </c>
       <c r="G83">
         <v>70</v>
@@ -8093,37 +8093,37 @@
         <v>28.732</v>
       </c>
       <c r="M83">
-        <v>31.92679800000001</v>
+        <v>32.320956</v>
       </c>
       <c r="N83">
-        <v>-3.194798000000006</v>
+        <v>-3.588956000000003</v>
       </c>
       <c r="O83">
-        <v>-0.575063640000001</v>
+        <v>-0.6460120800000005</v>
       </c>
       <c r="P83">
-        <v>-2.619734360000005</v>
+        <v>-2.942943920000002</v>
       </c>
       <c r="Q83">
-        <v>-2.951734360000005</v>
+        <v>-3.274943920000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3637713094163106</v>
+        <v>0.3814363821616613</v>
       </c>
       <c r="T83">
-        <v>5.361453081213112</v>
+        <v>5.659311585724953</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1619880578064859</v>
+        <v>0.1600125936868946</v>
       </c>
       <c r="W83">
-        <v>0.1230201531140079</v>
+        <v>0.1233101512467639</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8999336544804774</v>
+        <v>0.8889588538160813</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1697728728114454</v>
+        <v>0.1707828728114454</v>
       </c>
       <c r="C84">
-        <v>-20.0441634662304</v>
+        <v>-23.54988615476202</v>
       </c>
       <c r="D84">
-        <v>130.1258365337696</v>
+        <v>129.305113845238</v>
       </c>
       <c r="E84">
-        <v>203.57</v>
+        <v>206.255</v>
       </c>
       <c r="F84">
-        <v>220.17</v>
+        <v>222.855</v>
       </c>
       <c r="G84">
         <v>70</v>
@@ -8175,37 +8175,37 @@
         <v>28.732</v>
       </c>
       <c r="M84">
-        <v>32.320956</v>
+        <v>32.71511400000001</v>
       </c>
       <c r="N84">
-        <v>-3.588956000000003</v>
+        <v>-3.983114000000008</v>
       </c>
       <c r="O84">
-        <v>-0.6460120800000005</v>
+        <v>-0.7169605200000013</v>
       </c>
       <c r="P84">
-        <v>-2.942943920000002</v>
+        <v>-3.266153480000006</v>
       </c>
       <c r="Q84">
-        <v>-3.274943920000002</v>
+        <v>-3.598153480000006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3814363821616613</v>
+        <v>0.4011796987594061</v>
       </c>
       <c r="T84">
-        <v>5.659311585724953</v>
+        <v>5.992212267238186</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1600125936868946</v>
+        <v>0.1580847311123537</v>
       </c>
       <c r="W84">
-        <v>0.1233101512467639</v>
+        <v>0.1235931614727065</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8889588538160813</v>
+        <v>0.8782485061797429</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1707828728114454</v>
+        <v>0.1717928728114454</v>
       </c>
       <c r="C85">
-        <v>-23.54988615476202</v>
+        <v>-27.04532089475236</v>
       </c>
       <c r="D85">
-        <v>129.305113845238</v>
+        <v>128.4946791052477</v>
       </c>
       <c r="E85">
-        <v>206.255</v>
+        <v>208.94</v>
       </c>
       <c r="F85">
-        <v>222.855</v>
+        <v>225.54</v>
       </c>
       <c r="G85">
         <v>70</v>
@@ -8257,37 +8257,37 @@
         <v>28.732</v>
       </c>
       <c r="M85">
-        <v>32.71511400000001</v>
+        <v>33.109272</v>
       </c>
       <c r="N85">
-        <v>-3.983114000000008</v>
+        <v>-4.377272000000005</v>
       </c>
       <c r="O85">
-        <v>-0.7169605200000013</v>
+        <v>-0.7879089600000009</v>
       </c>
       <c r="P85">
-        <v>-3.266153480000006</v>
+        <v>-3.589363040000004</v>
       </c>
       <c r="Q85">
-        <v>-3.598153480000006</v>
+        <v>-3.921363040000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4011796987594061</v>
+        <v>0.423390929931869</v>
       </c>
       <c r="T85">
-        <v>5.992212267238186</v>
+        <v>6.366725533940572</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1580847311123537</v>
+        <v>0.1562027700276828</v>
       </c>
       <c r="W85">
-        <v>0.1235931614727065</v>
+        <v>0.1238694333599362</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8782485061797429</v>
+        <v>0.8677931668204604</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1717928728114454</v>
+        <v>0.1728028728114454</v>
       </c>
       <c r="C86">
-        <v>-27.04532089475234</v>
+        <v>-30.53065992404672</v>
       </c>
       <c r="D86">
-        <v>128.4946791052477</v>
+        <v>127.6943400759533</v>
       </c>
       <c r="E86">
-        <v>208.94</v>
+        <v>211.625</v>
       </c>
       <c r="F86">
-        <v>225.54</v>
+        <v>228.225</v>
       </c>
       <c r="G86">
         <v>70</v>
@@ -8339,37 +8339,37 @@
         <v>28.732</v>
       </c>
       <c r="M86">
-        <v>33.109272</v>
+        <v>33.50343</v>
       </c>
       <c r="N86">
-        <v>-4.377272000000005</v>
+        <v>-4.771430000000002</v>
       </c>
       <c r="O86">
-        <v>-0.7879089600000009</v>
+        <v>-0.8588574000000003</v>
       </c>
       <c r="P86">
-        <v>-3.589363040000004</v>
+        <v>-3.912572600000002</v>
       </c>
       <c r="Q86">
-        <v>-3.921363040000004</v>
+        <v>-4.244572600000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4233909299318687</v>
+        <v>0.4485636585939934</v>
       </c>
       <c r="T86">
-        <v>6.366725533940568</v>
+        <v>6.791173902869941</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1562027700276828</v>
+        <v>0.1543650903802984</v>
       </c>
       <c r="W86">
-        <v>0.1238694333599362</v>
+        <v>0.1241392047321722</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8677931668204604</v>
+        <v>0.8575838354461021</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1728028728114454</v>
+        <v>0.1738128728114454</v>
       </c>
       <c r="C87">
-        <v>-30.53065992404672</v>
+        <v>-34.00609072066428</v>
       </c>
       <c r="D87">
-        <v>127.6943400759533</v>
+        <v>126.9039092793357</v>
       </c>
       <c r="E87">
-        <v>211.625</v>
+        <v>214.31</v>
       </c>
       <c r="F87">
-        <v>228.225</v>
+        <v>230.91</v>
       </c>
       <c r="G87">
         <v>70</v>
@@ -8421,37 +8421,37 @@
         <v>28.732</v>
       </c>
       <c r="M87">
-        <v>33.50343</v>
+        <v>33.89758800000001</v>
       </c>
       <c r="N87">
-        <v>-4.771430000000002</v>
+        <v>-5.165588000000007</v>
       </c>
       <c r="O87">
-        <v>-0.8588574000000003</v>
+        <v>-0.9298058400000012</v>
       </c>
       <c r="P87">
-        <v>-3.912572600000002</v>
+        <v>-4.235782160000006</v>
       </c>
       <c r="Q87">
-        <v>-4.244572600000002</v>
+        <v>-4.567782160000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4485636585939934</v>
+        <v>0.4773324913507072</v>
       </c>
       <c r="T87">
-        <v>6.791173902869941</v>
+        <v>7.276257753074936</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1543650903802984</v>
+        <v>0.1525701474688995</v>
       </c>
       <c r="W87">
-        <v>0.1241392047321722</v>
+        <v>0.1244027023515656</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8575838354461021</v>
+        <v>0.8476119303827752</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1738128728114454</v>
+        <v>0.1748228728114454</v>
       </c>
       <c r="C88">
-        <v>-34.00609072066428</v>
+        <v>-37.47179614920904</v>
       </c>
       <c r="D88">
-        <v>126.9039092793357</v>
+        <v>126.123203850791</v>
       </c>
       <c r="E88">
-        <v>214.31</v>
+        <v>216.995</v>
       </c>
       <c r="F88">
-        <v>230.91</v>
+        <v>233.595</v>
       </c>
       <c r="G88">
         <v>70</v>
@@ -8503,37 +8503,37 @@
         <v>28.732</v>
       </c>
       <c r="M88">
-        <v>33.89758800000001</v>
+        <v>34.291746</v>
       </c>
       <c r="N88">
-        <v>-5.165588000000007</v>
+        <v>-5.559746000000004</v>
       </c>
       <c r="O88">
-        <v>-0.9298058400000012</v>
+        <v>-1.000754280000001</v>
       </c>
       <c r="P88">
-        <v>-4.235782160000006</v>
+        <v>-4.558991720000003</v>
       </c>
       <c r="Q88">
-        <v>-4.567782160000005</v>
+        <v>-4.890991720000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4773324913507072</v>
+        <v>0.5105272983776847</v>
       </c>
       <c r="T88">
-        <v>7.276257753074936</v>
+        <v>7.835969887926855</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1525701474688995</v>
+        <v>0.1508164676129352</v>
       </c>
       <c r="W88">
-        <v>0.1244027023515656</v>
+        <v>0.1246601425544211</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8476119303827752</v>
+        <v>0.8378692645163065</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1748228728114454</v>
+        <v>0.1758328728114454</v>
       </c>
       <c r="C89">
-        <v>-37.47179614920904</v>
+        <v>-40.92795460190942</v>
       </c>
       <c r="D89">
-        <v>126.123203850791</v>
+        <v>125.3520453980906</v>
       </c>
       <c r="E89">
-        <v>216.995</v>
+        <v>219.68</v>
       </c>
       <c r="F89">
-        <v>233.595</v>
+        <v>236.28</v>
       </c>
       <c r="G89">
         <v>70</v>
@@ -8585,37 +8585,37 @@
         <v>28.732</v>
       </c>
       <c r="M89">
-        <v>34.291746</v>
+        <v>34.685904</v>
       </c>
       <c r="N89">
-        <v>-5.559746000000004</v>
+        <v>-5.953904000000001</v>
       </c>
       <c r="O89">
-        <v>-1.000754280000001</v>
+        <v>-1.07170272</v>
       </c>
       <c r="P89">
-        <v>-4.558991720000003</v>
+        <v>-4.882201280000001</v>
       </c>
       <c r="Q89">
-        <v>-4.890991720000003</v>
+        <v>-5.214201280000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5105272983776847</v>
+        <v>0.5492545732424918</v>
       </c>
       <c r="T89">
-        <v>7.835969887926855</v>
+        <v>8.488967378587427</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1508164676129352</v>
+        <v>0.1491026441173336</v>
       </c>
       <c r="W89">
-        <v>0.1246601425544211</v>
+        <v>0.1249117318435754</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8378692645163065</v>
+        <v>0.8283480228740758</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1758328728114454</v>
+        <v>0.1768428728114454</v>
       </c>
       <c r="C90">
-        <v>-40.92795460190942</v>
+        <v>-44.37474013451504</v>
       </c>
       <c r="D90">
-        <v>125.3520453980906</v>
+        <v>124.590259865485</v>
       </c>
       <c r="E90">
-        <v>219.68</v>
+        <v>222.365</v>
       </c>
       <c r="F90">
-        <v>236.28</v>
+        <v>238.965</v>
       </c>
       <c r="G90">
         <v>70</v>
@@ -8667,37 +8667,37 @@
         <v>28.732</v>
       </c>
       <c r="M90">
-        <v>34.685904</v>
+        <v>35.08006200000001</v>
       </c>
       <c r="N90">
-        <v>-5.953904000000001</v>
+        <v>-6.348062000000006</v>
       </c>
       <c r="O90">
-        <v>-1.07170272</v>
+        <v>-1.142651160000001</v>
       </c>
       <c r="P90">
-        <v>-4.882201280000001</v>
+        <v>-5.205410840000004</v>
       </c>
       <c r="Q90">
-        <v>-5.214201280000001</v>
+        <v>-5.537410840000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5492545732424918</v>
+        <v>0.595023170809991</v>
       </c>
       <c r="T90">
-        <v>8.488967378587427</v>
+        <v>9.260691685731738</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1491026441173336</v>
+        <v>0.1474273335092737</v>
       </c>
       <c r="W90">
-        <v>0.1249117318435754</v>
+        <v>0.1251576674408386</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8283480228740758</v>
+        <v>0.8190407417181873</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1768428728114454</v>
+        <v>0.1778528728114454</v>
       </c>
       <c r="C91">
-        <v>-44.37474013451504</v>
+        <v>-47.8123225972686</v>
       </c>
       <c r="D91">
-        <v>124.590259865485</v>
+        <v>123.8376774027314</v>
       </c>
       <c r="E91">
-        <v>222.365</v>
+        <v>225.05</v>
       </c>
       <c r="F91">
-        <v>238.965</v>
+        <v>241.65</v>
       </c>
       <c r="G91">
         <v>70</v>
@@ -8749,37 +8749,37 @@
         <v>28.732</v>
       </c>
       <c r="M91">
-        <v>35.08006200000001</v>
+        <v>35.47422</v>
       </c>
       <c r="N91">
-        <v>-6.348062000000006</v>
+        <v>-6.742220000000003</v>
       </c>
       <c r="O91">
-        <v>-1.142651160000001</v>
+        <v>-1.2135996</v>
       </c>
       <c r="P91">
-        <v>-5.205410840000004</v>
+        <v>-5.528620400000003</v>
       </c>
       <c r="Q91">
-        <v>-5.537410840000004</v>
+        <v>-5.860620400000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.595023170809991</v>
+        <v>0.6499454878909903</v>
       </c>
       <c r="T91">
-        <v>9.260691685731738</v>
+        <v>10.18676085430491</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1474273335092737</v>
+        <v>0.1457892520258373</v>
       </c>
       <c r="W91">
-        <v>0.1251576674408386</v>
+        <v>0.1253981378026071</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8190407417181873</v>
+        <v>0.8099402890324297</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1778528728114454</v>
+        <v>0.1788628728114454</v>
       </c>
       <c r="C92">
-        <v>-47.8123225972686</v>
+        <v>-51.24086776115885</v>
       </c>
       <c r="D92">
-        <v>123.8376774027314</v>
+        <v>123.0941322388412</v>
       </c>
       <c r="E92">
-        <v>225.05</v>
+        <v>227.735</v>
       </c>
       <c r="F92">
-        <v>241.65</v>
+        <v>244.335</v>
       </c>
       <c r="G92">
         <v>70</v>
@@ -8831,37 +8831,37 @@
         <v>28.732</v>
       </c>
       <c r="M92">
-        <v>35.47422</v>
+        <v>35.86837800000001</v>
       </c>
       <c r="N92">
-        <v>-6.742220000000003</v>
+        <v>-7.136378000000008</v>
       </c>
       <c r="O92">
-        <v>-1.2135996</v>
+        <v>-1.284548040000001</v>
       </c>
       <c r="P92">
-        <v>-5.528620400000003</v>
+        <v>-5.851829960000006</v>
       </c>
       <c r="Q92">
-        <v>-5.860620400000003</v>
+        <v>-6.183829960000006</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6499454878909903</v>
+        <v>0.7170727643233225</v>
       </c>
       <c r="T92">
-        <v>10.18676085430491</v>
+        <v>11.3186231714499</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1457892520258373</v>
+        <v>0.1441871723332457</v>
       </c>
       <c r="W92">
-        <v>0.1253981378026071</v>
+        <v>0.1256333231014795</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8099402890324297</v>
+        <v>0.8010398462958095</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1788628728114454</v>
+        <v>0.2320065925402542</v>
       </c>
       <c r="C93">
-        <v>-51.24086776115885</v>
+        <v>-83.47815306855998</v>
       </c>
       <c r="D93">
-        <v>123.0941322388412</v>
+        <v>93.54184693144005</v>
       </c>
       <c r="E93">
-        <v>227.735</v>
+        <v>230.42</v>
       </c>
       <c r="F93">
-        <v>244.335</v>
+        <v>247.02</v>
       </c>
       <c r="G93">
         <v>70</v>
@@ -8913,45 +8913,45 @@
         <v>28.732</v>
       </c>
       <c r="M93">
-        <v>35.86837800000001</v>
+        <v>49.60161600000001</v>
       </c>
       <c r="N93">
-        <v>-7.136378000000008</v>
+        <v>-20.86961600000001</v>
       </c>
       <c r="O93">
-        <v>-1.284548040000001</v>
+        <v>-3.756530880000001</v>
       </c>
       <c r="P93">
-        <v>-5.851829960000006</v>
+        <v>-17.11308512000001</v>
       </c>
       <c r="Q93">
-        <v>-6.183829960000006</v>
+        <v>-17.44508512000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7170727643233225</v>
+        <v>0.8316533564738487</v>
       </c>
       <c r="T93">
-        <v>11.3186231714499</v>
+        <v>13.25061656406242</v>
       </c>
       <c r="U93">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1441871723332457</v>
+        <v>0.1042659577865366</v>
       </c>
       <c r="W93">
-        <v>0.1256333231014795</v>
+        <v>0.1798633956764635</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8010398462958095</v>
+        <v>0.5792553210363145</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2320065925402542</v>
+        <v>0.2335565925402542</v>
       </c>
       <c r="C94">
-        <v>-83.47815306855998</v>
+        <v>-86.81359569893735</v>
       </c>
       <c r="D94">
-        <v>93.54184693144005</v>
+        <v>92.89140430106266</v>
       </c>
       <c r="E94">
-        <v>230.42</v>
+        <v>233.105</v>
       </c>
       <c r="F94">
-        <v>247.02</v>
+        <v>249.705</v>
       </c>
       <c r="G94">
         <v>70</v>
@@ -8995,37 +8995,37 @@
         <v>28.732</v>
       </c>
       <c r="M94">
-        <v>49.60161600000001</v>
+        <v>50.140764</v>
       </c>
       <c r="N94">
-        <v>-20.86961600000001</v>
+        <v>-21.40876400000001</v>
       </c>
       <c r="O94">
-        <v>-3.756530880000001</v>
+        <v>-3.853577520000001</v>
       </c>
       <c r="P94">
-        <v>-17.11308512000001</v>
+        <v>-17.55518648</v>
       </c>
       <c r="Q94">
-        <v>-17.44508512000001</v>
+        <v>-17.88718648</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8316533564738487</v>
+        <v>0.9439181216843986</v>
       </c>
       <c r="T94">
-        <v>13.25061656406242</v>
+        <v>15.14356178749991</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1042659577865366</v>
+        <v>0.1031448184554986</v>
       </c>
       <c r="W94">
-        <v>0.1798633956764635</v>
+        <v>0.1800885204541359</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5792553210363145</v>
+        <v>0.5730267691972144</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2335565925402542</v>
+        <v>0.2351065925402543</v>
       </c>
       <c r="C95">
-        <v>-86.81359569893735</v>
+        <v>-90.14005509687863</v>
       </c>
       <c r="D95">
-        <v>92.89140430106266</v>
+        <v>92.24994490312139</v>
       </c>
       <c r="E95">
-        <v>233.105</v>
+        <v>235.79</v>
       </c>
       <c r="F95">
-        <v>249.705</v>
+        <v>252.39</v>
       </c>
       <c r="G95">
         <v>70</v>
@@ -9077,37 +9077,37 @@
         <v>28.732</v>
       </c>
       <c r="M95">
-        <v>50.140764</v>
+        <v>50.679912</v>
       </c>
       <c r="N95">
-        <v>-21.40876400000001</v>
+        <v>-21.947912</v>
       </c>
       <c r="O95">
-        <v>-3.853577520000001</v>
+        <v>-3.95062416</v>
       </c>
       <c r="P95">
-        <v>-17.55518648</v>
+        <v>-17.99728784</v>
       </c>
       <c r="Q95">
-        <v>-17.88718648</v>
+        <v>-18.32928784</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9439181216843986</v>
+        <v>1.093604475298465</v>
       </c>
       <c r="T95">
-        <v>15.14356178749991</v>
+        <v>17.66748875208323</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1031448184554986</v>
+        <v>0.1020475331527805</v>
       </c>
       <c r="W95">
-        <v>0.1800885204541359</v>
+        <v>0.1803088553429217</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5730267691972144</v>
+        <v>0.5669307397376696</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2351065925402543</v>
+        <v>0.2366565925402543</v>
       </c>
       <c r="C96">
-        <v>-90.14005509687863</v>
+        <v>-93.45771608658274</v>
       </c>
       <c r="D96">
-        <v>92.24994490312139</v>
+        <v>91.61728391341727</v>
       </c>
       <c r="E96">
-        <v>235.79</v>
+        <v>238.475</v>
       </c>
       <c r="F96">
-        <v>252.39</v>
+        <v>255.075</v>
       </c>
       <c r="G96">
         <v>70</v>
@@ -9159,37 +9159,37 @@
         <v>28.732</v>
       </c>
       <c r="M96">
-        <v>50.679912</v>
+        <v>51.21906000000001</v>
       </c>
       <c r="N96">
-        <v>-21.947912</v>
+        <v>-22.48706000000001</v>
       </c>
       <c r="O96">
-        <v>-3.95062416</v>
+        <v>-4.047670800000001</v>
       </c>
       <c r="P96">
-        <v>-17.99728784</v>
+        <v>-18.4393892</v>
       </c>
       <c r="Q96">
-        <v>-18.32928784</v>
+        <v>-18.77138920000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.093604475298465</v>
+        <v>1.303165370358159</v>
       </c>
       <c r="T96">
-        <v>17.66748875208323</v>
+        <v>21.20098650249989</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1020475331527805</v>
+        <v>0.1009733485932776</v>
       </c>
       <c r="W96">
-        <v>0.1803088553429217</v>
+        <v>0.1805245516024699</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5669307397376696</v>
+        <v>0.5609630477404309</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2366565925402543</v>
+        <v>0.2382065925402543</v>
       </c>
       <c r="C97">
-        <v>-93.45771608658274</v>
+        <v>-96.76675845659923</v>
       </c>
       <c r="D97">
-        <v>91.61728391341727</v>
+        <v>90.9932415434008</v>
       </c>
       <c r="E97">
-        <v>238.475</v>
+        <v>241.1600000000001</v>
       </c>
       <c r="F97">
-        <v>255.075</v>
+        <v>257.76</v>
       </c>
       <c r="G97">
         <v>70</v>
@@ -9241,37 +9241,37 @@
         <v>28.732</v>
       </c>
       <c r="M97">
-        <v>51.21906000000001</v>
+        <v>51.75820800000001</v>
       </c>
       <c r="N97">
-        <v>-22.48706000000001</v>
+        <v>-23.02620800000001</v>
       </c>
       <c r="O97">
-        <v>-4.047670800000001</v>
+        <v>-4.144717440000002</v>
       </c>
       <c r="P97">
-        <v>-18.4393892</v>
+        <v>-18.88149056000001</v>
       </c>
       <c r="Q97">
-        <v>-18.77138920000001</v>
+        <v>-19.21349056000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.303165370358159</v>
+        <v>1.617506712947699</v>
       </c>
       <c r="T97">
-        <v>21.20098650249989</v>
+        <v>26.50123312812487</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1009733485932776</v>
+        <v>0.09992154287876424</v>
       </c>
       <c r="W97">
-        <v>0.1805245516024699</v>
+        <v>0.1807357541899441</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5609630477404309</v>
+        <v>0.5551196826598014</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2382065925402542</v>
+        <v>0.2397565925402542</v>
       </c>
       <c r="C98">
-        <v>-96.76675845659918</v>
+        <v>-100.0673571301671</v>
       </c>
       <c r="D98">
-        <v>90.9932415434008</v>
+        <v>90.37764286983291</v>
       </c>
       <c r="E98">
-        <v>241.16</v>
+        <v>243.845</v>
       </c>
       <c r="F98">
-        <v>257.76</v>
+        <v>260.445</v>
       </c>
       <c r="G98">
         <v>70</v>
@@ -9323,37 +9323,37 @@
         <v>28.732</v>
       </c>
       <c r="M98">
-        <v>51.758208</v>
+        <v>52.297356</v>
       </c>
       <c r="N98">
-        <v>-23.026208</v>
+        <v>-23.565356</v>
       </c>
       <c r="O98">
-        <v>-4.144717440000001</v>
+        <v>-4.24176408</v>
       </c>
       <c r="P98">
-        <v>-18.88149056</v>
+        <v>-19.32359192</v>
       </c>
       <c r="Q98">
-        <v>-19.21349056</v>
+        <v>-19.65559192</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.617506712947695</v>
+        <v>2.141408950596927</v>
       </c>
       <c r="T98">
-        <v>26.5012331281248</v>
+        <v>35.3349775041664</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09992154287876427</v>
+        <v>0.09889142388001412</v>
       </c>
       <c r="W98">
-        <v>0.1807357541899441</v>
+        <v>0.1809426020848932</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5551196826598015</v>
+        <v>0.5493967993334118</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2397565925402542</v>
+        <v>0.2413065925402542</v>
       </c>
       <c r="C99">
-        <v>-100.0673571301671</v>
+        <v>-103.3596823286861</v>
       </c>
       <c r="D99">
-        <v>90.37764286983291</v>
+        <v>89.77031767131395</v>
       </c>
       <c r="E99">
-        <v>243.845</v>
+        <v>246.53</v>
       </c>
       <c r="F99">
-        <v>260.445</v>
+        <v>263.13</v>
       </c>
       <c r="G99">
         <v>70</v>
@@ -9405,37 +9405,37 @@
         <v>28.732</v>
       </c>
       <c r="M99">
-        <v>52.297356</v>
+        <v>52.836504</v>
       </c>
       <c r="N99">
-        <v>-23.565356</v>
+        <v>-24.104504</v>
       </c>
       <c r="O99">
-        <v>-4.24176408</v>
+        <v>-4.33881072</v>
       </c>
       <c r="P99">
-        <v>-19.32359192</v>
+        <v>-19.76569328</v>
       </c>
       <c r="Q99">
-        <v>-19.65559192</v>
+        <v>-20.09769328</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.141408950596927</v>
+        <v>3.18921342589539</v>
       </c>
       <c r="T99">
-        <v>35.3349775041664</v>
+        <v>53.0024662562496</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09889142388001412</v>
+        <v>0.09788232771797316</v>
       </c>
       <c r="W99">
-        <v>0.1809426020848932</v>
+        <v>0.181145228594231</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5493967993334118</v>
+        <v>0.5437907095442953</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2413065925402542</v>
+        <v>0.2428565925402542</v>
       </c>
       <c r="C100">
-        <v>-103.3596823286861</v>
+        <v>-106.6438997286403</v>
       </c>
       <c r="D100">
-        <v>89.77031767131395</v>
+        <v>89.17110027135971</v>
       </c>
       <c r="E100">
-        <v>246.53</v>
+        <v>249.215</v>
       </c>
       <c r="F100">
-        <v>263.13</v>
+        <v>265.815</v>
       </c>
       <c r="G100">
         <v>70</v>
@@ -9487,37 +9487,37 @@
         <v>28.732</v>
       </c>
       <c r="M100">
-        <v>52.836504</v>
+        <v>53.375652</v>
       </c>
       <c r="N100">
-        <v>-24.104504</v>
+        <v>-24.643652</v>
       </c>
       <c r="O100">
-        <v>-4.33881072</v>
+        <v>-4.43585736</v>
       </c>
       <c r="P100">
-        <v>-19.76569328</v>
+        <v>-20.20779464</v>
       </c>
       <c r="Q100">
-        <v>-20.09769328</v>
+        <v>-20.53979464</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.18921342589539</v>
+        <v>6.33262685179078</v>
       </c>
       <c r="T100">
-        <v>53.0024662562496</v>
+        <v>106.0049325124992</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09788232771797316</v>
+        <v>0.09689361733698353</v>
       </c>
       <c r="W100">
-        <v>0.181145228594231</v>
+        <v>0.1813437616387337</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5437907095442953</v>
+        <v>0.5382978740943529</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2428565925402542</v>
-      </c>
-      <c r="C101">
-        <v>-106.6438997286403</v>
-      </c>
-      <c r="D101">
-        <v>89.17110027135971</v>
-      </c>
-      <c r="E101">
-        <v>249.215</v>
-      </c>
-      <c r="F101">
-        <v>265.815</v>
-      </c>
-      <c r="G101">
-        <v>70</v>
-      </c>
-      <c r="H101">
-        <v>251.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.4</v>
-      </c>
-      <c r="K101">
-        <v>-0.332</v>
-      </c>
-      <c r="L101">
-        <v>28.732</v>
-      </c>
-      <c r="M101">
-        <v>53.375652</v>
-      </c>
-      <c r="N101">
-        <v>-24.643652</v>
-      </c>
-      <c r="O101">
-        <v>-4.43585736</v>
-      </c>
-      <c r="P101">
-        <v>-20.20779464</v>
-      </c>
-      <c r="Q101">
-        <v>-20.53979464</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.33262685179078</v>
-      </c>
-      <c r="T101">
-        <v>106.0049325124992</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09689361733698353</v>
-      </c>
-      <c r="W101">
-        <v>0.1813437616387337</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5382978740943529</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
